--- a/Fase 2/Sprint Backlogs/SIGMA_Sprint_Backlog_S2.xlsx
+++ b/Fase 2/Sprint Backlogs/SIGMA_Sprint_Backlog_S2.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Capstone\SIGMA\Fase 2\Sprint Backlogs\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Capstone\Fase 2\Sprint Backlogs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A2F9E0BA-75B2-46C1-9A9C-FF586AD234FB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{276DDB81-CE0E-4C3F-8E2D-5A7718621EF5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12720" tabRatio="500" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sprint" sheetId="1" r:id="rId1"/>
@@ -28,19 +28,6 @@
     <definedName name="_xlnm.Print_Titles" localSheetId="2">Tareas!$5:$5</definedName>
   </definedNames>
   <calcPr calcId="191029" iterateDelta="1E-4"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
 </workbook>
 </file>
 
@@ -101,81 +88,84 @@
     <t>Emilio Fuentes</t>
   </si>
   <si>
+    <t>Terminada</t>
+  </si>
+  <si>
+    <t>T-2002</t>
+  </si>
+  <si>
+    <t>SP SEL_ACTIVO: listado con filtros opcionales (id, texto, habilitado) y ORDER BY estable. Un solo SP sirve a la grilla y a la ficha.</t>
+  </si>
+  <si>
+    <t>T-2003</t>
+  </si>
+  <si>
+    <t>SP INS_ACTIVO: alta dentro de transacción. Valida código único por cliente y sella la fecha con FNC_PAIS_HORA.</t>
+  </si>
+  <si>
+    <t>T-2004</t>
+  </si>
+  <si>
+    <t>SP UPD_ACTIVO: edición. Los campos que la ficha no muestra se conservan con ISNULL(@X, columna) para no borrarlos al guardar.</t>
+  </si>
+  <si>
+    <t>T-2005</t>
+  </si>
+  <si>
+    <t>SP DEL_ACTIVO: baja lógica. Rechaza con mensaje si el registro tiene dependientes en vez de dejar huérfanos.</t>
+  </si>
+  <si>
+    <t>T-2006</t>
+  </si>
+  <si>
+    <t>Datos de prueba en Activo para poder ejercitar los criterios de aceptación.</t>
+  </si>
+  <si>
+    <t>T-2011</t>
+  </si>
+  <si>
+    <t>Listado Activos.aspx: grilla con búsqueda, filtro de habilitados y botón Nuevo.</t>
+  </si>
+  <si>
+    <t>Web</t>
+  </si>
+  <si>
+    <t>T-2012</t>
+  </si>
+  <si>
+    <t>Ficha Activo.aspx en RadWindow con las clases sigma-modal-*: campos, validadores y Guardar/Cerrar.</t>
+  </si>
+  <si>
+    <t>T-2013</t>
+  </si>
+  <si>
+    <t>Registrar ambas en Menus con su permiso: sin fila en Menus la pantalla no se abre.</t>
+  </si>
+  <si>
+    <t>T-2014</t>
+  </si>
+  <si>
+    <t>Permiso en el servidor: la acción se valida con Token.Puede / ExigirPagina, no escondiendo el botón. Y filtrar por cliente en sesión para que no se vea lo de otra empresa.</t>
+  </si>
+  <si>
+    <t>Seguridad</t>
+  </si>
+  <si>
+    <t>T-2015</t>
+  </si>
+  <si>
+    <t>Escribir y ejecutar un caso de prueba por cada criterio de aceptación de la historia, y dejar el resultado en la hoja Criterios de aceptación.</t>
+  </si>
+  <si>
+    <t>Pruebas</t>
+  </si>
+  <si>
+    <t>Catalina Pescio</t>
+  </si>
+  <si>
     <t>Por hacer</t>
   </si>
   <si>
-    <t>T-2002</t>
-  </si>
-  <si>
-    <t>SP SEL_ACTIVO: listado con filtros opcionales (id, texto, habilitado) y ORDER BY estable. Un solo SP sirve a la grilla y a la ficha.</t>
-  </si>
-  <si>
-    <t>T-2003</t>
-  </si>
-  <si>
-    <t>SP INS_ACTIVO: alta dentro de transacción. Valida código único por cliente y sella la fecha con FNC_PAIS_HORA.</t>
-  </si>
-  <si>
-    <t>T-2004</t>
-  </si>
-  <si>
-    <t>SP UPD_ACTIVO: edición. Los campos que la ficha no muestra se conservan con ISNULL(@X, columna) para no borrarlos al guardar.</t>
-  </si>
-  <si>
-    <t>T-2005</t>
-  </si>
-  <si>
-    <t>SP DEL_ACTIVO: baja lógica. Rechaza con mensaje si el registro tiene dependientes en vez de dejar huérfanos.</t>
-  </si>
-  <si>
-    <t>T-2006</t>
-  </si>
-  <si>
-    <t>Datos de prueba en Activo para poder ejercitar los criterios de aceptación.</t>
-  </si>
-  <si>
-    <t>T-2011</t>
-  </si>
-  <si>
-    <t>Listado Activos.aspx: grilla con búsqueda, filtro de habilitados y botón Nuevo.</t>
-  </si>
-  <si>
-    <t>Web</t>
-  </si>
-  <si>
-    <t>T-2012</t>
-  </si>
-  <si>
-    <t>Ficha Activo.aspx en RadWindow con las clases sigma-modal-*: campos, validadores y Guardar/Cerrar.</t>
-  </si>
-  <si>
-    <t>T-2013</t>
-  </si>
-  <si>
-    <t>Registrar ambas en Menus con su permiso: sin fila en Menus la pantalla no se abre.</t>
-  </si>
-  <si>
-    <t>T-2014</t>
-  </si>
-  <si>
-    <t>Permiso en el servidor: la acción se valida con Token.Puede / ExigirPagina, no escondiendo el botón. Y filtrar por cliente en sesión para que no se vea lo de otra empresa.</t>
-  </si>
-  <si>
-    <t>Seguridad</t>
-  </si>
-  <si>
-    <t>T-2015</t>
-  </si>
-  <si>
-    <t>Escribir y ejecutar un caso de prueba por cada criterio de aceptación de la historia, y dejar el resultado en la hoja Criterios de aceptación.</t>
-  </si>
-  <si>
-    <t>Pruebas</t>
-  </si>
-  <si>
-    <t>Catalina Pescio</t>
-  </si>
-  <si>
     <t>T-2016</t>
   </si>
   <si>
@@ -735,9 +725,6 @@
   </si>
   <si>
     <t>Modelo: revisar Suscripcion — columnas, FK e índices. Confirmar el índice único del código dentro del cliente.</t>
-  </si>
-  <si>
-    <t>Terminada</t>
   </si>
   <si>
     <t>Modelo revisado. Suscripcion, Suscripcion_Periodo y Suscripcion_Pago vienen del bloque 41; las guardas de tope y las 2 FK que faltaban en Cliente_Instalacion_Usuario, del bloque 47. · Terminada el 02-09-2026 (miércoles) por Bryan Chávez. Es anterior al inicio del Sprint 2 (16-09): trabajo adelantado, igual que el del 30-08.</t>
@@ -2989,57 +2976,6 @@
 </styleSheet>
 </file>
 
-<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>1</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>1257120</xdr:colOff>
-      <xdr:row>3</xdr:row>
-      <xdr:rowOff>37440</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="2" name="Image 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000002000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="211320" y="190440"/>
-          <a:ext cx="1257120" cy="418680"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:ln w="0">
-          <a:noFill/>
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-</xdr:wsDr>
-</file>
-
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
@@ -3368,7 +3304,7 @@
         <v>528</v>
       </c>
       <c r="C22" s="21" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="D22" s="19"/>
       <c r="E22" s="19"/>
@@ -3598,7 +3534,6 @@
   <headerFooter>
     <oddFooter>&amp;C&amp;8 SIGMA · Sprint Backlog · Sprint 2 · &amp;A · Página &amp;P de &amp;N</oddFooter>
   </headerFooter>
-  <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -3758,20 +3693,20 @@
         <v>9.25</v>
       </c>
       <c r="N6" s="11" t="s">
-        <v>18</v>
+        <v>43</v>
       </c>
       <c r="O6" s="12"/>
       <c r="P6" s="12"/>
     </row>
     <row r="7" spans="1:16" ht="82.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="13" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B7" s="13" t="s">
         <v>548</v>
       </c>
       <c r="C7" s="14" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D7" s="14" t="s">
         <v>569</v>
@@ -3805,20 +3740,20 @@
         <v>3.25</v>
       </c>
       <c r="N7" s="13" t="s">
-        <v>18</v>
+        <v>43</v>
       </c>
       <c r="O7" s="14"/>
       <c r="P7" s="14"/>
     </row>
     <row r="8" spans="1:16" ht="55.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="11" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="B8" s="11" t="s">
         <v>550</v>
       </c>
       <c r="C8" s="12" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="D8" s="12" t="s">
         <v>576</v>
@@ -3852,20 +3787,20 @@
         <v>16</v>
       </c>
       <c r="N8" s="11" t="s">
-        <v>18</v>
+        <v>43</v>
       </c>
       <c r="O8" s="12"/>
       <c r="P8" s="12"/>
     </row>
     <row r="9" spans="1:16" ht="41.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="13" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="B9" s="13" t="s">
         <v>546</v>
       </c>
       <c r="C9" s="14" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="D9" s="14" t="s">
         <v>580</v>
@@ -3899,20 +3834,20 @@
         <v>7.5</v>
       </c>
       <c r="N9" s="13" t="s">
-        <v>18</v>
+        <v>43</v>
       </c>
       <c r="O9" s="14"/>
       <c r="P9" s="14"/>
     </row>
     <row r="10" spans="1:16" ht="69" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="11" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="B10" s="11" t="s">
         <v>548</v>
       </c>
       <c r="C10" s="12" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="D10" s="12" t="s">
         <v>576</v>
@@ -3936,7 +3871,7 @@
         <v>572</v>
       </c>
       <c r="K10" s="12" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="L10" s="11">
         <v>3</v>
@@ -3946,7 +3881,7 @@
         <v>3.75</v>
       </c>
       <c r="N10" s="11" t="s">
-        <v>18</v>
+        <v>43</v>
       </c>
       <c r="O10" s="12"/>
       <c r="P10" s="12" t="s">
@@ -3955,13 +3890,13 @@
     </row>
     <row r="11" spans="1:16" ht="55.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="13" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="B11" s="13" t="s">
         <v>550</v>
       </c>
       <c r="C11" s="14" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="D11" s="14" t="s">
         <v>576</v>
@@ -3995,20 +3930,20 @@
         <v>6.25</v>
       </c>
       <c r="N11" s="13" t="s">
-        <v>18</v>
+        <v>43</v>
       </c>
       <c r="O11" s="14"/>
       <c r="P11" s="14"/>
     </row>
     <row r="12" spans="1:16" ht="96.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="11" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="B12" s="11" t="s">
         <v>546</v>
       </c>
       <c r="C12" s="12" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="D12" s="12" t="s">
         <v>569</v>
@@ -4042,20 +3977,20 @@
         <v>5.5</v>
       </c>
       <c r="N12" s="11" t="s">
-        <v>18</v>
+        <v>43</v>
       </c>
       <c r="O12" s="12"/>
       <c r="P12" s="12"/>
     </row>
     <row r="13" spans="1:16" ht="69" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="13" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="B13" s="13" t="s">
         <v>546</v>
       </c>
       <c r="C13" s="14" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="D13" s="14" t="s">
         <v>569</v>
@@ -4089,20 +4024,20 @@
         <v>5.5</v>
       </c>
       <c r="N13" s="13" t="s">
-        <v>18</v>
+        <v>43</v>
       </c>
       <c r="O13" s="14"/>
       <c r="P13" s="14"/>
     </row>
     <row r="14" spans="1:16" ht="82.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="11" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="B14" s="11" t="s">
         <v>548</v>
       </c>
       <c r="C14" s="12" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="D14" s="12" t="s">
         <v>576</v>
@@ -4136,7 +4071,7 @@
         <v>6</v>
       </c>
       <c r="N14" s="11" t="s">
-        <v>18</v>
+        <v>43</v>
       </c>
       <c r="O14" s="12"/>
       <c r="P14" s="12" t="s">
@@ -4145,13 +4080,13 @@
     </row>
     <row r="15" spans="1:16" ht="82.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="13" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="B15" s="13" t="s">
         <v>552</v>
       </c>
       <c r="C15" s="14" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="D15" s="14" t="s">
         <v>598</v>
@@ -4188,7 +4123,7 @@
         <v>601</v>
       </c>
       <c r="O15" s="14" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="P15" s="14" t="s">
         <v>602</v>
@@ -4236,7 +4171,7 @@
         <v>4.5</v>
       </c>
       <c r="N16" s="11" t="s">
-        <v>18</v>
+        <v>43</v>
       </c>
       <c r="O16" s="12"/>
       <c r="P16" s="12"/>
@@ -4286,7 +4221,7 @@
         <v>601</v>
       </c>
       <c r="O17" s="14" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="P17" s="14" t="s">
         <v>608</v>
@@ -4324,7 +4259,7 @@
         <v>595</v>
       </c>
       <c r="K18" s="12" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="L18" s="11">
         <v>2</v>
@@ -4334,7 +4269,7 @@
         <v>3.5</v>
       </c>
       <c r="N18" s="11" t="s">
-        <v>18</v>
+        <v>43</v>
       </c>
       <c r="O18" s="12"/>
       <c r="P18" s="12"/>
@@ -4371,7 +4306,7 @@
         <v>595</v>
       </c>
       <c r="K19" s="14" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="L19" s="13">
         <v>2</v>
@@ -4381,7 +4316,7 @@
         <v>5.75</v>
       </c>
       <c r="N19" s="13" t="s">
-        <v>18</v>
+        <v>43</v>
       </c>
       <c r="O19" s="14"/>
       <c r="P19" s="14"/>
@@ -4431,7 +4366,7 @@
         <v>601</v>
       </c>
       <c r="O20" s="12" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="P20" s="12" t="s">
         <v>617</v>
@@ -4469,7 +4404,7 @@
         <v>595</v>
       </c>
       <c r="K21" s="14" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="L21" s="13">
         <v>3</v>
@@ -4482,7 +4417,7 @@
         <v>621</v>
       </c>
       <c r="O21" s="14" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="P21" s="14" t="s">
         <v>622</v>
@@ -4530,7 +4465,7 @@
         <v>5.5</v>
       </c>
       <c r="N22" s="11" t="s">
-        <v>18</v>
+        <v>43</v>
       </c>
       <c r="O22" s="12"/>
       <c r="P22" s="12"/>
@@ -4577,7 +4512,7 @@
         <v>5.5</v>
       </c>
       <c r="N23" s="13" t="s">
-        <v>18</v>
+        <v>43</v>
       </c>
       <c r="O23" s="14"/>
       <c r="P23" s="14"/>
@@ -4624,7 +4559,7 @@
         <v>3.5</v>
       </c>
       <c r="N24" s="11" t="s">
-        <v>18</v>
+        <v>43</v>
       </c>
       <c r="O24" s="12"/>
       <c r="P24" s="12"/>
@@ -4671,7 +4606,7 @@
         <v>3.25</v>
       </c>
       <c r="N25" s="13" t="s">
-        <v>18</v>
+        <v>43</v>
       </c>
       <c r="O25" s="14"/>
       <c r="P25" s="14"/>
@@ -4718,7 +4653,7 @@
         <v>5.5</v>
       </c>
       <c r="N26" s="11" t="s">
-        <v>18</v>
+        <v>43</v>
       </c>
       <c r="O26" s="12"/>
       <c r="P26" s="12"/>
@@ -4765,7 +4700,7 @@
         <v>5.5</v>
       </c>
       <c r="N27" s="13" t="s">
-        <v>18</v>
+        <v>43</v>
       </c>
       <c r="O27" s="14"/>
       <c r="P27" s="14"/>
@@ -5221,14 +5156,14 @@
         <v>42</v>
       </c>
       <c r="H16" s="11" t="s">
-        <v>18</v>
+        <v>43</v>
       </c>
       <c r="I16" s="11"/>
       <c r="J16" s="12"/>
     </row>
     <row r="17" spans="1:10" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="11" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B17" s="11" t="s">
         <v>13</v>
@@ -5237,10 +5172,10 @@
         <v>14</v>
       </c>
       <c r="D17" s="17" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E17" s="11" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F17" s="11">
         <v>0.5</v>
@@ -5249,14 +5184,14 @@
         <v>42</v>
       </c>
       <c r="H17" s="11" t="s">
-        <v>18</v>
+        <v>43</v>
       </c>
       <c r="I17" s="11"/>
       <c r="J17" s="12"/>
     </row>
     <row r="18" spans="1:10" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="11" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B18" s="11" t="s">
         <v>13</v>
@@ -5265,10 +5200,10 @@
         <v>14</v>
       </c>
       <c r="D18" s="17" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="E18" s="11" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F18" s="11">
         <v>0.25</v>
@@ -5277,23 +5212,23 @@
         <v>42</v>
       </c>
       <c r="H18" s="11" t="s">
-        <v>18</v>
+        <v>43</v>
       </c>
       <c r="I18" s="11"/>
       <c r="J18" s="12"/>
     </row>
     <row r="19" spans="1:10" ht="55.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="11" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B19" s="11" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C19" s="12" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D19" s="17" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="E19" s="11" t="s">
         <v>16</v>
@@ -5302,26 +5237,26 @@
         <v>0.5</v>
       </c>
       <c r="G19" s="12" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="H19" s="11" t="s">
-        <v>18</v>
+        <v>43</v>
       </c>
       <c r="I19" s="11"/>
       <c r="J19" s="12"/>
     </row>
     <row r="20" spans="1:10" ht="41.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="11" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B20" s="11" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C20" s="12" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D20" s="17" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="E20" s="11" t="s">
         <v>16</v>
@@ -5333,23 +5268,23 @@
         <v>17</v>
       </c>
       <c r="H20" s="11" t="s">
-        <v>18</v>
+        <v>43</v>
       </c>
       <c r="I20" s="11"/>
       <c r="J20" s="12"/>
     </row>
     <row r="21" spans="1:10" ht="41.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="11" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B21" s="11" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C21" s="12" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D21" s="17" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E21" s="11" t="s">
         <v>16</v>
@@ -5361,23 +5296,23 @@
         <v>42</v>
       </c>
       <c r="H21" s="11" t="s">
-        <v>18</v>
+        <v>43</v>
       </c>
       <c r="I21" s="11"/>
       <c r="J21" s="12"/>
     </row>
     <row r="22" spans="1:10" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="11" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B22" s="11" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C22" s="12" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D22" s="17" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E22" s="11" t="s">
         <v>16</v>
@@ -5386,26 +5321,26 @@
         <v>0.25</v>
       </c>
       <c r="G22" s="12" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="H22" s="11" t="s">
-        <v>18</v>
+        <v>43</v>
       </c>
       <c r="I22" s="11"/>
       <c r="J22" s="12"/>
     </row>
     <row r="23" spans="1:10" ht="41.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="11" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B23" s="11" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C23" s="12" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D23" s="17" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E23" s="11" t="s">
         <v>16</v>
@@ -5417,23 +5352,23 @@
         <v>17</v>
       </c>
       <c r="H23" s="11" t="s">
-        <v>18</v>
+        <v>43</v>
       </c>
       <c r="I23" s="11"/>
       <c r="J23" s="12"/>
     </row>
     <row r="24" spans="1:10" ht="41.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="11" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="B24" s="11" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C24" s="12" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D24" s="17" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="E24" s="11" t="s">
         <v>16</v>
@@ -5445,23 +5380,23 @@
         <v>42</v>
       </c>
       <c r="H24" s="11" t="s">
-        <v>18</v>
+        <v>43</v>
       </c>
       <c r="I24" s="11"/>
       <c r="J24" s="12"/>
     </row>
     <row r="25" spans="1:10" ht="41.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="11" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B25" s="11" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C25" s="12" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D25" s="17" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="E25" s="11" t="s">
         <v>31</v>
@@ -5473,23 +5408,23 @@
         <v>17</v>
       </c>
       <c r="H25" s="11" t="s">
-        <v>18</v>
+        <v>43</v>
       </c>
       <c r="I25" s="11"/>
       <c r="J25" s="12"/>
     </row>
     <row r="26" spans="1:10" ht="41.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="11" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B26" s="11" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C26" s="12" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D26" s="17" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="E26" s="11" t="s">
         <v>31</v>
@@ -5498,23 +5433,23 @@
         <v>0.25</v>
       </c>
       <c r="G26" s="12" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="H26" s="11" t="s">
-        <v>18</v>
+        <v>43</v>
       </c>
       <c r="I26" s="11"/>
       <c r="J26" s="12"/>
     </row>
     <row r="27" spans="1:10" ht="41.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="11" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B27" s="11" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C27" s="12" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D27" s="17" t="s">
         <v>35</v>
@@ -5529,20 +5464,20 @@
         <v>17</v>
       </c>
       <c r="H27" s="11" t="s">
-        <v>18</v>
+        <v>43</v>
       </c>
       <c r="I27" s="11"/>
       <c r="J27" s="12"/>
     </row>
     <row r="28" spans="1:10" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="11" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B28" s="11" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C28" s="12" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D28" s="17" t="s">
         <v>37</v>
@@ -5557,20 +5492,20 @@
         <v>17</v>
       </c>
       <c r="H28" s="11" t="s">
-        <v>18</v>
+        <v>43</v>
       </c>
       <c r="I28" s="11"/>
       <c r="J28" s="12"/>
     </row>
     <row r="29" spans="1:10" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" s="11" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B29" s="11" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C29" s="12" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D29" s="17" t="s">
         <v>40</v>
@@ -5585,26 +5520,26 @@
         <v>42</v>
       </c>
       <c r="H29" s="11" t="s">
-        <v>18</v>
+        <v>43</v>
       </c>
       <c r="I29" s="11"/>
       <c r="J29" s="12"/>
     </row>
     <row r="30" spans="1:10" ht="41.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A30" s="11" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B30" s="11" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C30" s="12" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D30" s="17" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E30" s="11" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F30" s="11">
         <v>0.25</v>
@@ -5613,23 +5548,23 @@
         <v>42</v>
       </c>
       <c r="H30" s="11" t="s">
-        <v>18</v>
+        <v>43</v>
       </c>
       <c r="I30" s="11"/>
       <c r="J30" s="12"/>
     </row>
     <row r="31" spans="1:10" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A31" s="11" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="B31" s="11" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C31" s="12" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="D31" s="17" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="E31" s="11" t="s">
         <v>16</v>
@@ -5638,26 +5573,26 @@
         <v>1.5</v>
       </c>
       <c r="G31" s="12" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="H31" s="11" t="s">
-        <v>18</v>
+        <v>43</v>
       </c>
       <c r="I31" s="11"/>
       <c r="J31" s="12"/>
     </row>
     <row r="32" spans="1:10" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A32" s="11" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B32" s="11" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C32" s="12" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="D32" s="17" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="E32" s="11" t="s">
         <v>16</v>
@@ -5669,23 +5604,23 @@
         <v>17</v>
       </c>
       <c r="H32" s="11" t="s">
-        <v>18</v>
+        <v>43</v>
       </c>
       <c r="I32" s="11"/>
       <c r="J32" s="12"/>
     </row>
     <row r="33" spans="1:10" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A33" s="11" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="B33" s="11" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C33" s="12" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="D33" s="17" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="E33" s="11" t="s">
         <v>16</v>
@@ -5697,23 +5632,23 @@
         <v>42</v>
       </c>
       <c r="H33" s="11" t="s">
-        <v>18</v>
+        <v>43</v>
       </c>
       <c r="I33" s="11"/>
       <c r="J33" s="12"/>
     </row>
     <row r="34" spans="1:10" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A34" s="11" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="B34" s="11" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C34" s="12" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="D34" s="17" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="E34" s="11" t="s">
         <v>16</v>
@@ -5722,57 +5657,57 @@
         <v>1.25</v>
       </c>
       <c r="G34" s="12" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="H34" s="11" t="s">
-        <v>18</v>
+        <v>43</v>
       </c>
       <c r="I34" s="11"/>
       <c r="J34" s="12"/>
     </row>
     <row r="35" spans="1:10" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A35" s="11" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B35" s="11" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C35" s="12" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="D35" s="17" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="E35" s="11" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="F35" s="11">
         <v>1.5</v>
       </c>
       <c r="G35" s="12" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="H35" s="11" t="s">
-        <v>18</v>
+        <v>43</v>
       </c>
       <c r="I35" s="11"/>
       <c r="J35" s="12"/>
     </row>
     <row r="36" spans="1:10" ht="55.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A36" s="11" t="s">
+        <v>86</v>
+      </c>
+      <c r="B36" s="11" t="s">
+        <v>74</v>
+      </c>
+      <c r="C36" s="12" t="s">
+        <v>75</v>
+      </c>
+      <c r="D36" s="17" t="s">
+        <v>87</v>
+      </c>
+      <c r="E36" s="11" t="s">
         <v>85</v>
-      </c>
-      <c r="B36" s="11" t="s">
-        <v>73</v>
-      </c>
-      <c r="C36" s="12" t="s">
-        <v>74</v>
-      </c>
-      <c r="D36" s="17" t="s">
-        <v>86</v>
-      </c>
-      <c r="E36" s="11" t="s">
-        <v>84</v>
       </c>
       <c r="F36" s="11">
         <v>1.25</v>
@@ -5781,82 +5716,82 @@
         <v>17</v>
       </c>
       <c r="H36" s="11" t="s">
-        <v>18</v>
+        <v>43</v>
       </c>
       <c r="I36" s="11"/>
       <c r="J36" s="12"/>
     </row>
     <row r="37" spans="1:10" ht="41.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A37" s="11" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B37" s="11" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C37" s="12" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="D37" s="17" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="E37" s="11" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="F37" s="11">
         <v>1.25</v>
       </c>
       <c r="G37" s="12" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="H37" s="11" t="s">
-        <v>18</v>
+        <v>43</v>
       </c>
       <c r="I37" s="11"/>
       <c r="J37" s="12"/>
     </row>
     <row r="38" spans="1:10" ht="41.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A38" s="11" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B38" s="11" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C38" s="12" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="D38" s="17" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="E38" s="11" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="F38" s="11">
         <v>0.75</v>
       </c>
       <c r="G38" s="12" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="H38" s="11" t="s">
-        <v>18</v>
+        <v>43</v>
       </c>
       <c r="I38" s="11"/>
       <c r="J38" s="12"/>
     </row>
     <row r="39" spans="1:10" ht="41.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A39" s="11" t="s">
+        <v>93</v>
+      </c>
+      <c r="B39" s="11" t="s">
+        <v>74</v>
+      </c>
+      <c r="C39" s="12" t="s">
+        <v>75</v>
+      </c>
+      <c r="D39" s="17" t="s">
+        <v>94</v>
+      </c>
+      <c r="E39" s="11" t="s">
         <v>92</v>
-      </c>
-      <c r="B39" s="11" t="s">
-        <v>73</v>
-      </c>
-      <c r="C39" s="12" t="s">
-        <v>74</v>
-      </c>
-      <c r="D39" s="17" t="s">
-        <v>93</v>
-      </c>
-      <c r="E39" s="11" t="s">
-        <v>91</v>
       </c>
       <c r="F39" s="11">
         <v>0.75</v>
@@ -5865,48 +5800,48 @@
         <v>17</v>
       </c>
       <c r="H39" s="11" t="s">
-        <v>18</v>
+        <v>43</v>
       </c>
       <c r="I39" s="11"/>
       <c r="J39" s="12"/>
     </row>
     <row r="40" spans="1:10" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A40" s="11" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="B40" s="11" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C40" s="12" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="D40" s="17" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="E40" s="11" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="F40" s="11">
         <v>0.75</v>
       </c>
       <c r="G40" s="12" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="H40" s="11" t="s">
-        <v>18</v>
+        <v>43</v>
       </c>
       <c r="I40" s="11"/>
       <c r="J40" s="12"/>
     </row>
     <row r="41" spans="1:10" ht="41.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A41" s="11" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="B41" s="11" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C41" s="12" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="D41" s="17" t="s">
         <v>37</v>
@@ -5918,23 +5853,23 @@
         <v>1.5</v>
       </c>
       <c r="G41" s="12" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="H41" s="11" t="s">
-        <v>18</v>
+        <v>43</v>
       </c>
       <c r="I41" s="11"/>
       <c r="J41" s="12"/>
     </row>
     <row r="42" spans="1:10" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A42" s="11" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="B42" s="11" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C42" s="12" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="D42" s="17" t="s">
         <v>40</v>
@@ -5949,26 +5884,26 @@
         <v>42</v>
       </c>
       <c r="H42" s="11" t="s">
-        <v>18</v>
+        <v>43</v>
       </c>
       <c r="I42" s="11"/>
       <c r="J42" s="12"/>
     </row>
     <row r="43" spans="1:10" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A43" s="11" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="B43" s="11" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C43" s="12" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="D43" s="17" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E43" s="11" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F43" s="11">
         <v>0.75</v>
@@ -5977,26 +5912,26 @@
         <v>42</v>
       </c>
       <c r="H43" s="11" t="s">
-        <v>18</v>
+        <v>43</v>
       </c>
       <c r="I43" s="11"/>
       <c r="J43" s="12"/>
     </row>
     <row r="44" spans="1:10" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A44" s="11" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="B44" s="11" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C44" s="12" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="D44" s="17" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="E44" s="11" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F44" s="11">
         <v>0.5</v>
@@ -6005,20 +5940,20 @@
         <v>42</v>
       </c>
       <c r="H44" s="11" t="s">
-        <v>18</v>
+        <v>43</v>
       </c>
       <c r="I44" s="11"/>
       <c r="J44" s="12"/>
     </row>
     <row r="45" spans="1:10" ht="41.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A45" s="11" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="B45" s="11" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C45" s="12" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="D45" s="17" t="s">
         <v>15</v>
@@ -6033,23 +5968,23 @@
         <v>17</v>
       </c>
       <c r="H45" s="11" t="s">
-        <v>18</v>
+        <v>43</v>
       </c>
       <c r="I45" s="11"/>
       <c r="J45" s="12"/>
     </row>
     <row r="46" spans="1:10" ht="41.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A46" s="11" t="s">
+        <v>104</v>
+      </c>
+      <c r="B46" s="11" t="s">
+        <v>102</v>
+      </c>
+      <c r="C46" s="12" t="s">
         <v>103</v>
       </c>
-      <c r="B46" s="11" t="s">
-        <v>101</v>
-      </c>
-      <c r="C46" s="12" t="s">
-        <v>102</v>
-      </c>
       <c r="D46" s="17" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="E46" s="11" t="s">
         <v>16</v>
@@ -6061,23 +5996,23 @@
         <v>42</v>
       </c>
       <c r="H46" s="11" t="s">
-        <v>18</v>
+        <v>43</v>
       </c>
       <c r="I46" s="11"/>
       <c r="J46" s="12"/>
     </row>
     <row r="47" spans="1:10" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A47" s="11" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="B47" s="11" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C47" s="12" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="D47" s="17" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="E47" s="11" t="s">
         <v>16</v>
@@ -6086,23 +6021,23 @@
         <v>0.5</v>
       </c>
       <c r="G47" s="12" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="H47" s="11" t="s">
-        <v>18</v>
+        <v>43</v>
       </c>
       <c r="I47" s="11"/>
       <c r="J47" s="12"/>
     </row>
     <row r="48" spans="1:10" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A48" s="11" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="B48" s="11" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C48" s="12" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="D48" s="17" t="s">
         <v>28</v>
@@ -6117,26 +6052,26 @@
         <v>17</v>
       </c>
       <c r="H48" s="11" t="s">
-        <v>18</v>
+        <v>43</v>
       </c>
       <c r="I48" s="11"/>
       <c r="J48" s="12"/>
     </row>
     <row r="49" spans="1:10" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A49" s="11" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="B49" s="11" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C49" s="12" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="D49" s="17" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="E49" s="11" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="F49" s="11">
         <v>0.75</v>
@@ -6145,51 +6080,51 @@
         <v>17</v>
       </c>
       <c r="H49" s="11" t="s">
-        <v>18</v>
+        <v>43</v>
       </c>
       <c r="I49" s="11"/>
       <c r="J49" s="12"/>
     </row>
     <row r="50" spans="1:10" ht="55.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A50" s="11" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="B50" s="11" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C50" s="12" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="D50" s="17" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="E50" s="11" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="F50" s="11">
         <v>0.75</v>
       </c>
       <c r="G50" s="12" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="H50" s="11" t="s">
-        <v>18</v>
+        <v>43</v>
       </c>
       <c r="I50" s="11"/>
       <c r="J50" s="12"/>
     </row>
     <row r="51" spans="1:10" ht="41.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A51" s="11" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="B51" s="11" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C51" s="12" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="D51" s="17" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="E51" s="11" t="s">
         <v>31</v>
@@ -6201,26 +6136,26 @@
         <v>17</v>
       </c>
       <c r="H51" s="11" t="s">
-        <v>18</v>
+        <v>43</v>
       </c>
       <c r="I51" s="11"/>
       <c r="J51" s="12"/>
     </row>
     <row r="52" spans="1:10" ht="41.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A52" s="11" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="B52" s="11" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C52" s="12" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="D52" s="17" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="E52" s="11" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="F52" s="11">
         <v>0.75</v>
@@ -6229,20 +6164,20 @@
         <v>17</v>
       </c>
       <c r="H52" s="11" t="s">
-        <v>18</v>
+        <v>43</v>
       </c>
       <c r="I52" s="11"/>
       <c r="J52" s="12"/>
     </row>
     <row r="53" spans="1:10" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A53" s="11" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="B53" s="11" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C53" s="12" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="D53" s="17" t="s">
         <v>37</v>
@@ -6257,20 +6192,20 @@
         <v>17</v>
       </c>
       <c r="H53" s="11" t="s">
-        <v>18</v>
+        <v>43</v>
       </c>
       <c r="I53" s="11"/>
       <c r="J53" s="12"/>
     </row>
     <row r="54" spans="1:10" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A54" s="11" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="B54" s="11" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C54" s="12" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="D54" s="17" t="s">
         <v>40</v>
@@ -6285,26 +6220,26 @@
         <v>42</v>
       </c>
       <c r="H54" s="11" t="s">
-        <v>18</v>
+        <v>43</v>
       </c>
       <c r="I54" s="11"/>
       <c r="J54" s="12"/>
     </row>
     <row r="55" spans="1:10" ht="41.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A55" s="11" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="B55" s="11" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C55" s="12" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="D55" s="17" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E55" s="11" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F55" s="11">
         <v>0.25</v>
@@ -6313,23 +6248,23 @@
         <v>42</v>
       </c>
       <c r="H55" s="11" t="s">
-        <v>18</v>
+        <v>43</v>
       </c>
       <c r="I55" s="11"/>
       <c r="J55" s="12"/>
     </row>
     <row r="56" spans="1:10" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A56" s="11" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="B56" s="11" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="C56" s="12" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="D56" s="17" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="E56" s="11" t="s">
         <v>16</v>
@@ -6341,23 +6276,23 @@
         <v>42</v>
       </c>
       <c r="H56" s="11" t="s">
-        <v>18</v>
+        <v>43</v>
       </c>
       <c r="I56" s="11"/>
       <c r="J56" s="12"/>
     </row>
     <row r="57" spans="1:10" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A57" s="11" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="B57" s="11" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="C57" s="12" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="D57" s="17" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="E57" s="11" t="s">
         <v>16</v>
@@ -6366,26 +6301,26 @@
         <v>0.5</v>
       </c>
       <c r="G57" s="12" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="H57" s="11" t="s">
-        <v>18</v>
+        <v>43</v>
       </c>
       <c r="I57" s="11"/>
       <c r="J57" s="12"/>
     </row>
     <row r="58" spans="1:10" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A58" s="11" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="B58" s="11" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="C58" s="12" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="D58" s="17" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="E58" s="11" t="s">
         <v>16</v>
@@ -6397,23 +6332,23 @@
         <v>17</v>
       </c>
       <c r="H58" s="11" t="s">
-        <v>18</v>
+        <v>43</v>
       </c>
       <c r="I58" s="11"/>
       <c r="J58" s="12"/>
     </row>
     <row r="59" spans="1:10" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A59" s="11" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="B59" s="11" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="C59" s="12" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="D59" s="17" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="E59" s="11" t="s">
         <v>16</v>
@@ -6425,23 +6360,23 @@
         <v>42</v>
       </c>
       <c r="H59" s="11" t="s">
-        <v>18</v>
+        <v>43</v>
       </c>
       <c r="I59" s="11"/>
       <c r="J59" s="12"/>
     </row>
     <row r="60" spans="1:10" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A60" s="11" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="B60" s="11" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="C60" s="12" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="D60" s="17" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="E60" s="11" t="s">
         <v>16</v>
@@ -6450,29 +6385,29 @@
         <v>0.25</v>
       </c>
       <c r="G60" s="12" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="H60" s="11" t="s">
-        <v>18</v>
+        <v>43</v>
       </c>
       <c r="I60" s="11"/>
       <c r="J60" s="12"/>
     </row>
     <row r="61" spans="1:10" ht="41.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A61" s="11" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="B61" s="11" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="C61" s="12" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="D61" s="17" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="E61" s="11" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="F61" s="11">
         <v>0.5</v>
@@ -6481,54 +6416,54 @@
         <v>17</v>
       </c>
       <c r="H61" s="11" t="s">
-        <v>18</v>
+        <v>43</v>
       </c>
       <c r="I61" s="11"/>
       <c r="J61" s="12"/>
     </row>
     <row r="62" spans="1:10" ht="55.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A62" s="11" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="B62" s="11" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="C62" s="12" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="D62" s="17" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="E62" s="11" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="F62" s="11">
         <v>0.25</v>
       </c>
       <c r="G62" s="12" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="H62" s="11" t="s">
-        <v>18</v>
+        <v>43</v>
       </c>
       <c r="I62" s="11"/>
       <c r="J62" s="12"/>
     </row>
     <row r="63" spans="1:10" ht="41.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A63" s="11" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="B63" s="11" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="C63" s="12" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="D63" s="17" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="E63" s="11" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="F63" s="11">
         <v>0.25</v>
@@ -6537,48 +6472,48 @@
         <v>17</v>
       </c>
       <c r="H63" s="11" t="s">
-        <v>18</v>
+        <v>43</v>
       </c>
       <c r="I63" s="11"/>
       <c r="J63" s="12"/>
     </row>
     <row r="64" spans="1:10" ht="41.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A64" s="11" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="B64" s="11" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="C64" s="12" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="D64" s="17" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="E64" s="11" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="F64" s="11">
         <v>0.25</v>
       </c>
       <c r="G64" s="12" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="H64" s="11" t="s">
-        <v>18</v>
+        <v>43</v>
       </c>
       <c r="I64" s="11"/>
       <c r="J64" s="12"/>
     </row>
     <row r="65" spans="1:10" ht="41.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A65" s="11" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="B65" s="11" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="C65" s="12" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="D65" s="17" t="s">
         <v>37</v>
@@ -6590,23 +6525,23 @@
         <v>0.25</v>
       </c>
       <c r="G65" s="12" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="H65" s="11" t="s">
-        <v>18</v>
+        <v>43</v>
       </c>
       <c r="I65" s="11"/>
       <c r="J65" s="12"/>
     </row>
     <row r="66" spans="1:10" ht="41.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A66" s="11" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="B66" s="11" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="C66" s="12" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="D66" s="17" t="s">
         <v>40</v>
@@ -6621,26 +6556,26 @@
         <v>42</v>
       </c>
       <c r="H66" s="11" t="s">
-        <v>18</v>
+        <v>43</v>
       </c>
       <c r="I66" s="11"/>
       <c r="J66" s="12"/>
     </row>
     <row r="67" spans="1:10" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A67" s="11" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="B67" s="11" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="C67" s="12" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="D67" s="17" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E67" s="11" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F67" s="11">
         <v>0.25</v>
@@ -6649,23 +6584,23 @@
         <v>42</v>
       </c>
       <c r="H67" s="11" t="s">
-        <v>18</v>
+        <v>43</v>
       </c>
       <c r="I67" s="11"/>
       <c r="J67" s="12"/>
     </row>
     <row r="68" spans="1:10" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A68" s="11" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="B68" s="11" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="C68" s="12" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="D68" s="17" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="E68" s="11" t="s">
         <v>16</v>
@@ -6677,23 +6612,23 @@
         <v>17</v>
       </c>
       <c r="H68" s="11" t="s">
-        <v>18</v>
+        <v>43</v>
       </c>
       <c r="I68" s="11"/>
       <c r="J68" s="12"/>
     </row>
     <row r="69" spans="1:10" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A69" s="11" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="B69" s="11" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="C69" s="12" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="D69" s="17" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="E69" s="11" t="s">
         <v>16</v>
@@ -6705,23 +6640,23 @@
         <v>42</v>
       </c>
       <c r="H69" s="11" t="s">
-        <v>18</v>
+        <v>43</v>
       </c>
       <c r="I69" s="11"/>
       <c r="J69" s="12"/>
     </row>
     <row r="70" spans="1:10" ht="41.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A70" s="11" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="B70" s="11" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="C70" s="12" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="D70" s="17" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="E70" s="11" t="s">
         <v>16</v>
@@ -6730,26 +6665,26 @@
         <v>0.5</v>
       </c>
       <c r="G70" s="12" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="H70" s="11" t="s">
-        <v>18</v>
+        <v>43</v>
       </c>
       <c r="I70" s="11"/>
       <c r="J70" s="12"/>
     </row>
     <row r="71" spans="1:10" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A71" s="11" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="B71" s="11" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="C71" s="12" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="D71" s="17" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="E71" s="11" t="s">
         <v>16</v>
@@ -6761,54 +6696,54 @@
         <v>17</v>
       </c>
       <c r="H71" s="11" t="s">
-        <v>18</v>
+        <v>43</v>
       </c>
       <c r="I71" s="11"/>
       <c r="J71" s="12"/>
     </row>
     <row r="72" spans="1:10" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A72" s="11" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="B72" s="11" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="C72" s="12" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="D72" s="17" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="E72" s="11" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="F72" s="11">
         <v>0.75</v>
       </c>
       <c r="G72" s="12" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="H72" s="11" t="s">
-        <v>18</v>
+        <v>43</v>
       </c>
       <c r="I72" s="11"/>
       <c r="J72" s="12"/>
     </row>
     <row r="73" spans="1:10" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A73" s="11" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="B73" s="11" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="C73" s="12" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="D73" s="17" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="E73" s="11" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="F73" s="11">
         <v>0.5</v>
@@ -6817,54 +6752,54 @@
         <v>17</v>
       </c>
       <c r="H73" s="11" t="s">
-        <v>18</v>
+        <v>43</v>
       </c>
       <c r="I73" s="11"/>
       <c r="J73" s="12"/>
     </row>
     <row r="74" spans="1:10" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A74" s="11" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="B74" s="11" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="C74" s="12" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="D74" s="17" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="E74" s="11" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="F74" s="11">
         <v>0.5</v>
       </c>
       <c r="G74" s="12" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="H74" s="11" t="s">
-        <v>18</v>
+        <v>43</v>
       </c>
       <c r="I74" s="11"/>
       <c r="J74" s="12"/>
     </row>
     <row r="75" spans="1:10" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A75" s="11" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="B75" s="11" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="C75" s="12" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="D75" s="17" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="E75" s="11" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="F75" s="11">
         <v>0.5</v>
@@ -6873,54 +6808,54 @@
         <v>17</v>
       </c>
       <c r="H75" s="11" t="s">
-        <v>18</v>
+        <v>43</v>
       </c>
       <c r="I75" s="11"/>
       <c r="J75" s="12"/>
     </row>
     <row r="76" spans="1:10" ht="55.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A76" s="11" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="B76" s="11" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="C76" s="12" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="D76" s="17" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="E76" s="11" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="F76" s="11">
         <v>0.25</v>
       </c>
       <c r="G76" s="12" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="H76" s="11" t="s">
-        <v>18</v>
+        <v>43</v>
       </c>
       <c r="I76" s="11"/>
       <c r="J76" s="12"/>
     </row>
     <row r="77" spans="1:10" ht="41.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A77" s="11" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="B77" s="11" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="C77" s="12" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="D77" s="17" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="E77" s="11" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="F77" s="11">
         <v>0.25</v>
@@ -6929,20 +6864,20 @@
         <v>17</v>
       </c>
       <c r="H77" s="11" t="s">
-        <v>18</v>
+        <v>43</v>
       </c>
       <c r="I77" s="11"/>
       <c r="J77" s="12"/>
     </row>
     <row r="78" spans="1:10" ht="41.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A78" s="11" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="B78" s="11" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="C78" s="12" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="D78" s="17" t="s">
         <v>37</v>
@@ -6957,20 +6892,20 @@
         <v>17</v>
       </c>
       <c r="H78" s="11" t="s">
-        <v>18</v>
+        <v>43</v>
       </c>
       <c r="I78" s="11"/>
       <c r="J78" s="12"/>
     </row>
     <row r="79" spans="1:10" ht="41.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A79" s="11" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="B79" s="11" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="C79" s="12" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="D79" s="17" t="s">
         <v>40</v>
@@ -6985,26 +6920,26 @@
         <v>42</v>
       </c>
       <c r="H79" s="11" t="s">
-        <v>18</v>
+        <v>43</v>
       </c>
       <c r="I79" s="11"/>
       <c r="J79" s="12"/>
     </row>
     <row r="80" spans="1:10" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A80" s="11" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="B80" s="11" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="C80" s="12" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="D80" s="17" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E80" s="11" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F80" s="11">
         <v>0.25</v>
@@ -7013,23 +6948,23 @@
         <v>42</v>
       </c>
       <c r="H80" s="11" t="s">
-        <v>18</v>
+        <v>43</v>
       </c>
       <c r="I80" s="11"/>
       <c r="J80" s="12"/>
     </row>
     <row r="81" spans="1:10" ht="41.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A81" s="11" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="B81" s="11" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="C81" s="12" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="D81" s="17" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="E81" s="11" t="s">
         <v>16</v>
@@ -7041,23 +6976,23 @@
         <v>42</v>
       </c>
       <c r="H81" s="11" t="s">
-        <v>18</v>
+        <v>43</v>
       </c>
       <c r="I81" s="11"/>
       <c r="J81" s="12"/>
     </row>
     <row r="82" spans="1:10" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A82" s="11" t="s">
+        <v>167</v>
+      </c>
+      <c r="B82" s="11" t="s">
+        <v>165</v>
+      </c>
+      <c r="C82" s="12" t="s">
         <v>166</v>
       </c>
-      <c r="B82" s="11" t="s">
-        <v>164</v>
-      </c>
-      <c r="C82" s="12" t="s">
-        <v>165</v>
-      </c>
       <c r="D82" s="17" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="E82" s="11" t="s">
         <v>16</v>
@@ -7066,26 +7001,26 @@
         <v>0.5</v>
       </c>
       <c r="G82" s="12" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="H82" s="11" t="s">
-        <v>18</v>
+        <v>43</v>
       </c>
       <c r="I82" s="11"/>
       <c r="J82" s="12"/>
     </row>
     <row r="83" spans="1:10" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A83" s="11" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="B83" s="11" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="C83" s="12" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="D83" s="17" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="E83" s="11" t="s">
         <v>16</v>
@@ -7097,23 +7032,23 @@
         <v>17</v>
       </c>
       <c r="H83" s="11" t="s">
-        <v>18</v>
+        <v>43</v>
       </c>
       <c r="I83" s="11"/>
       <c r="J83" s="12"/>
     </row>
     <row r="84" spans="1:10" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A84" s="11" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="B84" s="11" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="C84" s="12" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="D84" s="17" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="E84" s="11" t="s">
         <v>16</v>
@@ -7125,23 +7060,23 @@
         <v>42</v>
       </c>
       <c r="H84" s="11" t="s">
-        <v>18</v>
+        <v>43</v>
       </c>
       <c r="I84" s="11"/>
       <c r="J84" s="12"/>
     </row>
     <row r="85" spans="1:10" ht="41.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A85" s="11" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="B85" s="11" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="C85" s="12" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="D85" s="17" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="E85" s="11" t="s">
         <v>16</v>
@@ -7150,26 +7085,26 @@
         <v>0.5</v>
       </c>
       <c r="G85" s="12" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="H85" s="11" t="s">
-        <v>18</v>
+        <v>43</v>
       </c>
       <c r="I85" s="11"/>
       <c r="J85" s="12"/>
     </row>
     <row r="86" spans="1:10" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A86" s="11" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="B86" s="11" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="C86" s="12" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="D86" s="17" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="E86" s="11" t="s">
         <v>16</v>
@@ -7181,23 +7116,23 @@
         <v>17</v>
       </c>
       <c r="H86" s="11" t="s">
-        <v>18</v>
+        <v>43</v>
       </c>
       <c r="I86" s="11"/>
       <c r="J86" s="12"/>
     </row>
     <row r="87" spans="1:10" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A87" s="11" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="B87" s="11" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="C87" s="12" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="D87" s="17" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="E87" s="11" t="s">
         <v>31</v>
@@ -7209,23 +7144,23 @@
         <v>17</v>
       </c>
       <c r="H87" s="11" t="s">
-        <v>18</v>
+        <v>43</v>
       </c>
       <c r="I87" s="11"/>
       <c r="J87" s="12"/>
     </row>
     <row r="88" spans="1:10" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A88" s="11" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="B88" s="11" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="C88" s="12" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="D88" s="17" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="E88" s="11" t="s">
         <v>31</v>
@@ -7234,23 +7169,23 @@
         <v>0.5</v>
       </c>
       <c r="G88" s="12" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="H88" s="11" t="s">
-        <v>18</v>
+        <v>43</v>
       </c>
       <c r="I88" s="11"/>
       <c r="J88" s="12"/>
     </row>
     <row r="89" spans="1:10" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A89" s="11" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="B89" s="11" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="C89" s="12" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="D89" s="17" t="s">
         <v>35</v>
@@ -7265,20 +7200,20 @@
         <v>17</v>
       </c>
       <c r="H89" s="11" t="s">
-        <v>18</v>
+        <v>43</v>
       </c>
       <c r="I89" s="11"/>
       <c r="J89" s="12"/>
     </row>
     <row r="90" spans="1:10" ht="55.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A90" s="11" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="B90" s="11" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="C90" s="12" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="D90" s="17" t="s">
         <v>37</v>
@@ -7290,23 +7225,23 @@
         <v>0.5</v>
       </c>
       <c r="G90" s="12" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="H90" s="11" t="s">
-        <v>18</v>
+        <v>43</v>
       </c>
       <c r="I90" s="11"/>
       <c r="J90" s="12"/>
     </row>
     <row r="91" spans="1:10" ht="41.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A91" s="11" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="B91" s="11" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="C91" s="12" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="D91" s="17" t="s">
         <v>40</v>
@@ -7321,26 +7256,26 @@
         <v>42</v>
       </c>
       <c r="H91" s="11" t="s">
-        <v>18</v>
+        <v>43</v>
       </c>
       <c r="I91" s="11"/>
       <c r="J91" s="12"/>
     </row>
     <row r="92" spans="1:10" ht="41.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A92" s="11" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="B92" s="11" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="C92" s="12" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="D92" s="17" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E92" s="11" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F92" s="11">
         <v>0.25</v>
@@ -7349,23 +7284,23 @@
         <v>42</v>
       </c>
       <c r="H92" s="11" t="s">
-        <v>18</v>
+        <v>43</v>
       </c>
       <c r="I92" s="11"/>
       <c r="J92" s="12"/>
     </row>
     <row r="93" spans="1:10" ht="41.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A93" s="11" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="B93" s="11" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="C93" s="12" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="D93" s="17" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="E93" s="11" t="s">
         <v>16</v>
@@ -7377,23 +7312,23 @@
         <v>42</v>
       </c>
       <c r="H93" s="11" t="s">
-        <v>18</v>
+        <v>43</v>
       </c>
       <c r="I93" s="11"/>
       <c r="J93" s="12"/>
     </row>
     <row r="94" spans="1:10" ht="41.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A94" s="11" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="B94" s="11" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="C94" s="12" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="D94" s="17" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="E94" s="11" t="s">
         <v>16</v>
@@ -7402,26 +7337,26 @@
         <v>0.5</v>
       </c>
       <c r="G94" s="12" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="H94" s="11" t="s">
-        <v>18</v>
+        <v>43</v>
       </c>
       <c r="I94" s="11"/>
       <c r="J94" s="12"/>
     </row>
     <row r="95" spans="1:10" ht="41.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A95" s="11" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="B95" s="11" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="C95" s="12" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="D95" s="17" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="E95" s="11" t="s">
         <v>16</v>
@@ -7433,23 +7368,23 @@
         <v>17</v>
       </c>
       <c r="H95" s="11" t="s">
-        <v>18</v>
+        <v>43</v>
       </c>
       <c r="I95" s="11"/>
       <c r="J95" s="12"/>
     </row>
     <row r="96" spans="1:10" ht="41.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A96" s="11" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="B96" s="11" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="C96" s="12" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="D96" s="17" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="E96" s="11" t="s">
         <v>16</v>
@@ -7461,23 +7396,23 @@
         <v>42</v>
       </c>
       <c r="H96" s="11" t="s">
-        <v>18</v>
+        <v>43</v>
       </c>
       <c r="I96" s="11"/>
       <c r="J96" s="12"/>
     </row>
     <row r="97" spans="1:10" ht="41.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A97" s="11" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="B97" s="11" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="C97" s="12" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="D97" s="17" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="E97" s="11" t="s">
         <v>16</v>
@@ -7486,26 +7421,26 @@
         <v>0.5</v>
       </c>
       <c r="G97" s="12" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="H97" s="11" t="s">
-        <v>18</v>
+        <v>43</v>
       </c>
       <c r="I97" s="11"/>
       <c r="J97" s="12"/>
     </row>
     <row r="98" spans="1:10" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A98" s="11" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="B98" s="11" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="C98" s="12" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="D98" s="17" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="E98" s="11" t="s">
         <v>16</v>
@@ -7517,23 +7452,23 @@
         <v>17</v>
       </c>
       <c r="H98" s="11" t="s">
-        <v>18</v>
+        <v>43</v>
       </c>
       <c r="I98" s="11"/>
       <c r="J98" s="12"/>
     </row>
     <row r="99" spans="1:10" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A99" s="11" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="B99" s="11" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="C99" s="12" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="D99" s="17" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="E99" s="11" t="s">
         <v>31</v>
@@ -7542,26 +7477,26 @@
         <v>0.5</v>
       </c>
       <c r="G99" s="12" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="H99" s="11" t="s">
-        <v>18</v>
+        <v>43</v>
       </c>
       <c r="I99" s="11"/>
       <c r="J99" s="12"/>
     </row>
     <row r="100" spans="1:10" ht="41.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A100" s="11" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="B100" s="11" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="C100" s="12" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="D100" s="17" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="E100" s="11" t="s">
         <v>31</v>
@@ -7573,20 +7508,20 @@
         <v>17</v>
       </c>
       <c r="H100" s="11" t="s">
-        <v>18</v>
+        <v>43</v>
       </c>
       <c r="I100" s="11"/>
       <c r="J100" s="12"/>
     </row>
     <row r="101" spans="1:10" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A101" s="11" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="B101" s="11" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="C101" s="12" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="D101" s="17" t="s">
         <v>35</v>
@@ -7598,23 +7533,23 @@
         <v>0.5</v>
       </c>
       <c r="G101" s="12" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="H101" s="11" t="s">
-        <v>18</v>
+        <v>43</v>
       </c>
       <c r="I101" s="11"/>
       <c r="J101" s="12"/>
     </row>
     <row r="102" spans="1:10" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A102" s="11" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="B102" s="11" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="C102" s="12" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="D102" s="17" t="s">
         <v>37</v>
@@ -7629,20 +7564,20 @@
         <v>17</v>
       </c>
       <c r="H102" s="11" t="s">
-        <v>18</v>
+        <v>43</v>
       </c>
       <c r="I102" s="11"/>
       <c r="J102" s="12"/>
     </row>
     <row r="103" spans="1:10" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A103" s="11" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="B103" s="11" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="C103" s="12" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="D103" s="17" t="s">
         <v>40</v>
@@ -7657,26 +7592,26 @@
         <v>42</v>
       </c>
       <c r="H103" s="11" t="s">
-        <v>18</v>
+        <v>43</v>
       </c>
       <c r="I103" s="11"/>
       <c r="J103" s="12"/>
     </row>
     <row r="104" spans="1:10" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A104" s="11" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="B104" s="11" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="C104" s="12" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="D104" s="17" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E104" s="11" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F104" s="11">
         <v>0.25</v>
@@ -7685,23 +7620,23 @@
         <v>42</v>
       </c>
       <c r="H104" s="11" t="s">
-        <v>18</v>
+        <v>43</v>
       </c>
       <c r="I104" s="11"/>
       <c r="J104" s="12"/>
     </row>
     <row r="105" spans="1:10" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A105" s="11" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="B105" s="11" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="C105" s="12" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="D105" s="17" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="E105" s="11" t="s">
         <v>16</v>
@@ -7713,23 +7648,23 @@
         <v>42</v>
       </c>
       <c r="H105" s="11" t="s">
-        <v>18</v>
+        <v>43</v>
       </c>
       <c r="I105" s="11"/>
       <c r="J105" s="12"/>
     </row>
     <row r="106" spans="1:10" ht="55.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A106" s="11" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="B106" s="11" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="C106" s="12" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="D106" s="17" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="E106" s="11" t="s">
         <v>16</v>
@@ -7738,26 +7673,26 @@
         <v>0.5</v>
       </c>
       <c r="G106" s="12" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="H106" s="11" t="s">
-        <v>18</v>
+        <v>43</v>
       </c>
       <c r="I106" s="11"/>
       <c r="J106" s="12"/>
     </row>
     <row r="107" spans="1:10" ht="41.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A107" s="11" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="B107" s="11" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="C107" s="12" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="D107" s="17" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="E107" s="11" t="s">
         <v>16</v>
@@ -7769,23 +7704,23 @@
         <v>17</v>
       </c>
       <c r="H107" s="11" t="s">
-        <v>18</v>
+        <v>43</v>
       </c>
       <c r="I107" s="11"/>
       <c r="J107" s="12"/>
     </row>
     <row r="108" spans="1:10" ht="41.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A108" s="11" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="B108" s="11" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="C108" s="12" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="D108" s="17" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="E108" s="11" t="s">
         <v>16</v>
@@ -7797,23 +7732,23 @@
         <v>42</v>
       </c>
       <c r="H108" s="11" t="s">
-        <v>18</v>
+        <v>43</v>
       </c>
       <c r="I108" s="11"/>
       <c r="J108" s="12"/>
     </row>
     <row r="109" spans="1:10" ht="41.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A109" s="11" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="B109" s="11" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="C109" s="12" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="D109" s="17" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="E109" s="11" t="s">
         <v>16</v>
@@ -7822,29 +7757,29 @@
         <v>0.5</v>
       </c>
       <c r="G109" s="12" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="H109" s="11" t="s">
-        <v>18</v>
+        <v>43</v>
       </c>
       <c r="I109" s="11"/>
       <c r="J109" s="12"/>
     </row>
     <row r="110" spans="1:10" ht="41.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A110" s="11" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="B110" s="11" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="C110" s="12" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="D110" s="17" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="E110" s="11" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="F110" s="11">
         <v>0.75</v>
@@ -7853,54 +7788,54 @@
         <v>17</v>
       </c>
       <c r="H110" s="11" t="s">
-        <v>18</v>
+        <v>43</v>
       </c>
       <c r="I110" s="11"/>
       <c r="J110" s="12"/>
     </row>
     <row r="111" spans="1:10" ht="41.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A111" s="11" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="B111" s="11" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="C111" s="12" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="D111" s="17" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="E111" s="11" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="F111" s="11">
         <v>0.5</v>
       </c>
       <c r="G111" s="12" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="H111" s="11" t="s">
-        <v>18</v>
+        <v>43</v>
       </c>
       <c r="I111" s="11"/>
       <c r="J111" s="12"/>
     </row>
     <row r="112" spans="1:10" ht="41.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A112" s="11" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="B112" s="11" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="C112" s="12" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="D112" s="17" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="E112" s="11" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="F112" s="11">
         <v>0.5</v>
@@ -7909,48 +7844,48 @@
         <v>17</v>
       </c>
       <c r="H112" s="11" t="s">
-        <v>18</v>
+        <v>43</v>
       </c>
       <c r="I112" s="11"/>
       <c r="J112" s="12"/>
     </row>
     <row r="113" spans="1:10" ht="41.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A113" s="11" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="B113" s="11" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="C113" s="12" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="D113" s="17" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="E113" s="11" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="F113" s="11">
         <v>0.5</v>
       </c>
       <c r="G113" s="12" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="H113" s="11" t="s">
-        <v>18</v>
+        <v>43</v>
       </c>
       <c r="I113" s="11"/>
       <c r="J113" s="12"/>
     </row>
     <row r="114" spans="1:10" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A114" s="11" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="B114" s="11" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="C114" s="12" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="D114" s="17" t="s">
         <v>37</v>
@@ -7962,23 +7897,23 @@
         <v>0.5</v>
       </c>
       <c r="G114" s="12" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="H114" s="11" t="s">
-        <v>18</v>
+        <v>43</v>
       </c>
       <c r="I114" s="11"/>
       <c r="J114" s="12"/>
     </row>
     <row r="115" spans="1:10" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A115" s="11" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="B115" s="11" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="C115" s="12" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="D115" s="17" t="s">
         <v>40</v>
@@ -7993,26 +7928,26 @@
         <v>42</v>
       </c>
       <c r="H115" s="11" t="s">
-        <v>18</v>
+        <v>43</v>
       </c>
       <c r="I115" s="11"/>
       <c r="J115" s="12"/>
     </row>
     <row r="116" spans="1:10" ht="41.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A116" s="11" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="B116" s="11" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="C116" s="12" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="D116" s="17" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E116" s="11" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F116" s="11">
         <v>0.25</v>
@@ -8021,23 +7956,23 @@
         <v>42</v>
       </c>
       <c r="H116" s="11" t="s">
-        <v>18</v>
+        <v>43</v>
       </c>
       <c r="I116" s="11"/>
       <c r="J116" s="12"/>
     </row>
     <row r="117" spans="1:10" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A117" s="11" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="B117" s="11" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="C117" s="12" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="D117" s="17" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="E117" s="11" t="s">
         <v>16</v>
@@ -8046,10 +7981,10 @@
         <v>0.5</v>
       </c>
       <c r="G117" s="12" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="H117" s="11" t="s">
-        <v>230</v>
+        <v>18</v>
       </c>
       <c r="I117" s="11">
         <v>0.5</v>
@@ -8063,10 +7998,10 @@
         <v>232</v>
       </c>
       <c r="B118" s="11" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="C118" s="12" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="D118" s="17" t="s">
         <v>233</v>
@@ -8078,10 +8013,10 @@
         <v>0.5</v>
       </c>
       <c r="G118" s="12" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="H118" s="11" t="s">
-        <v>230</v>
+        <v>18</v>
       </c>
       <c r="I118" s="11">
         <v>0.5</v>
@@ -8095,10 +8030,10 @@
         <v>235</v>
       </c>
       <c r="B119" s="11" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="C119" s="12" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="D119" s="17" t="s">
         <v>236</v>
@@ -8110,10 +8045,10 @@
         <v>0.5</v>
       </c>
       <c r="G119" s="12" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="H119" s="11" t="s">
-        <v>230</v>
+        <v>18</v>
       </c>
       <c r="I119" s="11">
         <v>0.5</v>
@@ -8127,10 +8062,10 @@
         <v>238</v>
       </c>
       <c r="B120" s="11" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="C120" s="12" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="D120" s="17" t="s">
         <v>239</v>
@@ -8142,10 +8077,10 @@
         <v>0.5</v>
       </c>
       <c r="G120" s="12" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="H120" s="11" t="s">
-        <v>230</v>
+        <v>18</v>
       </c>
       <c r="I120" s="11">
         <v>0.5</v>
@@ -8159,10 +8094,10 @@
         <v>241</v>
       </c>
       <c r="B121" s="11" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="C121" s="12" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="D121" s="17" t="s">
         <v>242</v>
@@ -8174,10 +8109,10 @@
         <v>0.5</v>
       </c>
       <c r="G121" s="12" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="H121" s="11" t="s">
-        <v>230</v>
+        <v>18</v>
       </c>
       <c r="I121" s="11">
         <v>0.5</v>
@@ -8191,25 +8126,25 @@
         <v>244</v>
       </c>
       <c r="B122" s="11" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="C122" s="12" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="D122" s="17" t="s">
         <v>245</v>
       </c>
       <c r="E122" s="11" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="F122" s="11">
         <v>0.75</v>
       </c>
       <c r="G122" s="12" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="H122" s="11" t="s">
-        <v>230</v>
+        <v>18</v>
       </c>
       <c r="I122" s="11">
         <v>0.75</v>
@@ -8223,25 +8158,25 @@
         <v>247</v>
       </c>
       <c r="B123" s="11" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="C123" s="12" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="D123" s="17" t="s">
         <v>248</v>
       </c>
       <c r="E123" s="11" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="F123" s="11">
         <v>0.75</v>
       </c>
       <c r="G123" s="12" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="H123" s="11" t="s">
-        <v>230</v>
+        <v>18</v>
       </c>
       <c r="I123" s="11">
         <v>0.75</v>
@@ -8255,10 +8190,10 @@
         <v>250</v>
       </c>
       <c r="B124" s="11" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="C124" s="12" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="D124" s="17" t="s">
         <v>251</v>
@@ -8270,10 +8205,10 @@
         <v>1.25</v>
       </c>
       <c r="G124" s="12" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="H124" s="11" t="s">
-        <v>230</v>
+        <v>18</v>
       </c>
       <c r="I124" s="11">
         <v>1.25</v>
@@ -8287,16 +8222,16 @@
         <v>253</v>
       </c>
       <c r="B125" s="11" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="C125" s="12" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="D125" s="17" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="E125" s="11" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="F125" s="11">
         <v>0.75</v>
@@ -8305,7 +8240,7 @@
         <v>17</v>
       </c>
       <c r="H125" s="11" t="s">
-        <v>18</v>
+        <v>43</v>
       </c>
       <c r="I125" s="11"/>
       <c r="J125" s="12"/>
@@ -8315,10 +8250,10 @@
         <v>254</v>
       </c>
       <c r="B126" s="11" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="C126" s="12" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="D126" s="17" t="s">
         <v>37</v>
@@ -8330,10 +8265,10 @@
         <v>0.5</v>
       </c>
       <c r="G126" s="12" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="H126" s="11" t="s">
-        <v>230</v>
+        <v>18</v>
       </c>
       <c r="I126" s="11">
         <v>0.5</v>
@@ -8347,10 +8282,10 @@
         <v>256</v>
       </c>
       <c r="B127" s="11" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="C127" s="12" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="D127" s="17" t="s">
         <v>40</v>
@@ -8365,7 +8300,7 @@
         <v>42</v>
       </c>
       <c r="H127" s="11" t="s">
-        <v>18</v>
+        <v>43</v>
       </c>
       <c r="I127" s="11"/>
       <c r="J127" s="12"/>
@@ -8375,16 +8310,16 @@
         <v>257</v>
       </c>
       <c r="B128" s="11" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="C128" s="12" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="D128" s="17" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E128" s="11" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F128" s="11">
         <v>0.25</v>
@@ -8393,7 +8328,7 @@
         <v>42</v>
       </c>
       <c r="H128" s="11" t="s">
-        <v>18</v>
+        <v>43</v>
       </c>
       <c r="I128" s="11"/>
       <c r="J128" s="12"/>
@@ -8418,10 +8353,10 @@
         <v>0.5</v>
       </c>
       <c r="G129" s="12" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="H129" s="11" t="s">
-        <v>18</v>
+        <v>43</v>
       </c>
       <c r="I129" s="11"/>
       <c r="J129" s="12"/>
@@ -8449,7 +8384,7 @@
         <v>17</v>
       </c>
       <c r="H130" s="11" t="s">
-        <v>18</v>
+        <v>43</v>
       </c>
       <c r="I130" s="11"/>
       <c r="J130" s="12"/>
@@ -8477,7 +8412,7 @@
         <v>42</v>
       </c>
       <c r="H131" s="11" t="s">
-        <v>18</v>
+        <v>43</v>
       </c>
       <c r="I131" s="11"/>
       <c r="J131" s="12"/>
@@ -8502,10 +8437,10 @@
         <v>0.25</v>
       </c>
       <c r="G132" s="12" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="H132" s="11" t="s">
-        <v>18</v>
+        <v>43</v>
       </c>
       <c r="I132" s="11"/>
       <c r="J132" s="12"/>
@@ -8533,7 +8468,7 @@
         <v>17</v>
       </c>
       <c r="H133" s="11" t="s">
-        <v>18</v>
+        <v>43</v>
       </c>
       <c r="I133" s="11"/>
       <c r="J133" s="12"/>
@@ -8552,16 +8487,16 @@
         <v>270</v>
       </c>
       <c r="E134" s="11" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="F134" s="11">
         <v>0.5</v>
       </c>
       <c r="G134" s="12" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="H134" s="11" t="s">
-        <v>18</v>
+        <v>43</v>
       </c>
       <c r="I134" s="11"/>
       <c r="J134" s="12"/>
@@ -8580,7 +8515,7 @@
         <v>248</v>
       </c>
       <c r="E135" s="11" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="F135" s="11">
         <v>0.5</v>
@@ -8589,7 +8524,7 @@
         <v>17</v>
       </c>
       <c r="H135" s="11" t="s">
-        <v>18</v>
+        <v>43</v>
       </c>
       <c r="I135" s="11"/>
       <c r="J135" s="12"/>
@@ -8614,10 +8549,10 @@
         <v>0.75</v>
       </c>
       <c r="G136" s="12" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="H136" s="11" t="s">
-        <v>18</v>
+        <v>43</v>
       </c>
       <c r="I136" s="11"/>
       <c r="J136" s="12"/>
@@ -8633,19 +8568,19 @@
         <v>260</v>
       </c>
       <c r="D137" s="17" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="E137" s="11" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="F137" s="11">
         <v>0.25</v>
       </c>
       <c r="G137" s="12" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="H137" s="11" t="s">
-        <v>18</v>
+        <v>43</v>
       </c>
       <c r="I137" s="11"/>
       <c r="J137" s="12"/>
@@ -8670,10 +8605,10 @@
         <v>0.25</v>
       </c>
       <c r="G138" s="12" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="H138" s="11" t="s">
-        <v>18</v>
+        <v>43</v>
       </c>
       <c r="I138" s="11"/>
       <c r="J138" s="12"/>
@@ -8701,7 +8636,7 @@
         <v>42</v>
       </c>
       <c r="H139" s="11" t="s">
-        <v>18</v>
+        <v>43</v>
       </c>
       <c r="I139" s="11"/>
       <c r="J139" s="12"/>
@@ -8717,10 +8652,10 @@
         <v>260</v>
       </c>
       <c r="D140" s="17" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E140" s="11" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F140" s="11">
         <v>0.25</v>
@@ -8729,7 +8664,7 @@
         <v>42</v>
       </c>
       <c r="H140" s="11" t="s">
-        <v>18</v>
+        <v>43</v>
       </c>
       <c r="I140" s="11"/>
       <c r="J140" s="12"/>
@@ -8745,7 +8680,7 @@
         <v>280</v>
       </c>
       <c r="D141" s="17" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="E141" s="11" t="s">
         <v>16</v>
@@ -8754,10 +8689,10 @@
         <v>0.75</v>
       </c>
       <c r="G141" s="12" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="H141" s="11" t="s">
-        <v>230</v>
+        <v>18</v>
       </c>
       <c r="I141" s="11">
         <v>0.75</v>
@@ -8786,10 +8721,10 @@
         <v>0.5</v>
       </c>
       <c r="G142" s="12" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="H142" s="11" t="s">
-        <v>230</v>
+        <v>18</v>
       </c>
       <c r="I142" s="11">
         <v>0.5</v>
@@ -8818,10 +8753,10 @@
         <v>0.5</v>
       </c>
       <c r="G143" s="12" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="H143" s="11" t="s">
-        <v>230</v>
+        <v>18</v>
       </c>
       <c r="I143" s="11">
         <v>0.5</v>
@@ -8850,10 +8785,10 @@
         <v>0.5</v>
       </c>
       <c r="G144" s="12" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="H144" s="11" t="s">
-        <v>230</v>
+        <v>18</v>
       </c>
       <c r="I144" s="11">
         <v>0.5</v>
@@ -8882,10 +8817,10 @@
         <v>0.5</v>
       </c>
       <c r="G145" s="12" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="H145" s="11" t="s">
-        <v>230</v>
+        <v>18</v>
       </c>
       <c r="I145" s="11">
         <v>0.5</v>
@@ -8914,10 +8849,10 @@
         <v>0.75</v>
       </c>
       <c r="G146" s="12" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="H146" s="11" t="s">
-        <v>230</v>
+        <v>18</v>
       </c>
       <c r="I146" s="11">
         <v>0.75</v>
@@ -8946,10 +8881,10 @@
         <v>0.75</v>
       </c>
       <c r="G147" s="12" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="H147" s="11" t="s">
-        <v>230</v>
+        <v>18</v>
       </c>
       <c r="I147" s="11">
         <v>0.75</v>
@@ -8978,10 +8913,10 @@
         <v>0.5</v>
       </c>
       <c r="G148" s="12" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="H148" s="11" t="s">
-        <v>230</v>
+        <v>18</v>
       </c>
       <c r="I148" s="11">
         <v>0.5</v>
@@ -9013,7 +8948,7 @@
         <v>42</v>
       </c>
       <c r="H149" s="11" t="s">
-        <v>18</v>
+        <v>43</v>
       </c>
       <c r="I149" s="11"/>
       <c r="J149" s="12"/>
@@ -9029,10 +8964,10 @@
         <v>280</v>
       </c>
       <c r="D150" s="17" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E150" s="11" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F150" s="11">
         <v>0.25</v>
@@ -9041,7 +8976,7 @@
         <v>42</v>
       </c>
       <c r="H150" s="11" t="s">
-        <v>18</v>
+        <v>43</v>
       </c>
       <c r="I150" s="11"/>
       <c r="J150" s="12"/>
@@ -9057,7 +8992,7 @@
         <v>305</v>
       </c>
       <c r="D151" s="17" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="E151" s="11" t="s">
         <v>16</v>
@@ -9069,7 +9004,7 @@
         <v>17</v>
       </c>
       <c r="H151" s="11" t="s">
-        <v>18</v>
+        <v>43</v>
       </c>
       <c r="I151" s="11"/>
       <c r="J151" s="12"/>
@@ -9097,7 +9032,7 @@
         <v>42</v>
       </c>
       <c r="H152" s="11" t="s">
-        <v>18</v>
+        <v>43</v>
       </c>
       <c r="I152" s="11"/>
       <c r="J152" s="12"/>
@@ -9122,10 +9057,10 @@
         <v>0.5</v>
       </c>
       <c r="G153" s="12" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="H153" s="11" t="s">
-        <v>18</v>
+        <v>43</v>
       </c>
       <c r="I153" s="11"/>
       <c r="J153" s="12"/>
@@ -9153,7 +9088,7 @@
         <v>17</v>
       </c>
       <c r="H154" s="11" t="s">
-        <v>18</v>
+        <v>43</v>
       </c>
       <c r="I154" s="11"/>
       <c r="J154" s="12"/>
@@ -9169,7 +9104,7 @@
         <v>305</v>
       </c>
       <c r="D155" s="17" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="E155" s="11" t="s">
         <v>16</v>
@@ -9181,7 +9116,7 @@
         <v>42</v>
       </c>
       <c r="H155" s="11" t="s">
-        <v>18</v>
+        <v>43</v>
       </c>
       <c r="I155" s="11"/>
       <c r="J155" s="12"/>
@@ -9209,7 +9144,7 @@
         <v>17</v>
       </c>
       <c r="H156" s="11" t="s">
-        <v>18</v>
+        <v>43</v>
       </c>
       <c r="I156" s="11"/>
       <c r="J156" s="12"/>
@@ -9234,10 +9169,10 @@
         <v>0.25</v>
       </c>
       <c r="G157" s="12" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="H157" s="11" t="s">
-        <v>18</v>
+        <v>43</v>
       </c>
       <c r="I157" s="11"/>
       <c r="J157" s="12"/>
@@ -9265,7 +9200,7 @@
         <v>42</v>
       </c>
       <c r="H158" s="11" t="s">
-        <v>18</v>
+        <v>43</v>
       </c>
       <c r="I158" s="11"/>
       <c r="J158" s="12"/>
@@ -9281,10 +9216,10 @@
         <v>305</v>
       </c>
       <c r="D159" s="17" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E159" s="11" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F159" s="11">
         <v>0.25</v>
@@ -9293,7 +9228,7 @@
         <v>42</v>
       </c>
       <c r="H159" s="11" t="s">
-        <v>18</v>
+        <v>43</v>
       </c>
       <c r="I159" s="11"/>
       <c r="J159" s="12"/>
@@ -9309,7 +9244,7 @@
         <v>319</v>
       </c>
       <c r="D160" s="17" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="E160" s="11" t="s">
         <v>16</v>
@@ -9318,10 +9253,10 @@
         <v>0.75</v>
       </c>
       <c r="G160" s="12" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="H160" s="11" t="s">
-        <v>18</v>
+        <v>43</v>
       </c>
       <c r="I160" s="11"/>
       <c r="J160" s="12"/>
@@ -9349,7 +9284,7 @@
         <v>17</v>
       </c>
       <c r="H161" s="11" t="s">
-        <v>18</v>
+        <v>43</v>
       </c>
       <c r="I161" s="11"/>
       <c r="J161" s="12"/>
@@ -9377,7 +9312,7 @@
         <v>42</v>
       </c>
       <c r="H162" s="11" t="s">
-        <v>18</v>
+        <v>43</v>
       </c>
       <c r="I162" s="11"/>
       <c r="J162" s="12"/>
@@ -9393,7 +9328,7 @@
         <v>319</v>
       </c>
       <c r="D163" s="17" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="E163" s="11" t="s">
         <v>16</v>
@@ -9402,10 +9337,10 @@
         <v>0.5</v>
       </c>
       <c r="G163" s="12" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="H163" s="11" t="s">
-        <v>18</v>
+        <v>43</v>
       </c>
       <c r="I163" s="11"/>
       <c r="J163" s="12"/>
@@ -9430,10 +9365,10 @@
         <v>1.5</v>
       </c>
       <c r="G164" s="12" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="H164" s="11" t="s">
-        <v>18</v>
+        <v>43</v>
       </c>
       <c r="I164" s="11"/>
       <c r="J164" s="12"/>
@@ -9461,7 +9396,7 @@
         <v>17</v>
       </c>
       <c r="H165" s="11" t="s">
-        <v>18</v>
+        <v>43</v>
       </c>
       <c r="I165" s="11"/>
       <c r="J165" s="12"/>
@@ -9489,7 +9424,7 @@
         <v>42</v>
       </c>
       <c r="H166" s="11" t="s">
-        <v>18</v>
+        <v>43</v>
       </c>
       <c r="I166" s="11"/>
       <c r="J166" s="12"/>
@@ -9505,10 +9440,10 @@
         <v>319</v>
       </c>
       <c r="D167" s="17" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E167" s="11" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F167" s="11">
         <v>0.25</v>
@@ -9517,7 +9452,7 @@
         <v>42</v>
       </c>
       <c r="H167" s="11" t="s">
-        <v>18</v>
+        <v>43</v>
       </c>
       <c r="I167" s="11"/>
       <c r="J167" s="12"/>
@@ -9542,10 +9477,10 @@
         <v>0.5</v>
       </c>
       <c r="G168" s="12" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="H168" s="11" t="s">
-        <v>230</v>
+        <v>18</v>
       </c>
       <c r="I168" s="11">
         <v>0.5</v>
@@ -9574,10 +9509,10 @@
         <v>0.5</v>
       </c>
       <c r="G169" s="12" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="H169" s="11" t="s">
-        <v>230</v>
+        <v>18</v>
       </c>
       <c r="I169" s="11">
         <v>0.5</v>
@@ -9606,10 +9541,10 @@
         <v>0.5</v>
       </c>
       <c r="G170" s="12" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="H170" s="11" t="s">
-        <v>230</v>
+        <v>18</v>
       </c>
       <c r="I170" s="11">
         <v>0.5</v>
@@ -9638,10 +9573,10 @@
         <v>0.5</v>
       </c>
       <c r="G171" s="12" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="H171" s="11" t="s">
-        <v>230</v>
+        <v>18</v>
       </c>
       <c r="I171" s="11">
         <v>0.5</v>
@@ -9670,10 +9605,10 @@
         <v>0.5</v>
       </c>
       <c r="G172" s="12" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="H172" s="11" t="s">
-        <v>230</v>
+        <v>18</v>
       </c>
       <c r="I172" s="11">
         <v>0.5</v>
@@ -9702,10 +9637,10 @@
         <v>0.25</v>
       </c>
       <c r="G173" s="12" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="H173" s="11" t="s">
-        <v>230</v>
+        <v>18</v>
       </c>
       <c r="I173" s="11">
         <v>0.25</v>
@@ -9734,10 +9669,10 @@
         <v>0.5</v>
       </c>
       <c r="G174" s="12" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="H174" s="11" t="s">
-        <v>230</v>
+        <v>18</v>
       </c>
       <c r="I174" s="11">
         <v>0.5</v>
@@ -9766,10 +9701,10 @@
         <v>0.5</v>
       </c>
       <c r="G175" s="12" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="H175" s="11" t="s">
-        <v>230</v>
+        <v>18</v>
       </c>
       <c r="I175" s="11">
         <v>0.5</v>
@@ -9798,10 +9733,10 @@
         <v>0.5</v>
       </c>
       <c r="G176" s="12" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="H176" s="11" t="s">
-        <v>230</v>
+        <v>18</v>
       </c>
       <c r="I176" s="11">
         <v>0.5</v>
@@ -9830,10 +9765,10 @@
         <v>0.5</v>
       </c>
       <c r="G177" s="12" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="H177" s="11" t="s">
-        <v>230</v>
+        <v>18</v>
       </c>
       <c r="I177" s="11">
         <v>0.5</v>
@@ -9865,7 +9800,7 @@
         <v>42</v>
       </c>
       <c r="H178" s="11" t="s">
-        <v>18</v>
+        <v>43</v>
       </c>
       <c r="I178" s="11"/>
       <c r="J178" s="12"/>
@@ -9881,10 +9816,10 @@
         <v>332</v>
       </c>
       <c r="D179" s="17" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E179" s="11" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F179" s="11">
         <v>0.25</v>
@@ -9893,7 +9828,7 @@
         <v>42</v>
       </c>
       <c r="H179" s="11" t="s">
-        <v>18</v>
+        <v>43</v>
       </c>
       <c r="I179" s="11"/>
       <c r="J179" s="12"/>
@@ -9918,10 +9853,10 @@
         <v>0.75</v>
       </c>
       <c r="G180" s="12" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="H180" s="11" t="s">
-        <v>230</v>
+        <v>18</v>
       </c>
       <c r="I180" s="11">
         <v>0.75</v>
@@ -9950,10 +9885,10 @@
         <v>0.5</v>
       </c>
       <c r="G181" s="12" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="H181" s="11" t="s">
-        <v>230</v>
+        <v>18</v>
       </c>
       <c r="I181" s="11">
         <v>0.5</v>
@@ -9982,10 +9917,10 @@
         <v>0.5</v>
       </c>
       <c r="G182" s="12" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="H182" s="11" t="s">
-        <v>230</v>
+        <v>18</v>
       </c>
       <c r="I182" s="11">
         <v>0.5</v>
@@ -10014,10 +9949,10 @@
         <v>0.5</v>
       </c>
       <c r="G183" s="12" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="H183" s="11" t="s">
-        <v>230</v>
+        <v>18</v>
       </c>
       <c r="I183" s="11">
         <v>0.5</v>
@@ -10046,10 +9981,10 @@
         <v>0.5</v>
       </c>
       <c r="G184" s="12" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="H184" s="11" t="s">
-        <v>18</v>
+        <v>43</v>
       </c>
       <c r="I184" s="11"/>
       <c r="J184" s="12" t="s">
@@ -10076,10 +10011,10 @@
         <v>0.75</v>
       </c>
       <c r="G185" s="12" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="H185" s="11" t="s">
-        <v>230</v>
+        <v>18</v>
       </c>
       <c r="I185" s="11">
         <v>0.75</v>
@@ -10108,10 +10043,10 @@
         <v>0.75</v>
       </c>
       <c r="G186" s="12" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="H186" s="11" t="s">
-        <v>230</v>
+        <v>18</v>
       </c>
       <c r="I186" s="11">
         <v>0.75</v>
@@ -10140,10 +10075,10 @@
         <v>0.5</v>
       </c>
       <c r="G187" s="12" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="H187" s="11" t="s">
-        <v>230</v>
+        <v>18</v>
       </c>
       <c r="I187" s="11">
         <v>0.5</v>
@@ -10175,7 +10110,7 @@
         <v>42</v>
       </c>
       <c r="H188" s="11" t="s">
-        <v>18</v>
+        <v>43</v>
       </c>
       <c r="I188" s="11"/>
       <c r="J188" s="12"/>
@@ -10191,10 +10126,10 @@
         <v>364</v>
       </c>
       <c r="D189" s="17" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E189" s="11" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F189" s="11">
         <v>0.25</v>
@@ -10203,7 +10138,7 @@
         <v>42</v>
       </c>
       <c r="H189" s="11" t="s">
-        <v>18</v>
+        <v>43</v>
       </c>
       <c r="I189" s="11"/>
       <c r="J189" s="12"/>
@@ -10228,10 +10163,10 @@
         <v>0.5</v>
       </c>
       <c r="G190" s="12" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="H190" s="11" t="s">
-        <v>18</v>
+        <v>43</v>
       </c>
       <c r="I190" s="11"/>
       <c r="J190" s="12"/>
@@ -10259,7 +10194,7 @@
         <v>17</v>
       </c>
       <c r="H191" s="11" t="s">
-        <v>18</v>
+        <v>43</v>
       </c>
       <c r="I191" s="11"/>
       <c r="J191" s="12"/>
@@ -10287,7 +10222,7 @@
         <v>42</v>
       </c>
       <c r="H192" s="11" t="s">
-        <v>18</v>
+        <v>43</v>
       </c>
       <c r="I192" s="11"/>
       <c r="J192" s="12"/>
@@ -10312,10 +10247,10 @@
         <v>0.5</v>
       </c>
       <c r="G193" s="12" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="H193" s="11" t="s">
-        <v>18</v>
+        <v>43</v>
       </c>
       <c r="I193" s="11"/>
       <c r="J193" s="12"/>
@@ -10343,7 +10278,7 @@
         <v>17</v>
       </c>
       <c r="H194" s="11" t="s">
-        <v>18</v>
+        <v>43</v>
       </c>
       <c r="I194" s="11"/>
       <c r="J194" s="12"/>
@@ -10371,7 +10306,7 @@
         <v>42</v>
       </c>
       <c r="H195" s="11" t="s">
-        <v>18</v>
+        <v>43</v>
       </c>
       <c r="I195" s="11"/>
       <c r="J195" s="12"/>
@@ -10396,10 +10331,10 @@
         <v>0.5</v>
       </c>
       <c r="G196" s="12" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="H196" s="11" t="s">
-        <v>18</v>
+        <v>43</v>
       </c>
       <c r="I196" s="11"/>
       <c r="J196" s="12"/>
@@ -10427,7 +10362,7 @@
         <v>17</v>
       </c>
       <c r="H197" s="11" t="s">
-        <v>18</v>
+        <v>43</v>
       </c>
       <c r="I197" s="11"/>
       <c r="J197" s="12"/>
@@ -10452,10 +10387,10 @@
         <v>0.5</v>
       </c>
       <c r="G198" s="12" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="H198" s="11" t="s">
-        <v>18</v>
+        <v>43</v>
       </c>
       <c r="I198" s="11"/>
       <c r="J198" s="12"/>
@@ -10480,10 +10415,10 @@
         <v>0.5</v>
       </c>
       <c r="G199" s="12" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="H199" s="11" t="s">
-        <v>18</v>
+        <v>43</v>
       </c>
       <c r="I199" s="11"/>
       <c r="J199" s="12"/>
@@ -10511,7 +10446,7 @@
         <v>42</v>
       </c>
       <c r="H200" s="11" t="s">
-        <v>18</v>
+        <v>43</v>
       </c>
       <c r="I200" s="11"/>
       <c r="J200" s="12"/>
@@ -10527,10 +10462,10 @@
         <v>391</v>
       </c>
       <c r="D201" s="17" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E201" s="11" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F201" s="11">
         <v>0.25</v>
@@ -10539,7 +10474,7 @@
         <v>42</v>
       </c>
       <c r="H201" s="11" t="s">
-        <v>18</v>
+        <v>43</v>
       </c>
       <c r="I201" s="11"/>
       <c r="J201" s="12"/>
@@ -10564,10 +10499,10 @@
         <v>0.5</v>
       </c>
       <c r="G202" s="12" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="H202" s="11" t="s">
-        <v>18</v>
+        <v>43</v>
       </c>
       <c r="I202" s="11"/>
       <c r="J202" s="12"/>
@@ -10595,7 +10530,7 @@
         <v>17</v>
       </c>
       <c r="H203" s="11" t="s">
-        <v>18</v>
+        <v>43</v>
       </c>
       <c r="I203" s="11"/>
       <c r="J203" s="12"/>
@@ -10623,7 +10558,7 @@
         <v>42</v>
       </c>
       <c r="H204" s="11" t="s">
-        <v>18</v>
+        <v>43</v>
       </c>
       <c r="I204" s="11"/>
       <c r="J204" s="12"/>
@@ -10648,10 +10583,10 @@
         <v>0.5</v>
       </c>
       <c r="G205" s="12" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="H205" s="11" t="s">
-        <v>18</v>
+        <v>43</v>
       </c>
       <c r="I205" s="11"/>
       <c r="J205" s="12"/>
@@ -10679,7 +10614,7 @@
         <v>17</v>
       </c>
       <c r="H206" s="11" t="s">
-        <v>18</v>
+        <v>43</v>
       </c>
       <c r="I206" s="11"/>
       <c r="J206" s="12"/>
@@ -10707,7 +10642,7 @@
         <v>42</v>
       </c>
       <c r="H207" s="11" t="s">
-        <v>18</v>
+        <v>43</v>
       </c>
       <c r="I207" s="11"/>
       <c r="J207" s="12"/>
@@ -10735,7 +10670,7 @@
         <v>17</v>
       </c>
       <c r="H208" s="11" t="s">
-        <v>18</v>
+        <v>43</v>
       </c>
       <c r="I208" s="11"/>
       <c r="J208" s="12"/>
@@ -10760,10 +10695,10 @@
         <v>0.5</v>
       </c>
       <c r="G209" s="12" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="H209" s="11" t="s">
-        <v>18</v>
+        <v>43</v>
       </c>
       <c r="I209" s="11"/>
       <c r="J209" s="12"/>
@@ -10791,7 +10726,7 @@
         <v>17</v>
       </c>
       <c r="H210" s="11" t="s">
-        <v>18</v>
+        <v>43</v>
       </c>
       <c r="I210" s="11"/>
       <c r="J210" s="12"/>
@@ -10819,7 +10754,7 @@
         <v>17</v>
       </c>
       <c r="H211" s="11" t="s">
-        <v>18</v>
+        <v>43</v>
       </c>
       <c r="I211" s="11"/>
       <c r="J211" s="12"/>
@@ -10847,7 +10782,7 @@
         <v>42</v>
       </c>
       <c r="H212" s="11" t="s">
-        <v>18</v>
+        <v>43</v>
       </c>
       <c r="I212" s="11"/>
       <c r="J212" s="12"/>
@@ -10863,10 +10798,10 @@
         <v>413</v>
       </c>
       <c r="D213" s="17" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E213" s="11" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F213" s="11">
         <v>0.25</v>
@@ -10875,7 +10810,7 @@
         <v>42</v>
       </c>
       <c r="H213" s="11" t="s">
-        <v>18</v>
+        <v>43</v>
       </c>
       <c r="I213" s="11"/>
       <c r="J213" s="12"/>
@@ -10891,7 +10826,7 @@
         <v>435</v>
       </c>
       <c r="D214" s="17" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="E214" s="11" t="s">
         <v>16</v>
@@ -10900,10 +10835,10 @@
         <v>0.5</v>
       </c>
       <c r="G214" s="12" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="H214" s="11" t="s">
-        <v>18</v>
+        <v>43</v>
       </c>
       <c r="I214" s="11"/>
       <c r="J214" s="12"/>
@@ -10931,7 +10866,7 @@
         <v>17</v>
       </c>
       <c r="H215" s="11" t="s">
-        <v>18</v>
+        <v>43</v>
       </c>
       <c r="I215" s="11"/>
       <c r="J215" s="12"/>
@@ -10959,7 +10894,7 @@
         <v>42</v>
       </c>
       <c r="H216" s="11" t="s">
-        <v>18</v>
+        <v>43</v>
       </c>
       <c r="I216" s="11"/>
       <c r="J216" s="12"/>
@@ -10984,10 +10919,10 @@
         <v>0.25</v>
       </c>
       <c r="G217" s="12" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="H217" s="11" t="s">
-        <v>18</v>
+        <v>43</v>
       </c>
       <c r="I217" s="11"/>
       <c r="J217" s="12"/>
@@ -11012,10 +10947,10 @@
         <v>0.75</v>
       </c>
       <c r="G218" s="12" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="H218" s="11" t="s">
-        <v>18</v>
+        <v>43</v>
       </c>
       <c r="I218" s="11"/>
       <c r="J218" s="12"/>
@@ -11040,10 +10975,10 @@
         <v>0.25</v>
       </c>
       <c r="G219" s="12" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="H219" s="11" t="s">
-        <v>18</v>
+        <v>43</v>
       </c>
       <c r="I219" s="11"/>
       <c r="J219" s="12"/>
@@ -11071,7 +11006,7 @@
         <v>42</v>
       </c>
       <c r="H220" s="11" t="s">
-        <v>18</v>
+        <v>43</v>
       </c>
       <c r="I220" s="11"/>
       <c r="J220" s="12"/>
@@ -11087,10 +11022,10 @@
         <v>435</v>
       </c>
       <c r="D221" s="17" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E221" s="11" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F221" s="11">
         <v>0.25</v>
@@ -11099,7 +11034,7 @@
         <v>42</v>
       </c>
       <c r="H221" s="11" t="s">
-        <v>18</v>
+        <v>43</v>
       </c>
       <c r="I221" s="11"/>
       <c r="J221" s="12"/>
@@ -11127,7 +11062,7 @@
         <v>17</v>
       </c>
       <c r="H222" s="11" t="s">
-        <v>18</v>
+        <v>43</v>
       </c>
       <c r="I222" s="11"/>
       <c r="J222" s="12"/>
@@ -11155,7 +11090,7 @@
         <v>42</v>
       </c>
       <c r="H223" s="11" t="s">
-        <v>18</v>
+        <v>43</v>
       </c>
       <c r="I223" s="11"/>
       <c r="J223" s="12"/>
@@ -11180,10 +11115,10 @@
         <v>0.25</v>
       </c>
       <c r="G224" s="12" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="H224" s="11" t="s">
-        <v>18</v>
+        <v>43</v>
       </c>
       <c r="I224" s="11"/>
       <c r="J224" s="12"/>
@@ -11211,7 +11146,7 @@
         <v>17</v>
       </c>
       <c r="H225" s="11" t="s">
-        <v>18</v>
+        <v>43</v>
       </c>
       <c r="I225" s="11"/>
       <c r="J225" s="12"/>
@@ -11239,7 +11174,7 @@
         <v>42</v>
       </c>
       <c r="H226" s="11" t="s">
-        <v>18</v>
+        <v>43</v>
       </c>
       <c r="I226" s="11"/>
       <c r="J226" s="12"/>
@@ -11264,10 +11199,10 @@
         <v>0.25</v>
       </c>
       <c r="G227" s="12" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="H227" s="11" t="s">
-        <v>18</v>
+        <v>43</v>
       </c>
       <c r="I227" s="11"/>
       <c r="J227" s="12"/>
@@ -11295,7 +11230,7 @@
         <v>17</v>
       </c>
       <c r="H228" s="11" t="s">
-        <v>18</v>
+        <v>43</v>
       </c>
       <c r="I228" s="11"/>
       <c r="J228" s="12"/>
@@ -11320,10 +11255,10 @@
         <v>0.25</v>
       </c>
       <c r="G229" s="12" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="H229" s="11" t="s">
-        <v>18</v>
+        <v>43</v>
       </c>
       <c r="I229" s="11"/>
       <c r="J229" s="12"/>
@@ -11351,7 +11286,7 @@
         <v>17</v>
       </c>
       <c r="H230" s="11" t="s">
-        <v>18</v>
+        <v>43</v>
       </c>
       <c r="I230" s="11"/>
       <c r="J230" s="12"/>
@@ -11379,7 +11314,7 @@
         <v>17</v>
       </c>
       <c r="H231" s="11" t="s">
-        <v>18</v>
+        <v>43</v>
       </c>
       <c r="I231" s="11"/>
       <c r="J231" s="12"/>
@@ -11407,7 +11342,7 @@
         <v>42</v>
       </c>
       <c r="H232" s="11" t="s">
-        <v>18</v>
+        <v>43</v>
       </c>
       <c r="I232" s="11"/>
       <c r="J232" s="12"/>
@@ -11423,10 +11358,10 @@
         <v>448</v>
       </c>
       <c r="D233" s="17" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E233" s="11" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F233" s="11">
         <v>0.25</v>
@@ -11435,7 +11370,7 @@
         <v>42</v>
       </c>
       <c r="H233" s="11" t="s">
-        <v>18</v>
+        <v>43</v>
       </c>
       <c r="I233" s="11"/>
       <c r="J233" s="12"/>
@@ -11463,7 +11398,7 @@
         <v>17</v>
       </c>
       <c r="H234" s="11" t="s">
-        <v>18</v>
+        <v>43</v>
       </c>
       <c r="I234" s="11"/>
       <c r="J234" s="12"/>
@@ -11491,7 +11426,7 @@
         <v>42</v>
       </c>
       <c r="H235" s="11" t="s">
-        <v>18</v>
+        <v>43</v>
       </c>
       <c r="I235" s="11"/>
       <c r="J235" s="12"/>
@@ -11516,10 +11451,10 @@
         <v>0.5</v>
       </c>
       <c r="G236" s="12" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="H236" s="11" t="s">
-        <v>18</v>
+        <v>43</v>
       </c>
       <c r="I236" s="11"/>
       <c r="J236" s="12"/>
@@ -11547,7 +11482,7 @@
         <v>17</v>
       </c>
       <c r="H237" s="11" t="s">
-        <v>18</v>
+        <v>43</v>
       </c>
       <c r="I237" s="11"/>
       <c r="J237" s="12"/>
@@ -11575,7 +11510,7 @@
         <v>42</v>
       </c>
       <c r="H238" s="11" t="s">
-        <v>18</v>
+        <v>43</v>
       </c>
       <c r="I238" s="11"/>
       <c r="J238" s="12"/>
@@ -11600,10 +11535,10 @@
         <v>0.25</v>
       </c>
       <c r="G239" s="12" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="H239" s="11" t="s">
-        <v>18</v>
+        <v>43</v>
       </c>
       <c r="I239" s="11"/>
       <c r="J239" s="12"/>
@@ -11628,10 +11563,10 @@
         <v>0.5</v>
       </c>
       <c r="G240" s="12" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="H240" s="11" t="s">
-        <v>18</v>
+        <v>43</v>
       </c>
       <c r="I240" s="11"/>
       <c r="J240" s="12"/>
@@ -11659,7 +11594,7 @@
         <v>17</v>
       </c>
       <c r="H241" s="11" t="s">
-        <v>18</v>
+        <v>43</v>
       </c>
       <c r="I241" s="11"/>
       <c r="J241" s="12"/>
@@ -11684,10 +11619,10 @@
         <v>0.5</v>
       </c>
       <c r="G242" s="12" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="H242" s="11" t="s">
-        <v>18</v>
+        <v>43</v>
       </c>
       <c r="I242" s="11"/>
       <c r="J242" s="12"/>
@@ -11712,10 +11647,10 @@
         <v>0.5</v>
       </c>
       <c r="G243" s="12" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="H243" s="11" t="s">
-        <v>18</v>
+        <v>43</v>
       </c>
       <c r="I243" s="11"/>
       <c r="J243" s="12"/>
@@ -11743,7 +11678,7 @@
         <v>42</v>
       </c>
       <c r="H244" s="11" t="s">
-        <v>18</v>
+        <v>43</v>
       </c>
       <c r="I244" s="11"/>
       <c r="J244" s="12"/>
@@ -11759,10 +11694,10 @@
         <v>470</v>
       </c>
       <c r="D245" s="17" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E245" s="11" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F245" s="11">
         <v>0.25</v>
@@ -11771,7 +11706,7 @@
         <v>42</v>
       </c>
       <c r="H245" s="11" t="s">
-        <v>18</v>
+        <v>43</v>
       </c>
       <c r="I245" s="11"/>
       <c r="J245" s="12"/>
@@ -11799,7 +11734,7 @@
         <v>17</v>
       </c>
       <c r="H246" s="11" t="s">
-        <v>18</v>
+        <v>43</v>
       </c>
       <c r="I246" s="11"/>
       <c r="J246" s="12"/>
@@ -11827,7 +11762,7 @@
         <v>42</v>
       </c>
       <c r="H247" s="11" t="s">
-        <v>18</v>
+        <v>43</v>
       </c>
       <c r="I247" s="11"/>
       <c r="J247" s="12"/>
@@ -11852,10 +11787,10 @@
         <v>0.5</v>
       </c>
       <c r="G248" s="12" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="H248" s="11" t="s">
-        <v>18</v>
+        <v>43</v>
       </c>
       <c r="I248" s="11"/>
       <c r="J248" s="12"/>
@@ -11883,7 +11818,7 @@
         <v>17</v>
       </c>
       <c r="H249" s="11" t="s">
-        <v>18</v>
+        <v>43</v>
       </c>
       <c r="I249" s="11"/>
       <c r="J249" s="12"/>
@@ -11911,7 +11846,7 @@
         <v>42</v>
       </c>
       <c r="H250" s="11" t="s">
-        <v>18</v>
+        <v>43</v>
       </c>
       <c r="I250" s="11"/>
       <c r="J250" s="12"/>
@@ -11936,10 +11871,10 @@
         <v>0.25</v>
       </c>
       <c r="G251" s="12" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="H251" s="11" t="s">
-        <v>18</v>
+        <v>43</v>
       </c>
       <c r="I251" s="11"/>
       <c r="J251" s="12"/>
@@ -11967,7 +11902,7 @@
         <v>17</v>
       </c>
       <c r="H252" s="11" t="s">
-        <v>18</v>
+        <v>43</v>
       </c>
       <c r="I252" s="11"/>
       <c r="J252" s="12"/>
@@ -11992,10 +11927,10 @@
         <v>0.5</v>
       </c>
       <c r="G253" s="12" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="H253" s="11" t="s">
-        <v>18</v>
+        <v>43</v>
       </c>
       <c r="I253" s="11"/>
       <c r="J253" s="12"/>
@@ -12023,7 +11958,7 @@
         <v>17</v>
       </c>
       <c r="H254" s="11" t="s">
-        <v>18</v>
+        <v>43</v>
       </c>
       <c r="I254" s="11"/>
       <c r="J254" s="12"/>
@@ -12051,7 +11986,7 @@
         <v>17</v>
       </c>
       <c r="H255" s="11" t="s">
-        <v>18</v>
+        <v>43</v>
       </c>
       <c r="I255" s="11"/>
       <c r="J255" s="12"/>
@@ -12079,7 +12014,7 @@
         <v>42</v>
       </c>
       <c r="H256" s="11" t="s">
-        <v>18</v>
+        <v>43</v>
       </c>
       <c r="I256" s="11"/>
       <c r="J256" s="12"/>
@@ -12095,10 +12030,10 @@
         <v>492</v>
       </c>
       <c r="D257" s="17" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E257" s="11" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F257" s="11">
         <v>0.25</v>
@@ -12107,7 +12042,7 @@
         <v>42</v>
       </c>
       <c r="H257" s="11" t="s">
-        <v>18</v>
+        <v>43</v>
       </c>
       <c r="I257" s="11"/>
       <c r="J257" s="12"/>
@@ -12345,10 +12280,10 @@
     </row>
     <row r="10" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="11" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B10" s="12" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C10" s="11">
         <v>1</v>
@@ -12365,10 +12300,10 @@
     </row>
     <row r="11" spans="1:6" ht="51.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="13" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B11" s="14" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C11" s="13">
         <v>2</v>
@@ -12385,10 +12320,10 @@
     </row>
     <row r="12" spans="1:6" ht="39" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="11" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B12" s="12" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C12" s="11">
         <v>3</v>
@@ -12405,10 +12340,10 @@
     </row>
     <row r="13" spans="1:6" ht="39" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="13" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="B13" s="14" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C13" s="13">
         <v>1</v>
@@ -12425,10 +12360,10 @@
     </row>
     <row r="14" spans="1:6" ht="39" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="11" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="B14" s="12" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C14" s="11">
         <v>2</v>
@@ -12445,10 +12380,10 @@
     </row>
     <row r="15" spans="1:6" ht="39" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="13" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="B15" s="14" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C15" s="13">
         <v>3</v>
@@ -12465,10 +12400,10 @@
     </row>
     <row r="16" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="11" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="B16" s="12" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="C16" s="11">
         <v>1</v>
@@ -12485,10 +12420,10 @@
     </row>
     <row r="17" spans="1:6" ht="39" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="13" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="B17" s="14" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="C17" s="13">
         <v>2</v>
@@ -12505,10 +12440,10 @@
     </row>
     <row r="18" spans="1:6" ht="51.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="11" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="B18" s="12" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="C18" s="11">
         <v>3</v>
@@ -12525,10 +12460,10 @@
     </row>
     <row r="19" spans="1:6" ht="39" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="13" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="B19" s="14" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="C19" s="13">
         <v>1</v>
@@ -12545,10 +12480,10 @@
     </row>
     <row r="20" spans="1:6" ht="51.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="11" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="B20" s="12" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="C20" s="11">
         <v>2</v>
@@ -12565,10 +12500,10 @@
     </row>
     <row r="21" spans="1:6" ht="51.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="13" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="B21" s="14" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="C21" s="13">
         <v>3</v>
@@ -12585,10 +12520,10 @@
     </row>
     <row r="22" spans="1:6" ht="39" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="11" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="B22" s="12" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="C22" s="11">
         <v>1</v>
@@ -12605,10 +12540,10 @@
     </row>
     <row r="23" spans="1:6" ht="51.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="13" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="B23" s="14" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="C23" s="13">
         <v>2</v>
@@ -12625,10 +12560,10 @@
     </row>
     <row r="24" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="11" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="B24" s="12" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="C24" s="11">
         <v>3</v>
@@ -12645,10 +12580,10 @@
     </row>
     <row r="25" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="13" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="B25" s="14" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="C25" s="13">
         <v>4</v>
@@ -12665,10 +12600,10 @@
     </row>
     <row r="26" spans="1:6" ht="39" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="11" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="B26" s="12" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="C26" s="11">
         <v>1</v>
@@ -12685,10 +12620,10 @@
     </row>
     <row r="27" spans="1:6" ht="51.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="13" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="B27" s="14" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="C27" s="13">
         <v>2</v>
@@ -12705,10 +12640,10 @@
     </row>
     <row r="28" spans="1:6" ht="39" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="11" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="B28" s="12" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="C28" s="11">
         <v>1</v>
@@ -12725,10 +12660,10 @@
     </row>
     <row r="29" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" s="13" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="B29" s="14" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="C29" s="13">
         <v>2</v>
@@ -12745,10 +12680,10 @@
     </row>
     <row r="30" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A30" s="11" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="B30" s="12" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="C30" s="11">
         <v>3</v>
@@ -12765,10 +12700,10 @@
     </row>
     <row r="31" spans="1:6" ht="51.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A31" s="13" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="B31" s="14" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="C31" s="13">
         <v>1</v>
@@ -12785,10 +12720,10 @@
     </row>
     <row r="32" spans="1:6" ht="39" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A32" s="11" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="B32" s="12" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="C32" s="11">
         <v>2</v>
@@ -12805,10 +12740,10 @@
     </row>
     <row r="33" spans="1:6" ht="51.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A33" s="13" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="B33" s="14" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="C33" s="13">
         <v>1</v>
@@ -12825,10 +12760,10 @@
     </row>
     <row r="34" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A34" s="11" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="B34" s="12" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="C34" s="11">
         <v>2</v>
@@ -12845,10 +12780,10 @@
     </row>
     <row r="35" spans="1:6" ht="51.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A35" s="13" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="B35" s="14" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="C35" s="13">
         <v>3</v>
@@ -12865,10 +12800,10 @@
     </row>
     <row r="36" spans="1:6" ht="51.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A36" s="11" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="B36" s="12" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="C36" s="11">
         <v>4</v>
@@ -13583,7 +13518,7 @@
         <v>10</v>
       </c>
       <c r="B14" s="14" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C14" s="14" t="s">
         <v>777</v>

--- a/Fase 2/Sprint Backlogs/SIGMA_Sprint_Backlog_S2.xlsx
+++ b/Fase 2/Sprint Backlogs/SIGMA_Sprint_Backlog_S2.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Capstone\Fase 2\Sprint Backlogs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{276DDB81-CE0E-4C3F-8E2D-5A7718621EF5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B0BFA16B-7389-42CC-8487-355E941CF3B0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12720" tabRatio="500" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="15504" yWindow="3432" windowWidth="7536" windowHeight="9072" tabRatio="500" firstSheet="2" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sprint" sheetId="1" r:id="rId1"/>
@@ -22,7 +22,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Criterios de aceptación'!$A$5:$F$61</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Historias!$A$5:$P$27</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">Tareas!$A$5:$J$141</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">Tareas!$A$5:$J$257</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="3">'Criterios de aceptación'!$5:$5</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="1">Historias!$5:$5</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="2">Tareas!$5:$5</definedName>
@@ -196,75 +196,75 @@
     <t>Modelo: revisar Activo_Medidor — columnas, FK e índices. Confirmar el índice único del código dentro del cliente.</t>
   </si>
   <si>
+    <t>T-2019</t>
+  </si>
+  <si>
+    <t>SP SEL_ACTIVO_MEDIDOR: listado con filtros opcionales (id, texto, habilitado) y ORDER BY estable. Un solo SP sirve a la grilla y a la ficha.</t>
+  </si>
+  <si>
+    <t>T-2020</t>
+  </si>
+  <si>
+    <t>SP INS_ACTIVO_MEDIDOR: alta dentro de transacción. Valida código único por cliente y sella la fecha con FNC_PAIS_HORA.</t>
+  </si>
+  <si>
+    <t>T-2021</t>
+  </si>
+  <si>
+    <t>SP UPD_ACTIVO_MEDIDOR: edición. Los campos que la ficha no muestra se conservan con ISNULL(@X, columna) para no borrarlos al guardar.</t>
+  </si>
+  <si>
+    <t>T-2022</t>
+  </si>
+  <si>
+    <t>SP DEL_ACTIVO_MEDIDOR: baja lógica. Rechaza con mensaje si el registro tiene dependientes en vez de dejar huérfanos.</t>
+  </si>
+  <si>
+    <t>T-2023</t>
+  </si>
+  <si>
+    <t>Datos de prueba en Activo_Medidor para poder ejercitar los criterios de aceptación.</t>
+  </si>
+  <si>
+    <t>T-2028</t>
+  </si>
+  <si>
+    <t>Listado ActivoMedidors.aspx: grilla con búsqueda, filtro de habilitados y botón Nuevo.</t>
+  </si>
+  <si>
+    <t>T-2029</t>
+  </si>
+  <si>
+    <t>Ficha ActivoMedidor.aspx en RadWindow con las clases sigma-modal-*: campos, validadores y Guardar/Cerrar.</t>
+  </si>
+  <si>
+    <t>T-2030</t>
+  </si>
+  <si>
+    <t>T-2031</t>
+  </si>
+  <si>
+    <t>T-2032</t>
+  </si>
+  <si>
+    <t>T-2033</t>
+  </si>
+  <si>
+    <t>T-2034</t>
+  </si>
+  <si>
+    <t>HU-150</t>
+  </si>
+  <si>
+    <t>Sincronizar los datos hacia el dispositivo</t>
+  </si>
+  <si>
+    <t>Modelo: CREAR la tabla Sincronizacion_Lote — todavía no existe. Columnas, PK, FK a sus padres y columna sin_uuid con índice UNIQUE para que la sincronización no duplique.</t>
+  </si>
+  <si>
     <t>Bryan Chávez</t>
   </si>
   <si>
-    <t>T-2019</t>
-  </si>
-  <si>
-    <t>SP SEL_ACTIVO_MEDIDOR: listado con filtros opcionales (id, texto, habilitado) y ORDER BY estable. Un solo SP sirve a la grilla y a la ficha.</t>
-  </si>
-  <si>
-    <t>T-2020</t>
-  </si>
-  <si>
-    <t>SP INS_ACTIVO_MEDIDOR: alta dentro de transacción. Valida código único por cliente y sella la fecha con FNC_PAIS_HORA.</t>
-  </si>
-  <si>
-    <t>T-2021</t>
-  </si>
-  <si>
-    <t>SP UPD_ACTIVO_MEDIDOR: edición. Los campos que la ficha no muestra se conservan con ISNULL(@X, columna) para no borrarlos al guardar.</t>
-  </si>
-  <si>
-    <t>T-2022</t>
-  </si>
-  <si>
-    <t>SP DEL_ACTIVO_MEDIDOR: baja lógica. Rechaza con mensaje si el registro tiene dependientes en vez de dejar huérfanos.</t>
-  </si>
-  <si>
-    <t>T-2023</t>
-  </si>
-  <si>
-    <t>Datos de prueba en Activo_Medidor para poder ejercitar los criterios de aceptación.</t>
-  </si>
-  <si>
-    <t>T-2028</t>
-  </si>
-  <si>
-    <t>Listado ActivoMedidors.aspx: grilla con búsqueda, filtro de habilitados y botón Nuevo.</t>
-  </si>
-  <si>
-    <t>T-2029</t>
-  </si>
-  <si>
-    <t>Ficha ActivoMedidor.aspx en RadWindow con las clases sigma-modal-*: campos, validadores y Guardar/Cerrar.</t>
-  </si>
-  <si>
-    <t>T-2030</t>
-  </si>
-  <si>
-    <t>T-2031</t>
-  </si>
-  <si>
-    <t>T-2032</t>
-  </si>
-  <si>
-    <t>T-2033</t>
-  </si>
-  <si>
-    <t>T-2034</t>
-  </si>
-  <si>
-    <t>HU-150</t>
-  </si>
-  <si>
-    <t>Sincronizar los datos hacia el dispositivo</t>
-  </si>
-  <si>
-    <t>Modelo: CREAR la tabla Sincronizacion_Lote — todavía no existe. Columnas, PK, FK a sus padres y columna sin_uuid con índice UNIQUE para que la sincronización no duplique.</t>
-  </si>
-  <si>
     <t>T-2035</t>
   </si>
   <si>
@@ -1756,6 +1756,9 @@
     <t>HU-033, HU-032</t>
   </si>
   <si>
+    <t>En curso</t>
+  </si>
+  <si>
     <t>registrar el horómetro o contador de un equipo</t>
   </si>
   <si>
@@ -1895,9 +1898,6 @@
   </si>
   <si>
     <t>recuperar el servicio sin depender de una gestión telefonica</t>
-  </si>
-  <si>
-    <t>En curso</t>
   </si>
   <si>
     <t>Construida el 02-09-2026 por Bryan Chávez: INS y SEL_SUSCRIPCION_PAGO del bloque 41, Pago.aspx y Pagos.aspx, comprobante como Archivo categoria 12. La correccion se construyo el 02-09 (bloque 59, UPD_SUSCRIPCION_PAGO). FALTAN los datos de prueba: el script esta listo pero no hay periodos emitidos sobre los que sembrar (T-2212). Y la verificacion de los criterios, que es de Catalina.</t>
@@ -3304,7 +3304,7 @@
         <v>528</v>
       </c>
       <c r="C22" s="21" t="s">
-        <v>54</v>
+        <v>76</v>
       </c>
       <c r="D22" s="19"/>
       <c r="E22" s="19"/>
@@ -3514,10 +3514,10 @@
   </sheetData>
   <mergeCells count="10">
     <mergeCell ref="B11:H13"/>
+    <mergeCell ref="C21:H21"/>
     <mergeCell ref="C20:H20"/>
+    <mergeCell ref="C16:H16"/>
     <mergeCell ref="C19:H19"/>
-    <mergeCell ref="C16:H16"/>
-    <mergeCell ref="C21:H21"/>
     <mergeCell ref="C22:H22"/>
     <mergeCell ref="B43:H44"/>
     <mergeCell ref="C23:H23"/>
@@ -3693,7 +3693,7 @@
         <v>9.25</v>
       </c>
       <c r="N6" s="11" t="s">
-        <v>43</v>
+        <v>574</v>
       </c>
       <c r="O6" s="12"/>
       <c r="P6" s="12"/>
@@ -3712,10 +3712,10 @@
         <v>569</v>
       </c>
       <c r="E7" s="14" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="F7" s="14" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="G7" s="13" t="s">
         <v>31</v>
@@ -3747,25 +3747,25 @@
     </row>
     <row r="8" spans="1:16" ht="55.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="11" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B8" s="11" t="s">
         <v>550</v>
       </c>
       <c r="C8" s="12" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D8" s="12" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="E8" s="12" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="F8" s="12" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="G8" s="11" t="s">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="H8" s="11">
         <v>13</v>
@@ -3803,16 +3803,16 @@
         <v>103</v>
       </c>
       <c r="D9" s="14" t="s">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="E9" s="14" t="s">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="F9" s="14" t="s">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="G9" s="13" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="H9" s="13">
         <v>5</v>
@@ -3850,16 +3850,16 @@
         <v>122</v>
       </c>
       <c r="D10" s="12" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="E10" s="12" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="F10" s="12" t="s">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="G10" s="11" t="s">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="H10" s="11">
         <v>3</v>
@@ -3885,7 +3885,7 @@
       </c>
       <c r="O10" s="12"/>
       <c r="P10" s="12" t="s">
-        <v>586</v>
+        <v>587</v>
       </c>
     </row>
     <row r="11" spans="1:16" ht="55.2" customHeight="1" x14ac:dyDescent="0.3">
@@ -3899,16 +3899,16 @@
         <v>144</v>
       </c>
       <c r="D11" s="14" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="E11" s="14" t="s">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="F11" s="14" t="s">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="G11" s="13" t="s">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="H11" s="13">
         <v>5</v>
@@ -3920,7 +3920,7 @@
         <v>572</v>
       </c>
       <c r="K11" s="14" t="s">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="L11" s="13">
         <v>4</v>
@@ -3949,10 +3949,10 @@
         <v>569</v>
       </c>
       <c r="E12" s="12" t="s">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="F12" s="12" t="s">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="G12" s="11" t="s">
         <v>31</v>
@@ -3967,7 +3967,7 @@
         <v>572</v>
       </c>
       <c r="K12" s="12" t="s">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="L12" s="11">
         <v>2</v>
@@ -3996,10 +3996,10 @@
         <v>569</v>
       </c>
       <c r="E13" s="14" t="s">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="F13" s="14" t="s">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="G13" s="13" t="s">
         <v>31</v>
@@ -4011,7 +4011,7 @@
         <v>80</v>
       </c>
       <c r="J13" s="13" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="K13" s="14" t="s">
         <v>13</v>
@@ -4040,16 +4040,16 @@
         <v>208</v>
       </c>
       <c r="D14" s="12" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="E14" s="12" t="s">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="F14" s="12" t="s">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="G14" s="11" t="s">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="H14" s="11">
         <v>5</v>
@@ -4058,7 +4058,7 @@
         <v>80</v>
       </c>
       <c r="J14" s="11" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="K14" s="12" t="s">
         <v>412</v>
@@ -4075,7 +4075,7 @@
       </c>
       <c r="O14" s="12"/>
       <c r="P14" s="12" t="s">
-        <v>586</v>
+        <v>587</v>
       </c>
     </row>
     <row r="15" spans="1:16" ht="82.8" customHeight="1" x14ac:dyDescent="0.3">
@@ -4089,16 +4089,16 @@
         <v>229</v>
       </c>
       <c r="D15" s="14" t="s">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="E15" s="14" t="s">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="F15" s="14" t="s">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="G15" s="13" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="H15" s="13">
         <v>5</v>
@@ -4107,7 +4107,7 @@
         <v>80</v>
       </c>
       <c r="J15" s="13" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="K15" s="14" t="s">
         <v>279</v>
@@ -4120,13 +4120,13 @@
         <v>7.5</v>
       </c>
       <c r="N15" s="13" t="s">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="O15" s="14" t="s">
-        <v>54</v>
+        <v>76</v>
       </c>
       <c r="P15" s="14" t="s">
-        <v>602</v>
+        <v>603</v>
       </c>
     </row>
     <row r="16" spans="1:16" ht="82.8" customHeight="1" x14ac:dyDescent="0.3">
@@ -4140,16 +4140,16 @@
         <v>260</v>
       </c>
       <c r="D16" s="12" t="s">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="E16" s="12" t="s">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="F16" s="12" t="s">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="G16" s="11" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="H16" s="11">
         <v>3</v>
@@ -4158,7 +4158,7 @@
         <v>75</v>
       </c>
       <c r="J16" s="11" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="K16" s="12" t="s">
         <v>13</v>
@@ -4187,13 +4187,13 @@
         <v>280</v>
       </c>
       <c r="D17" s="14" t="s">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="E17" s="14" t="s">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="F17" s="14" t="s">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="G17" s="13" t="s">
         <v>31</v>
@@ -4205,7 +4205,7 @@
         <v>75</v>
       </c>
       <c r="J17" s="13" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="K17" s="14" t="s">
         <v>331</v>
@@ -4218,13 +4218,13 @@
         <v>5.75</v>
       </c>
       <c r="N17" s="13" t="s">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="O17" s="14" t="s">
-        <v>54</v>
+        <v>76</v>
       </c>
       <c r="P17" s="14" t="s">
-        <v>608</v>
+        <v>609</v>
       </c>
     </row>
     <row r="18" spans="1:16" ht="82.8" customHeight="1" x14ac:dyDescent="0.3">
@@ -4241,10 +4241,10 @@
         <v>569</v>
       </c>
       <c r="E18" s="12" t="s">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="F18" s="12" t="s">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="G18" s="11" t="s">
         <v>31</v>
@@ -4256,7 +4256,7 @@
         <v>70</v>
       </c>
       <c r="J18" s="11" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="K18" s="12" t="s">
         <v>165</v>
@@ -4285,13 +4285,13 @@
         <v>319</v>
       </c>
       <c r="D19" s="14" t="s">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="E19" s="14" t="s">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="F19" s="14" t="s">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="G19" s="13" t="s">
         <v>31</v>
@@ -4303,7 +4303,7 @@
         <v>70</v>
       </c>
       <c r="J19" s="13" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="K19" s="14" t="s">
         <v>207</v>
@@ -4332,13 +4332,13 @@
         <v>332</v>
       </c>
       <c r="D20" s="12" t="s">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="E20" s="12" t="s">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="F20" s="12" t="s">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="G20" s="11" t="s">
         <v>31</v>
@@ -4350,10 +4350,10 @@
         <v>70</v>
       </c>
       <c r="J20" s="11" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="K20" s="12" t="s">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="L20" s="11">
         <v>3</v>
@@ -4363,13 +4363,13 @@
         <v>5.5</v>
       </c>
       <c r="N20" s="11" t="s">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="O20" s="12" t="s">
-        <v>54</v>
+        <v>76</v>
       </c>
       <c r="P20" s="12" t="s">
-        <v>617</v>
+        <v>618</v>
       </c>
     </row>
     <row r="21" spans="1:16" ht="69" customHeight="1" x14ac:dyDescent="0.3">
@@ -4383,13 +4383,13 @@
         <v>364</v>
       </c>
       <c r="D21" s="14" t="s">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="E21" s="14" t="s">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="F21" s="14" t="s">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="G21" s="13" t="s">
         <v>31</v>
@@ -4401,7 +4401,7 @@
         <v>70</v>
       </c>
       <c r="J21" s="13" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="K21" s="14" t="s">
         <v>228</v>
@@ -4414,10 +4414,10 @@
         <v>5.75</v>
       </c>
       <c r="N21" s="13" t="s">
-        <v>621</v>
+        <v>574</v>
       </c>
       <c r="O21" s="14" t="s">
-        <v>54</v>
+        <v>76</v>
       </c>
       <c r="P21" s="14" t="s">
         <v>622</v>
@@ -4452,10 +4452,10 @@
         <v>65</v>
       </c>
       <c r="J22" s="11" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="K22" s="12" t="s">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="L22" s="11">
         <v>2</v>
@@ -4499,7 +4499,7 @@
         <v>65</v>
       </c>
       <c r="J23" s="13" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="K23" s="14" t="s">
         <v>469</v>
@@ -4528,7 +4528,7 @@
         <v>435</v>
       </c>
       <c r="D24" s="12" t="s">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="E24" s="12" t="s">
         <v>627</v>
@@ -4546,7 +4546,7 @@
         <v>65</v>
       </c>
       <c r="J24" s="11" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="K24" s="12" t="s">
         <v>279</v>
@@ -4622,7 +4622,7 @@
         <v>470</v>
       </c>
       <c r="D26" s="12" t="s">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="E26" s="12" t="s">
         <v>632</v>
@@ -4643,7 +4643,7 @@
         <v>631</v>
       </c>
       <c r="K26" s="12" t="s">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="L26" s="11">
         <v>2</v>
@@ -4775,7 +4775,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <sheetPr>
+  <sheetPr filterMode="1">
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:J315"/>
@@ -4853,7 +4853,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="6" spans="1:10" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:10" ht="27.6" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="11" t="s">
         <v>12</v>
       </c>
@@ -4881,7 +4881,7 @@
       <c r="I6" s="11"/>
       <c r="J6" s="12"/>
     </row>
-    <row r="7" spans="1:10" ht="41.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:10" ht="41.4" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="11" t="s">
         <v>19</v>
       </c>
@@ -4909,7 +4909,7 @@
       <c r="I7" s="11"/>
       <c r="J7" s="12"/>
     </row>
-    <row r="8" spans="1:10" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:10" ht="27.6" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="11" t="s">
         <v>21</v>
       </c>
@@ -4937,7 +4937,7 @@
       <c r="I8" s="11"/>
       <c r="J8" s="12"/>
     </row>
-    <row r="9" spans="1:10" ht="41.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:10" ht="41.4" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="11" t="s">
         <v>23</v>
       </c>
@@ -4965,7 +4965,7 @@
       <c r="I9" s="11"/>
       <c r="J9" s="12"/>
     </row>
-    <row r="10" spans="1:10" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:10" ht="27.6" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="11" t="s">
         <v>25</v>
       </c>
@@ -4993,7 +4993,7 @@
       <c r="I10" s="11"/>
       <c r="J10" s="12"/>
     </row>
-    <row r="11" spans="1:10" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:10" ht="27.6" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="11" t="s">
         <v>27</v>
       </c>
@@ -5021,7 +5021,7 @@
       <c r="I11" s="11"/>
       <c r="J11" s="12"/>
     </row>
-    <row r="12" spans="1:10" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:10" ht="27.6" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="11" t="s">
         <v>29</v>
       </c>
@@ -5049,7 +5049,7 @@
       <c r="I12" s="11"/>
       <c r="J12" s="12"/>
     </row>
-    <row r="13" spans="1:10" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:10" ht="27.6" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="11" t="s">
         <v>32</v>
       </c>
@@ -5077,7 +5077,7 @@
       <c r="I13" s="11"/>
       <c r="J13" s="12"/>
     </row>
-    <row r="14" spans="1:10" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:10" ht="27.6" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="11" t="s">
         <v>34</v>
       </c>
@@ -5105,7 +5105,7 @@
       <c r="I14" s="11"/>
       <c r="J14" s="12"/>
     </row>
-    <row r="15" spans="1:10" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:10" ht="27.6" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="11" t="s">
         <v>36</v>
       </c>
@@ -5133,7 +5133,7 @@
       <c r="I15" s="11"/>
       <c r="J15" s="12"/>
     </row>
-    <row r="16" spans="1:10" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:10" ht="27.6" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="11" t="s">
         <v>39</v>
       </c>
@@ -5161,7 +5161,7 @@
       <c r="I16" s="11"/>
       <c r="J16" s="12"/>
     </row>
-    <row r="17" spans="1:10" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:10" ht="27.6" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="11" t="s">
         <v>44</v>
       </c>
@@ -5189,7 +5189,7 @@
       <c r="I17" s="11"/>
       <c r="J17" s="12"/>
     </row>
-    <row r="18" spans="1:10" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:10" ht="27.6" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="11" t="s">
         <v>47</v>
       </c>
@@ -5237,17 +5237,17 @@
         <v>0.5</v>
       </c>
       <c r="G19" s="12" t="s">
-        <v>54</v>
+        <v>17</v>
       </c>
       <c r="H19" s="11" t="s">
-        <v>43</v>
+        <v>18</v>
       </c>
       <c r="I19" s="11"/>
       <c r="J19" s="12"/>
     </row>
     <row r="20" spans="1:10" ht="41.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="11" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B20" s="11" t="s">
         <v>51</v>
@@ -5256,7 +5256,7 @@
         <v>52</v>
       </c>
       <c r="D20" s="17" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="E20" s="11" t="s">
         <v>16</v>
@@ -5268,14 +5268,14 @@
         <v>17</v>
       </c>
       <c r="H20" s="11" t="s">
-        <v>43</v>
+        <v>18</v>
       </c>
       <c r="I20" s="11"/>
       <c r="J20" s="12"/>
     </row>
     <row r="21" spans="1:10" ht="41.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="11" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B21" s="11" t="s">
         <v>51</v>
@@ -5284,7 +5284,7 @@
         <v>52</v>
       </c>
       <c r="D21" s="17" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="E21" s="11" t="s">
         <v>16</v>
@@ -5293,17 +5293,17 @@
         <v>0.25</v>
       </c>
       <c r="G21" s="12" t="s">
-        <v>42</v>
+        <v>17</v>
       </c>
       <c r="H21" s="11" t="s">
-        <v>43</v>
+        <v>18</v>
       </c>
       <c r="I21" s="11"/>
       <c r="J21" s="12"/>
     </row>
     <row r="22" spans="1:10" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="11" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B22" s="11" t="s">
         <v>51</v>
@@ -5312,7 +5312,7 @@
         <v>52</v>
       </c>
       <c r="D22" s="17" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E22" s="11" t="s">
         <v>16</v>
@@ -5321,17 +5321,17 @@
         <v>0.25</v>
       </c>
       <c r="G22" s="12" t="s">
-        <v>54</v>
+        <v>17</v>
       </c>
       <c r="H22" s="11" t="s">
-        <v>43</v>
+        <v>18</v>
       </c>
       <c r="I22" s="11"/>
       <c r="J22" s="12"/>
     </row>
     <row r="23" spans="1:10" ht="41.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="11" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B23" s="11" t="s">
         <v>51</v>
@@ -5340,7 +5340,7 @@
         <v>52</v>
       </c>
       <c r="D23" s="17" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="E23" s="11" t="s">
         <v>16</v>
@@ -5352,14 +5352,14 @@
         <v>17</v>
       </c>
       <c r="H23" s="11" t="s">
-        <v>43</v>
+        <v>18</v>
       </c>
       <c r="I23" s="11"/>
       <c r="J23" s="12"/>
     </row>
     <row r="24" spans="1:10" ht="41.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="11" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B24" s="11" t="s">
         <v>51</v>
@@ -5368,7 +5368,7 @@
         <v>52</v>
       </c>
       <c r="D24" s="17" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="E24" s="11" t="s">
         <v>16</v>
@@ -5377,17 +5377,17 @@
         <v>0.25</v>
       </c>
       <c r="G24" s="12" t="s">
-        <v>42</v>
+        <v>17</v>
       </c>
       <c r="H24" s="11" t="s">
-        <v>43</v>
+        <v>18</v>
       </c>
       <c r="I24" s="11"/>
       <c r="J24" s="12"/>
     </row>
     <row r="25" spans="1:10" ht="41.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="11" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B25" s="11" t="s">
         <v>51</v>
@@ -5396,7 +5396,7 @@
         <v>52</v>
       </c>
       <c r="D25" s="17" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="E25" s="11" t="s">
         <v>31</v>
@@ -5408,14 +5408,14 @@
         <v>17</v>
       </c>
       <c r="H25" s="11" t="s">
-        <v>43</v>
+        <v>18</v>
       </c>
       <c r="I25" s="11"/>
       <c r="J25" s="12"/>
     </row>
     <row r="26" spans="1:10" ht="41.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="11" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B26" s="11" t="s">
         <v>51</v>
@@ -5424,7 +5424,7 @@
         <v>52</v>
       </c>
       <c r="D26" s="17" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="E26" s="11" t="s">
         <v>31</v>
@@ -5433,17 +5433,17 @@
         <v>0.25</v>
       </c>
       <c r="G26" s="12" t="s">
-        <v>54</v>
+        <v>17</v>
       </c>
       <c r="H26" s="11" t="s">
-        <v>43</v>
+        <v>18</v>
       </c>
       <c r="I26" s="11"/>
       <c r="J26" s="12"/>
     </row>
     <row r="27" spans="1:10" ht="41.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="11" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B27" s="11" t="s">
         <v>51</v>
@@ -5464,14 +5464,14 @@
         <v>17</v>
       </c>
       <c r="H27" s="11" t="s">
-        <v>43</v>
+        <v>18</v>
       </c>
       <c r="I27" s="11"/>
       <c r="J27" s="12"/>
     </row>
     <row r="28" spans="1:10" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="11" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B28" s="11" t="s">
         <v>51</v>
@@ -5492,14 +5492,14 @@
         <v>17</v>
       </c>
       <c r="H28" s="11" t="s">
-        <v>43</v>
+        <v>18</v>
       </c>
       <c r="I28" s="11"/>
       <c r="J28" s="12"/>
     </row>
-    <row r="29" spans="1:10" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:10" ht="27.6" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" s="11" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B29" s="11" t="s">
         <v>51</v>
@@ -5525,9 +5525,9 @@
       <c r="I29" s="11"/>
       <c r="J29" s="12"/>
     </row>
-    <row r="30" spans="1:10" ht="41.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:10" ht="41.4" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A30" s="11" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B30" s="11" t="s">
         <v>51</v>
@@ -5553,18 +5553,18 @@
       <c r="I30" s="11"/>
       <c r="J30" s="12"/>
     </row>
-    <row r="31" spans="1:10" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:10" ht="27.6" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A31" s="11" t="s">
+        <v>72</v>
+      </c>
+      <c r="B31" s="11" t="s">
         <v>73</v>
       </c>
-      <c r="B31" s="11" t="s">
+      <c r="C31" s="12" t="s">
         <v>74</v>
       </c>
-      <c r="C31" s="12" t="s">
+      <c r="D31" s="17" t="s">
         <v>75</v>
-      </c>
-      <c r="D31" s="17" t="s">
-        <v>76</v>
       </c>
       <c r="E31" s="11" t="s">
         <v>16</v>
@@ -5573,7 +5573,7 @@
         <v>1.5</v>
       </c>
       <c r="G31" s="12" t="s">
-        <v>54</v>
+        <v>76</v>
       </c>
       <c r="H31" s="11" t="s">
         <v>43</v>
@@ -5581,15 +5581,15 @@
       <c r="I31" s="11"/>
       <c r="J31" s="12"/>
     </row>
-    <row r="32" spans="1:10" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:10" ht="27.6" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A32" s="11" t="s">
         <v>77</v>
       </c>
       <c r="B32" s="11" t="s">
+        <v>73</v>
+      </c>
+      <c r="C32" s="12" t="s">
         <v>74</v>
-      </c>
-      <c r="C32" s="12" t="s">
-        <v>75</v>
       </c>
       <c r="D32" s="17" t="s">
         <v>78</v>
@@ -5609,15 +5609,15 @@
       <c r="I32" s="11"/>
       <c r="J32" s="12"/>
     </row>
-    <row r="33" spans="1:10" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:10" ht="27.6" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A33" s="11" t="s">
         <v>79</v>
       </c>
       <c r="B33" s="11" t="s">
+        <v>73</v>
+      </c>
+      <c r="C33" s="12" t="s">
         <v>74</v>
-      </c>
-      <c r="C33" s="12" t="s">
-        <v>75</v>
       </c>
       <c r="D33" s="17" t="s">
         <v>80</v>
@@ -5637,15 +5637,15 @@
       <c r="I33" s="11"/>
       <c r="J33" s="12"/>
     </row>
-    <row r="34" spans="1:10" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:10" ht="27.6" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A34" s="11" t="s">
         <v>81</v>
       </c>
       <c r="B34" s="11" t="s">
+        <v>73</v>
+      </c>
+      <c r="C34" s="12" t="s">
         <v>74</v>
-      </c>
-      <c r="C34" s="12" t="s">
-        <v>75</v>
       </c>
       <c r="D34" s="17" t="s">
         <v>82</v>
@@ -5657,7 +5657,7 @@
         <v>1.25</v>
       </c>
       <c r="G34" s="12" t="s">
-        <v>54</v>
+        <v>76</v>
       </c>
       <c r="H34" s="11" t="s">
         <v>43</v>
@@ -5665,15 +5665,15 @@
       <c r="I34" s="11"/>
       <c r="J34" s="12"/>
     </row>
-    <row r="35" spans="1:10" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:10" ht="27.6" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A35" s="11" t="s">
         <v>83</v>
       </c>
       <c r="B35" s="11" t="s">
+        <v>73</v>
+      </c>
+      <c r="C35" s="12" t="s">
         <v>74</v>
-      </c>
-      <c r="C35" s="12" t="s">
-        <v>75</v>
       </c>
       <c r="D35" s="17" t="s">
         <v>84</v>
@@ -5685,7 +5685,7 @@
         <v>1.5</v>
       </c>
       <c r="G35" s="12" t="s">
-        <v>54</v>
+        <v>76</v>
       </c>
       <c r="H35" s="11" t="s">
         <v>43</v>
@@ -5693,15 +5693,15 @@
       <c r="I35" s="11"/>
       <c r="J35" s="12"/>
     </row>
-    <row r="36" spans="1:10" ht="55.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:10" ht="55.2" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A36" s="11" t="s">
         <v>86</v>
       </c>
       <c r="B36" s="11" t="s">
+        <v>73</v>
+      </c>
+      <c r="C36" s="12" t="s">
         <v>74</v>
-      </c>
-      <c r="C36" s="12" t="s">
-        <v>75</v>
       </c>
       <c r="D36" s="17" t="s">
         <v>87</v>
@@ -5721,15 +5721,15 @@
       <c r="I36" s="11"/>
       <c r="J36" s="12"/>
     </row>
-    <row r="37" spans="1:10" ht="41.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:10" ht="41.4" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A37" s="11" t="s">
         <v>88</v>
       </c>
       <c r="B37" s="11" t="s">
+        <v>73</v>
+      </c>
+      <c r="C37" s="12" t="s">
         <v>74</v>
-      </c>
-      <c r="C37" s="12" t="s">
-        <v>75</v>
       </c>
       <c r="D37" s="17" t="s">
         <v>89</v>
@@ -5741,7 +5741,7 @@
         <v>1.25</v>
       </c>
       <c r="G37" s="12" t="s">
-        <v>54</v>
+        <v>76</v>
       </c>
       <c r="H37" s="11" t="s">
         <v>43</v>
@@ -5749,15 +5749,15 @@
       <c r="I37" s="11"/>
       <c r="J37" s="12"/>
     </row>
-    <row r="38" spans="1:10" ht="41.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:10" ht="41.4" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A38" s="11" t="s">
         <v>90</v>
       </c>
       <c r="B38" s="11" t="s">
+        <v>73</v>
+      </c>
+      <c r="C38" s="12" t="s">
         <v>74</v>
-      </c>
-      <c r="C38" s="12" t="s">
-        <v>75</v>
       </c>
       <c r="D38" s="17" t="s">
         <v>91</v>
@@ -5769,7 +5769,7 @@
         <v>0.75</v>
       </c>
       <c r="G38" s="12" t="s">
-        <v>54</v>
+        <v>76</v>
       </c>
       <c r="H38" s="11" t="s">
         <v>43</v>
@@ -5777,15 +5777,15 @@
       <c r="I38" s="11"/>
       <c r="J38" s="12"/>
     </row>
-    <row r="39" spans="1:10" ht="41.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:10" ht="41.4" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A39" s="11" t="s">
         <v>93</v>
       </c>
       <c r="B39" s="11" t="s">
+        <v>73</v>
+      </c>
+      <c r="C39" s="12" t="s">
         <v>74</v>
-      </c>
-      <c r="C39" s="12" t="s">
-        <v>75</v>
       </c>
       <c r="D39" s="17" t="s">
         <v>94</v>
@@ -5805,15 +5805,15 @@
       <c r="I39" s="11"/>
       <c r="J39" s="12"/>
     </row>
-    <row r="40" spans="1:10" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:10" ht="27.6" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A40" s="11" t="s">
         <v>95</v>
       </c>
       <c r="B40" s="11" t="s">
+        <v>73</v>
+      </c>
+      <c r="C40" s="12" t="s">
         <v>74</v>
-      </c>
-      <c r="C40" s="12" t="s">
-        <v>75</v>
       </c>
       <c r="D40" s="17" t="s">
         <v>96</v>
@@ -5825,7 +5825,7 @@
         <v>0.75</v>
       </c>
       <c r="G40" s="12" t="s">
-        <v>54</v>
+        <v>76</v>
       </c>
       <c r="H40" s="11" t="s">
         <v>43</v>
@@ -5833,15 +5833,15 @@
       <c r="I40" s="11"/>
       <c r="J40" s="12"/>
     </row>
-    <row r="41" spans="1:10" ht="41.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:10" ht="41.4" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A41" s="11" t="s">
         <v>97</v>
       </c>
       <c r="B41" s="11" t="s">
+        <v>73</v>
+      </c>
+      <c r="C41" s="12" t="s">
         <v>74</v>
-      </c>
-      <c r="C41" s="12" t="s">
-        <v>75</v>
       </c>
       <c r="D41" s="17" t="s">
         <v>37</v>
@@ -5853,7 +5853,7 @@
         <v>1.5</v>
       </c>
       <c r="G41" s="12" t="s">
-        <v>54</v>
+        <v>76</v>
       </c>
       <c r="H41" s="11" t="s">
         <v>43</v>
@@ -5861,15 +5861,15 @@
       <c r="I41" s="11"/>
       <c r="J41" s="12"/>
     </row>
-    <row r="42" spans="1:10" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:10" ht="27.6" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A42" s="11" t="s">
         <v>98</v>
       </c>
       <c r="B42" s="11" t="s">
+        <v>73</v>
+      </c>
+      <c r="C42" s="12" t="s">
         <v>74</v>
-      </c>
-      <c r="C42" s="12" t="s">
-        <v>75</v>
       </c>
       <c r="D42" s="17" t="s">
         <v>40</v>
@@ -5889,15 +5889,15 @@
       <c r="I42" s="11"/>
       <c r="J42" s="12"/>
     </row>
-    <row r="43" spans="1:10" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:10" ht="27.6" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A43" s="11" t="s">
         <v>99</v>
       </c>
       <c r="B43" s="11" t="s">
+        <v>73</v>
+      </c>
+      <c r="C43" s="12" t="s">
         <v>74</v>
-      </c>
-      <c r="C43" s="12" t="s">
-        <v>75</v>
       </c>
       <c r="D43" s="17" t="s">
         <v>45</v>
@@ -5917,15 +5917,15 @@
       <c r="I43" s="11"/>
       <c r="J43" s="12"/>
     </row>
-    <row r="44" spans="1:10" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:10" ht="27.6" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A44" s="11" t="s">
         <v>100</v>
       </c>
       <c r="B44" s="11" t="s">
+        <v>73</v>
+      </c>
+      <c r="C44" s="12" t="s">
         <v>74</v>
-      </c>
-      <c r="C44" s="12" t="s">
-        <v>75</v>
       </c>
       <c r="D44" s="17" t="s">
         <v>48</v>
@@ -6021,7 +6021,7 @@
         <v>0.5</v>
       </c>
       <c r="G47" s="12" t="s">
-        <v>54</v>
+        <v>76</v>
       </c>
       <c r="H47" s="11" t="s">
         <v>43</v>
@@ -6105,7 +6105,7 @@
         <v>0.75</v>
       </c>
       <c r="G50" s="12" t="s">
-        <v>54</v>
+        <v>76</v>
       </c>
       <c r="H50" s="11" t="s">
         <v>43</v>
@@ -6141,7 +6141,7 @@
       <c r="I51" s="11"/>
       <c r="J51" s="12"/>
     </row>
-    <row r="52" spans="1:10" ht="41.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:10" ht="41.4" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A52" s="11" t="s">
         <v>115</v>
       </c>
@@ -6197,7 +6197,7 @@
       <c r="I53" s="11"/>
       <c r="J53" s="12"/>
     </row>
-    <row r="54" spans="1:10" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:10" ht="27.6" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A54" s="11" t="s">
         <v>118</v>
       </c>
@@ -6225,7 +6225,7 @@
       <c r="I54" s="11"/>
       <c r="J54" s="12"/>
     </row>
-    <row r="55" spans="1:10" ht="41.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:10" ht="41.4" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A55" s="11" t="s">
         <v>119</v>
       </c>
@@ -6253,7 +6253,7 @@
       <c r="I55" s="11"/>
       <c r="J55" s="12"/>
     </row>
-    <row r="56" spans="1:10" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:10" ht="27.6" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A56" s="11" t="s">
         <v>120</v>
       </c>
@@ -6281,7 +6281,7 @@
       <c r="I56" s="11"/>
       <c r="J56" s="12"/>
     </row>
-    <row r="57" spans="1:10" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:10" ht="27.6" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A57" s="11" t="s">
         <v>124</v>
       </c>
@@ -6301,7 +6301,7 @@
         <v>0.5</v>
       </c>
       <c r="G57" s="12" t="s">
-        <v>54</v>
+        <v>76</v>
       </c>
       <c r="H57" s="11" t="s">
         <v>43</v>
@@ -6309,7 +6309,7 @@
       <c r="I57" s="11"/>
       <c r="J57" s="12"/>
     </row>
-    <row r="58" spans="1:10" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:10" ht="27.6" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A58" s="11" t="s">
         <v>126</v>
       </c>
@@ -6337,7 +6337,7 @@
       <c r="I58" s="11"/>
       <c r="J58" s="12"/>
     </row>
-    <row r="59" spans="1:10" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:10" ht="27.6" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A59" s="11" t="s">
         <v>128</v>
       </c>
@@ -6365,7 +6365,7 @@
       <c r="I59" s="11"/>
       <c r="J59" s="12"/>
     </row>
-    <row r="60" spans="1:10" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:10" ht="27.6" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A60" s="11" t="s">
         <v>130</v>
       </c>
@@ -6385,7 +6385,7 @@
         <v>0.25</v>
       </c>
       <c r="G60" s="12" t="s">
-        <v>54</v>
+        <v>76</v>
       </c>
       <c r="H60" s="11" t="s">
         <v>43</v>
@@ -6393,7 +6393,7 @@
       <c r="I60" s="11"/>
       <c r="J60" s="12"/>
     </row>
-    <row r="61" spans="1:10" ht="41.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:10" ht="41.4" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A61" s="11" t="s">
         <v>132</v>
       </c>
@@ -6421,7 +6421,7 @@
       <c r="I61" s="11"/>
       <c r="J61" s="12"/>
     </row>
-    <row r="62" spans="1:10" ht="55.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:10" ht="55.2" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A62" s="11" t="s">
         <v>134</v>
       </c>
@@ -6441,7 +6441,7 @@
         <v>0.25</v>
       </c>
       <c r="G62" s="12" t="s">
-        <v>54</v>
+        <v>76</v>
       </c>
       <c r="H62" s="11" t="s">
         <v>43</v>
@@ -6449,7 +6449,7 @@
       <c r="I62" s="11"/>
       <c r="J62" s="12"/>
     </row>
-    <row r="63" spans="1:10" ht="41.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:10" ht="41.4" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A63" s="11" t="s">
         <v>136</v>
       </c>
@@ -6477,7 +6477,7 @@
       <c r="I63" s="11"/>
       <c r="J63" s="12"/>
     </row>
-    <row r="64" spans="1:10" ht="41.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:10" ht="41.4" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A64" s="11" t="s">
         <v>138</v>
       </c>
@@ -6497,7 +6497,7 @@
         <v>0.25</v>
       </c>
       <c r="G64" s="12" t="s">
-        <v>54</v>
+        <v>76</v>
       </c>
       <c r="H64" s="11" t="s">
         <v>43</v>
@@ -6505,7 +6505,7 @@
       <c r="I64" s="11"/>
       <c r="J64" s="12"/>
     </row>
-    <row r="65" spans="1:10" ht="41.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:10" ht="41.4" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A65" s="11" t="s">
         <v>139</v>
       </c>
@@ -6525,7 +6525,7 @@
         <v>0.25</v>
       </c>
       <c r="G65" s="12" t="s">
-        <v>54</v>
+        <v>76</v>
       </c>
       <c r="H65" s="11" t="s">
         <v>43</v>
@@ -6533,7 +6533,7 @@
       <c r="I65" s="11"/>
       <c r="J65" s="12"/>
     </row>
-    <row r="66" spans="1:10" ht="41.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:10" ht="41.4" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A66" s="11" t="s">
         <v>140</v>
       </c>
@@ -6561,7 +6561,7 @@
       <c r="I66" s="11"/>
       <c r="J66" s="12"/>
     </row>
-    <row r="67" spans="1:10" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:10" ht="27.6" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A67" s="11" t="s">
         <v>141</v>
       </c>
@@ -6589,7 +6589,7 @@
       <c r="I67" s="11"/>
       <c r="J67" s="12"/>
     </row>
-    <row r="68" spans="1:10" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:10" ht="27.6" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A68" s="11" t="s">
         <v>142</v>
       </c>
@@ -6617,7 +6617,7 @@
       <c r="I68" s="11"/>
       <c r="J68" s="12"/>
     </row>
-    <row r="69" spans="1:10" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:10" ht="27.6" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A69" s="11" t="s">
         <v>146</v>
       </c>
@@ -6645,7 +6645,7 @@
       <c r="I69" s="11"/>
       <c r="J69" s="12"/>
     </row>
-    <row r="70" spans="1:10" ht="41.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:10" ht="41.4" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A70" s="11" t="s">
         <v>148</v>
       </c>
@@ -6665,7 +6665,7 @@
         <v>0.5</v>
       </c>
       <c r="G70" s="12" t="s">
-        <v>54</v>
+        <v>76</v>
       </c>
       <c r="H70" s="11" t="s">
         <v>43</v>
@@ -6673,7 +6673,7 @@
       <c r="I70" s="11"/>
       <c r="J70" s="12"/>
     </row>
-    <row r="71" spans="1:10" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:10" ht="27.6" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A71" s="11" t="s">
         <v>150</v>
       </c>
@@ -6701,7 +6701,7 @@
       <c r="I71" s="11"/>
       <c r="J71" s="12"/>
     </row>
-    <row r="72" spans="1:10" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:10" ht="27.6" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A72" s="11" t="s">
         <v>152</v>
       </c>
@@ -6721,7 +6721,7 @@
         <v>0.75</v>
       </c>
       <c r="G72" s="12" t="s">
-        <v>54</v>
+        <v>76</v>
       </c>
       <c r="H72" s="11" t="s">
         <v>43</v>
@@ -6729,7 +6729,7 @@
       <c r="I72" s="11"/>
       <c r="J72" s="12"/>
     </row>
-    <row r="73" spans="1:10" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:10" ht="27.6" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A73" s="11" t="s">
         <v>154</v>
       </c>
@@ -6757,7 +6757,7 @@
       <c r="I73" s="11"/>
       <c r="J73" s="12"/>
     </row>
-    <row r="74" spans="1:10" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:10" ht="27.6" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A74" s="11" t="s">
         <v>156</v>
       </c>
@@ -6777,7 +6777,7 @@
         <v>0.5</v>
       </c>
       <c r="G74" s="12" t="s">
-        <v>54</v>
+        <v>76</v>
       </c>
       <c r="H74" s="11" t="s">
         <v>43</v>
@@ -6785,7 +6785,7 @@
       <c r="I74" s="11"/>
       <c r="J74" s="12"/>
     </row>
-    <row r="75" spans="1:10" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:10" ht="27.6" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A75" s="11" t="s">
         <v>157</v>
       </c>
@@ -6813,7 +6813,7 @@
       <c r="I75" s="11"/>
       <c r="J75" s="12"/>
     </row>
-    <row r="76" spans="1:10" ht="55.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:10" ht="55.2" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A76" s="11" t="s">
         <v>159</v>
       </c>
@@ -6833,7 +6833,7 @@
         <v>0.25</v>
       </c>
       <c r="G76" s="12" t="s">
-        <v>54</v>
+        <v>76</v>
       </c>
       <c r="H76" s="11" t="s">
         <v>43</v>
@@ -6841,7 +6841,7 @@
       <c r="I76" s="11"/>
       <c r="J76" s="12"/>
     </row>
-    <row r="77" spans="1:10" ht="41.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:10" ht="41.4" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A77" s="11" t="s">
         <v>160</v>
       </c>
@@ -6869,7 +6869,7 @@
       <c r="I77" s="11"/>
       <c r="J77" s="12"/>
     </row>
-    <row r="78" spans="1:10" ht="41.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:10" ht="41.4" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A78" s="11" t="s">
         <v>161</v>
       </c>
@@ -6897,7 +6897,7 @@
       <c r="I78" s="11"/>
       <c r="J78" s="12"/>
     </row>
-    <row r="79" spans="1:10" ht="41.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:10" ht="41.4" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A79" s="11" t="s">
         <v>162</v>
       </c>
@@ -6925,7 +6925,7 @@
       <c r="I79" s="11"/>
       <c r="J79" s="12"/>
     </row>
-    <row r="80" spans="1:10" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:10" ht="27.6" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A80" s="11" t="s">
         <v>163</v>
       </c>
@@ -6953,7 +6953,7 @@
       <c r="I80" s="11"/>
       <c r="J80" s="12"/>
     </row>
-    <row r="81" spans="1:10" ht="41.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:10" ht="41.4" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A81" s="11" t="s">
         <v>164</v>
       </c>
@@ -6981,7 +6981,7 @@
       <c r="I81" s="11"/>
       <c r="J81" s="12"/>
     </row>
-    <row r="82" spans="1:10" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:10" ht="27.6" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A82" s="11" t="s">
         <v>167</v>
       </c>
@@ -7001,7 +7001,7 @@
         <v>0.5</v>
       </c>
       <c r="G82" s="12" t="s">
-        <v>54</v>
+        <v>76</v>
       </c>
       <c r="H82" s="11" t="s">
         <v>43</v>
@@ -7009,7 +7009,7 @@
       <c r="I82" s="11"/>
       <c r="J82" s="12"/>
     </row>
-    <row r="83" spans="1:10" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:10" ht="27.6" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A83" s="11" t="s">
         <v>169</v>
       </c>
@@ -7037,7 +7037,7 @@
       <c r="I83" s="11"/>
       <c r="J83" s="12"/>
     </row>
-    <row r="84" spans="1:10" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:10" ht="27.6" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A84" s="11" t="s">
         <v>171</v>
       </c>
@@ -7065,7 +7065,7 @@
       <c r="I84" s="11"/>
       <c r="J84" s="12"/>
     </row>
-    <row r="85" spans="1:10" ht="41.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:10" ht="41.4" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A85" s="11" t="s">
         <v>173</v>
       </c>
@@ -7085,7 +7085,7 @@
         <v>0.5</v>
       </c>
       <c r="G85" s="12" t="s">
-        <v>54</v>
+        <v>76</v>
       </c>
       <c r="H85" s="11" t="s">
         <v>43</v>
@@ -7093,7 +7093,7 @@
       <c r="I85" s="11"/>
       <c r="J85" s="12"/>
     </row>
-    <row r="86" spans="1:10" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:10" ht="27.6" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A86" s="11" t="s">
         <v>175</v>
       </c>
@@ -7121,7 +7121,7 @@
       <c r="I86" s="11"/>
       <c r="J86" s="12"/>
     </row>
-    <row r="87" spans="1:10" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:10" ht="27.6" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A87" s="11" t="s">
         <v>176</v>
       </c>
@@ -7149,7 +7149,7 @@
       <c r="I87" s="11"/>
       <c r="J87" s="12"/>
     </row>
-    <row r="88" spans="1:10" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:10" ht="27.6" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A88" s="11" t="s">
         <v>178</v>
       </c>
@@ -7169,7 +7169,7 @@
         <v>0.5</v>
       </c>
       <c r="G88" s="12" t="s">
-        <v>54</v>
+        <v>76</v>
       </c>
       <c r="H88" s="11" t="s">
         <v>43</v>
@@ -7177,7 +7177,7 @@
       <c r="I88" s="11"/>
       <c r="J88" s="12"/>
     </row>
-    <row r="89" spans="1:10" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:10" ht="27.6" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A89" s="11" t="s">
         <v>180</v>
       </c>
@@ -7205,7 +7205,7 @@
       <c r="I89" s="11"/>
       <c r="J89" s="12"/>
     </row>
-    <row r="90" spans="1:10" ht="55.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:10" ht="55.2" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A90" s="11" t="s">
         <v>181</v>
       </c>
@@ -7225,7 +7225,7 @@
         <v>0.5</v>
       </c>
       <c r="G90" s="12" t="s">
-        <v>54</v>
+        <v>76</v>
       </c>
       <c r="H90" s="11" t="s">
         <v>43</v>
@@ -7233,7 +7233,7 @@
       <c r="I90" s="11"/>
       <c r="J90" s="12"/>
     </row>
-    <row r="91" spans="1:10" ht="41.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:10" ht="41.4" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A91" s="11" t="s">
         <v>182</v>
       </c>
@@ -7261,7 +7261,7 @@
       <c r="I91" s="11"/>
       <c r="J91" s="12"/>
     </row>
-    <row r="92" spans="1:10" ht="41.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:10" ht="41.4" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A92" s="11" t="s">
         <v>183</v>
       </c>
@@ -7337,7 +7337,7 @@
         <v>0.5</v>
       </c>
       <c r="G94" s="12" t="s">
-        <v>54</v>
+        <v>76</v>
       </c>
       <c r="H94" s="11" t="s">
         <v>43</v>
@@ -7421,7 +7421,7 @@
         <v>0.5</v>
       </c>
       <c r="G97" s="12" t="s">
-        <v>54</v>
+        <v>76</v>
       </c>
       <c r="H97" s="11" t="s">
         <v>43</v>
@@ -7477,7 +7477,7 @@
         <v>0.5</v>
       </c>
       <c r="G99" s="12" t="s">
-        <v>54</v>
+        <v>76</v>
       </c>
       <c r="H99" s="11" t="s">
         <v>43</v>
@@ -7533,7 +7533,7 @@
         <v>0.5</v>
       </c>
       <c r="G101" s="12" t="s">
-        <v>54</v>
+        <v>76</v>
       </c>
       <c r="H101" s="11" t="s">
         <v>43</v>
@@ -7569,7 +7569,7 @@
       <c r="I102" s="11"/>
       <c r="J102" s="12"/>
     </row>
-    <row r="103" spans="1:10" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:10" ht="27.6" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A103" s="11" t="s">
         <v>204</v>
       </c>
@@ -7597,7 +7597,7 @@
       <c r="I103" s="11"/>
       <c r="J103" s="12"/>
     </row>
-    <row r="104" spans="1:10" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:10" ht="27.6" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A104" s="11" t="s">
         <v>205</v>
       </c>
@@ -7625,7 +7625,7 @@
       <c r="I104" s="11"/>
       <c r="J104" s="12"/>
     </row>
-    <row r="105" spans="1:10" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:10" ht="27.6" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A105" s="11" t="s">
         <v>206</v>
       </c>
@@ -7653,7 +7653,7 @@
       <c r="I105" s="11"/>
       <c r="J105" s="12"/>
     </row>
-    <row r="106" spans="1:10" ht="55.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:10" ht="55.2" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A106" s="11" t="s">
         <v>210</v>
       </c>
@@ -7673,7 +7673,7 @@
         <v>0.5</v>
       </c>
       <c r="G106" s="12" t="s">
-        <v>54</v>
+        <v>76</v>
       </c>
       <c r="H106" s="11" t="s">
         <v>43</v>
@@ -7681,7 +7681,7 @@
       <c r="I106" s="11"/>
       <c r="J106" s="12"/>
     </row>
-    <row r="107" spans="1:10" ht="41.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:10" ht="41.4" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A107" s="11" t="s">
         <v>212</v>
       </c>
@@ -7709,7 +7709,7 @@
       <c r="I107" s="11"/>
       <c r="J107" s="12"/>
     </row>
-    <row r="108" spans="1:10" ht="41.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:10" ht="41.4" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A108" s="11" t="s">
         <v>214</v>
       </c>
@@ -7737,7 +7737,7 @@
       <c r="I108" s="11"/>
       <c r="J108" s="12"/>
     </row>
-    <row r="109" spans="1:10" ht="41.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:10" ht="41.4" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A109" s="11" t="s">
         <v>216</v>
       </c>
@@ -7757,7 +7757,7 @@
         <v>0.5</v>
       </c>
       <c r="G109" s="12" t="s">
-        <v>54</v>
+        <v>76</v>
       </c>
       <c r="H109" s="11" t="s">
         <v>43</v>
@@ -7765,7 +7765,7 @@
       <c r="I109" s="11"/>
       <c r="J109" s="12"/>
     </row>
-    <row r="110" spans="1:10" ht="41.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:10" ht="41.4" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A110" s="11" t="s">
         <v>218</v>
       </c>
@@ -7793,7 +7793,7 @@
       <c r="I110" s="11"/>
       <c r="J110" s="12"/>
     </row>
-    <row r="111" spans="1:10" ht="41.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:10" ht="41.4" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A111" s="11" t="s">
         <v>220</v>
       </c>
@@ -7813,7 +7813,7 @@
         <v>0.5</v>
       </c>
       <c r="G111" s="12" t="s">
-        <v>54</v>
+        <v>76</v>
       </c>
       <c r="H111" s="11" t="s">
         <v>43</v>
@@ -7821,7 +7821,7 @@
       <c r="I111" s="11"/>
       <c r="J111" s="12"/>
     </row>
-    <row r="112" spans="1:10" ht="41.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:10" ht="41.4" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A112" s="11" t="s">
         <v>222</v>
       </c>
@@ -7849,7 +7849,7 @@
       <c r="I112" s="11"/>
       <c r="J112" s="12"/>
     </row>
-    <row r="113" spans="1:10" ht="41.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:10" ht="41.4" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A113" s="11" t="s">
         <v>223</v>
       </c>
@@ -7869,7 +7869,7 @@
         <v>0.5</v>
       </c>
       <c r="G113" s="12" t="s">
-        <v>54</v>
+        <v>76</v>
       </c>
       <c r="H113" s="11" t="s">
         <v>43</v>
@@ -7877,7 +7877,7 @@
       <c r="I113" s="11"/>
       <c r="J113" s="12"/>
     </row>
-    <row r="114" spans="1:10" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:10" ht="27.6" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A114" s="11" t="s">
         <v>224</v>
       </c>
@@ -7897,7 +7897,7 @@
         <v>0.5</v>
       </c>
       <c r="G114" s="12" t="s">
-        <v>54</v>
+        <v>76</v>
       </c>
       <c r="H114" s="11" t="s">
         <v>43</v>
@@ -7905,7 +7905,7 @@
       <c r="I114" s="11"/>
       <c r="J114" s="12"/>
     </row>
-    <row r="115" spans="1:10" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:10" ht="27.6" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A115" s="11" t="s">
         <v>225</v>
       </c>
@@ -7933,7 +7933,7 @@
       <c r="I115" s="11"/>
       <c r="J115" s="12"/>
     </row>
-    <row r="116" spans="1:10" ht="41.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:10" ht="41.4" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A116" s="11" t="s">
         <v>226</v>
       </c>
@@ -7961,7 +7961,7 @@
       <c r="I116" s="11"/>
       <c r="J116" s="12"/>
     </row>
-    <row r="117" spans="1:10" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:10" ht="27.6" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A117" s="11" t="s">
         <v>227</v>
       </c>
@@ -7981,7 +7981,7 @@
         <v>0.5</v>
       </c>
       <c r="G117" s="12" t="s">
-        <v>54</v>
+        <v>76</v>
       </c>
       <c r="H117" s="11" t="s">
         <v>18</v>
@@ -7993,7 +7993,7 @@
         <v>231</v>
       </c>
     </row>
-    <row r="118" spans="1:10" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:10" ht="27.6" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A118" s="11" t="s">
         <v>232</v>
       </c>
@@ -8013,7 +8013,7 @@
         <v>0.5</v>
       </c>
       <c r="G118" s="12" t="s">
-        <v>54</v>
+        <v>76</v>
       </c>
       <c r="H118" s="11" t="s">
         <v>18</v>
@@ -8025,7 +8025,7 @@
         <v>234</v>
       </c>
     </row>
-    <row r="119" spans="1:10" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:10" ht="27.6" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A119" s="11" t="s">
         <v>235</v>
       </c>
@@ -8045,7 +8045,7 @@
         <v>0.5</v>
       </c>
       <c r="G119" s="12" t="s">
-        <v>54</v>
+        <v>76</v>
       </c>
       <c r="H119" s="11" t="s">
         <v>18</v>
@@ -8057,7 +8057,7 @@
         <v>237</v>
       </c>
     </row>
-    <row r="120" spans="1:10" ht="41.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:10" ht="41.4" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A120" s="11" t="s">
         <v>238</v>
       </c>
@@ -8077,7 +8077,7 @@
         <v>0.5</v>
       </c>
       <c r="G120" s="12" t="s">
-        <v>54</v>
+        <v>76</v>
       </c>
       <c r="H120" s="11" t="s">
         <v>18</v>
@@ -8089,7 +8089,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="121" spans="1:10" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:10" ht="27.6" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A121" s="11" t="s">
         <v>241</v>
       </c>
@@ -8109,7 +8109,7 @@
         <v>0.5</v>
       </c>
       <c r="G121" s="12" t="s">
-        <v>54</v>
+        <v>76</v>
       </c>
       <c r="H121" s="11" t="s">
         <v>18</v>
@@ -8121,7 +8121,7 @@
         <v>243</v>
       </c>
     </row>
-    <row r="122" spans="1:10" ht="55.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:10" ht="55.2" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A122" s="11" t="s">
         <v>244</v>
       </c>
@@ -8141,7 +8141,7 @@
         <v>0.75</v>
       </c>
       <c r="G122" s="12" t="s">
-        <v>54</v>
+        <v>76</v>
       </c>
       <c r="H122" s="11" t="s">
         <v>18</v>
@@ -8153,7 +8153,7 @@
         <v>246</v>
       </c>
     </row>
-    <row r="123" spans="1:10" ht="41.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:10" ht="41.4" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A123" s="11" t="s">
         <v>247</v>
       </c>
@@ -8173,7 +8173,7 @@
         <v>0.75</v>
       </c>
       <c r="G123" s="12" t="s">
-        <v>54</v>
+        <v>76</v>
       </c>
       <c r="H123" s="11" t="s">
         <v>18</v>
@@ -8185,7 +8185,7 @@
         <v>249</v>
       </c>
     </row>
-    <row r="124" spans="1:10" ht="41.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:10" ht="41.4" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A124" s="11" t="s">
         <v>250</v>
       </c>
@@ -8205,7 +8205,7 @@
         <v>1.25</v>
       </c>
       <c r="G124" s="12" t="s">
-        <v>54</v>
+        <v>76</v>
       </c>
       <c r="H124" s="11" t="s">
         <v>18</v>
@@ -8217,7 +8217,7 @@
         <v>252</v>
       </c>
     </row>
-    <row r="125" spans="1:10" ht="41.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:10" ht="41.4" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A125" s="11" t="s">
         <v>253</v>
       </c>
@@ -8245,7 +8245,7 @@
       <c r="I125" s="11"/>
       <c r="J125" s="12"/>
     </row>
-    <row r="126" spans="1:10" ht="41.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:10" ht="41.4" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A126" s="11" t="s">
         <v>254</v>
       </c>
@@ -8265,7 +8265,7 @@
         <v>0.5</v>
       </c>
       <c r="G126" s="12" t="s">
-        <v>54</v>
+        <v>76</v>
       </c>
       <c r="H126" s="11" t="s">
         <v>18</v>
@@ -8277,7 +8277,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="127" spans="1:10" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:10" ht="27.6" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A127" s="11" t="s">
         <v>256</v>
       </c>
@@ -8305,7 +8305,7 @@
       <c r="I127" s="11"/>
       <c r="J127" s="12"/>
     </row>
-    <row r="128" spans="1:10" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:10" ht="27.6" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A128" s="11" t="s">
         <v>257</v>
       </c>
@@ -8353,7 +8353,7 @@
         <v>0.5</v>
       </c>
       <c r="G129" s="12" t="s">
-        <v>54</v>
+        <v>76</v>
       </c>
       <c r="H129" s="11" t="s">
         <v>43</v>
@@ -8437,7 +8437,7 @@
         <v>0.25</v>
       </c>
       <c r="G132" s="12" t="s">
-        <v>54</v>
+        <v>76</v>
       </c>
       <c r="H132" s="11" t="s">
         <v>43</v>
@@ -8493,7 +8493,7 @@
         <v>0.5</v>
       </c>
       <c r="G134" s="12" t="s">
-        <v>54</v>
+        <v>76</v>
       </c>
       <c r="H134" s="11" t="s">
         <v>43</v>
@@ -8549,7 +8549,7 @@
         <v>0.75</v>
       </c>
       <c r="G136" s="12" t="s">
-        <v>54</v>
+        <v>76</v>
       </c>
       <c r="H136" s="11" t="s">
         <v>43</v>
@@ -8557,7 +8557,7 @@
       <c r="I136" s="11"/>
       <c r="J136" s="12"/>
     </row>
-    <row r="137" spans="1:10" ht="41.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="137" spans="1:10" ht="41.4" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A137" s="11" t="s">
         <v>274</v>
       </c>
@@ -8577,7 +8577,7 @@
         <v>0.25</v>
       </c>
       <c r="G137" s="12" t="s">
-        <v>54</v>
+        <v>76</v>
       </c>
       <c r="H137" s="11" t="s">
         <v>43</v>
@@ -8605,7 +8605,7 @@
         <v>0.25</v>
       </c>
       <c r="G138" s="12" t="s">
-        <v>54</v>
+        <v>76</v>
       </c>
       <c r="H138" s="11" t="s">
         <v>43</v>
@@ -8613,7 +8613,7 @@
       <c r="I138" s="11"/>
       <c r="J138" s="12"/>
     </row>
-    <row r="139" spans="1:10" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="139" spans="1:10" ht="27.6" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A139" s="11" t="s">
         <v>276</v>
       </c>
@@ -8641,7 +8641,7 @@
       <c r="I139" s="11"/>
       <c r="J139" s="12"/>
     </row>
-    <row r="140" spans="1:10" ht="41.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="140" spans="1:10" ht="41.4" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A140" s="11" t="s">
         <v>277</v>
       </c>
@@ -8669,7 +8669,7 @@
       <c r="I140" s="11"/>
       <c r="J140" s="12"/>
     </row>
-    <row r="141" spans="1:10" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="141" spans="1:10" ht="27.6" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A141" s="11" t="s">
         <v>278</v>
       </c>
@@ -8689,7 +8689,7 @@
         <v>0.75</v>
       </c>
       <c r="G141" s="12" t="s">
-        <v>54</v>
+        <v>76</v>
       </c>
       <c r="H141" s="11" t="s">
         <v>18</v>
@@ -8701,7 +8701,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="142" spans="1:10" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="142" spans="1:10" ht="27.6" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A142" s="11" t="s">
         <v>282</v>
       </c>
@@ -8721,7 +8721,7 @@
         <v>0.5</v>
       </c>
       <c r="G142" s="12" t="s">
-        <v>54</v>
+        <v>76</v>
       </c>
       <c r="H142" s="11" t="s">
         <v>18</v>
@@ -8733,7 +8733,7 @@
         <v>284</v>
       </c>
     </row>
-    <row r="143" spans="1:10" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="143" spans="1:10" ht="27.6" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A143" s="11" t="s">
         <v>285</v>
       </c>
@@ -8753,7 +8753,7 @@
         <v>0.5</v>
       </c>
       <c r="G143" s="12" t="s">
-        <v>54</v>
+        <v>76</v>
       </c>
       <c r="H143" s="11" t="s">
         <v>18</v>
@@ -8765,7 +8765,7 @@
         <v>287</v>
       </c>
     </row>
-    <row r="144" spans="1:10" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="144" spans="1:10" ht="27.6" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A144" s="11" t="s">
         <v>288</v>
       </c>
@@ -8785,7 +8785,7 @@
         <v>0.5</v>
       </c>
       <c r="G144" s="12" t="s">
-        <v>54</v>
+        <v>76</v>
       </c>
       <c r="H144" s="11" t="s">
         <v>18</v>
@@ -8797,7 +8797,7 @@
         <v>290</v>
       </c>
     </row>
-    <row r="145" spans="1:10" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="145" spans="1:10" ht="27.6" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A145" s="11" t="s">
         <v>291</v>
       </c>
@@ -8817,7 +8817,7 @@
         <v>0.5</v>
       </c>
       <c r="G145" s="12" t="s">
-        <v>54</v>
+        <v>76</v>
       </c>
       <c r="H145" s="11" t="s">
         <v>18</v>
@@ -8829,7 +8829,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="146" spans="1:10" ht="41.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="146" spans="1:10" ht="41.4" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A146" s="11" t="s">
         <v>293</v>
       </c>
@@ -8849,7 +8849,7 @@
         <v>0.75</v>
       </c>
       <c r="G146" s="12" t="s">
-        <v>54</v>
+        <v>76</v>
       </c>
       <c r="H146" s="11" t="s">
         <v>18</v>
@@ -8861,7 +8861,7 @@
         <v>295</v>
       </c>
     </row>
-    <row r="147" spans="1:10" ht="151.80000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="147" spans="1:10" ht="151.80000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A147" s="11" t="s">
         <v>296</v>
       </c>
@@ -8881,7 +8881,7 @@
         <v>0.75</v>
       </c>
       <c r="G147" s="12" t="s">
-        <v>54</v>
+        <v>76</v>
       </c>
       <c r="H147" s="11" t="s">
         <v>18</v>
@@ -8893,7 +8893,7 @@
         <v>298</v>
       </c>
     </row>
-    <row r="148" spans="1:10" ht="55.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="148" spans="1:10" ht="55.2" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A148" s="11" t="s">
         <v>299</v>
       </c>
@@ -8913,7 +8913,7 @@
         <v>0.5</v>
       </c>
       <c r="G148" s="12" t="s">
-        <v>54</v>
+        <v>76</v>
       </c>
       <c r="H148" s="11" t="s">
         <v>18</v>
@@ -8925,7 +8925,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="149" spans="1:10" ht="41.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="149" spans="1:10" ht="41.4" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A149" s="11" t="s">
         <v>301</v>
       </c>
@@ -8953,7 +8953,7 @@
       <c r="I149" s="11"/>
       <c r="J149" s="12"/>
     </row>
-    <row r="150" spans="1:10" ht="41.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="150" spans="1:10" ht="41.4" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A150" s="11" t="s">
         <v>302</v>
       </c>
@@ -8981,7 +8981,7 @@
       <c r="I150" s="11"/>
       <c r="J150" s="12"/>
     </row>
-    <row r="151" spans="1:10" ht="41.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="151" spans="1:10" ht="41.4" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A151" s="11" t="s">
         <v>303</v>
       </c>
@@ -9009,7 +9009,7 @@
       <c r="I151" s="11"/>
       <c r="J151" s="12"/>
     </row>
-    <row r="152" spans="1:10" ht="41.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="152" spans="1:10" ht="41.4" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A152" s="11" t="s">
         <v>306</v>
       </c>
@@ -9037,7 +9037,7 @@
       <c r="I152" s="11"/>
       <c r="J152" s="12"/>
     </row>
-    <row r="153" spans="1:10" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="153" spans="1:10" ht="27.6" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A153" s="11" t="s">
         <v>308</v>
       </c>
@@ -9057,7 +9057,7 @@
         <v>0.5</v>
       </c>
       <c r="G153" s="12" t="s">
-        <v>54</v>
+        <v>76</v>
       </c>
       <c r="H153" s="11" t="s">
         <v>43</v>
@@ -9065,7 +9065,7 @@
       <c r="I153" s="11"/>
       <c r="J153" s="12"/>
     </row>
-    <row r="154" spans="1:10" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="154" spans="1:10" ht="27.6" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A154" s="11" t="s">
         <v>309</v>
       </c>
@@ -9093,7 +9093,7 @@
       <c r="I154" s="11"/>
       <c r="J154" s="12"/>
     </row>
-    <row r="155" spans="1:10" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="155" spans="1:10" ht="27.6" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A155" s="11" t="s">
         <v>311</v>
       </c>
@@ -9121,7 +9121,7 @@
       <c r="I155" s="11"/>
       <c r="J155" s="12"/>
     </row>
-    <row r="156" spans="1:10" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="156" spans="1:10" ht="27.6" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A156" s="11" t="s">
         <v>312</v>
       </c>
@@ -9149,7 +9149,7 @@
       <c r="I156" s="11"/>
       <c r="J156" s="12"/>
     </row>
-    <row r="157" spans="1:10" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="157" spans="1:10" ht="27.6" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A157" s="11" t="s">
         <v>314</v>
       </c>
@@ -9169,7 +9169,7 @@
         <v>0.25</v>
       </c>
       <c r="G157" s="12" t="s">
-        <v>54</v>
+        <v>76</v>
       </c>
       <c r="H157" s="11" t="s">
         <v>43</v>
@@ -9177,7 +9177,7 @@
       <c r="I157" s="11"/>
       <c r="J157" s="12"/>
     </row>
-    <row r="158" spans="1:10" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="158" spans="1:10" ht="27.6" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A158" s="11" t="s">
         <v>315</v>
       </c>
@@ -9205,7 +9205,7 @@
       <c r="I158" s="11"/>
       <c r="J158" s="12"/>
     </row>
-    <row r="159" spans="1:10" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="159" spans="1:10" ht="27.6" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A159" s="11" t="s">
         <v>316</v>
       </c>
@@ -9233,7 +9233,7 @@
       <c r="I159" s="11"/>
       <c r="J159" s="12"/>
     </row>
-    <row r="160" spans="1:10" ht="55.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="160" spans="1:10" ht="55.2" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A160" s="11" t="s">
         <v>317</v>
       </c>
@@ -9253,7 +9253,7 @@
         <v>0.75</v>
       </c>
       <c r="G160" s="12" t="s">
-        <v>54</v>
+        <v>76</v>
       </c>
       <c r="H160" s="11" t="s">
         <v>43</v>
@@ -9261,7 +9261,7 @@
       <c r="I160" s="11"/>
       <c r="J160" s="12"/>
     </row>
-    <row r="161" spans="1:10" ht="41.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="161" spans="1:10" ht="41.4" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A161" s="11" t="s">
         <v>320</v>
       </c>
@@ -9289,7 +9289,7 @@
       <c r="I161" s="11"/>
       <c r="J161" s="12"/>
     </row>
-    <row r="162" spans="1:10" ht="41.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="162" spans="1:10" ht="41.4" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A162" s="11" t="s">
         <v>322</v>
       </c>
@@ -9317,7 +9317,7 @@
       <c r="I162" s="11"/>
       <c r="J162" s="12"/>
     </row>
-    <row r="163" spans="1:10" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="163" spans="1:10" ht="27.6" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A163" s="11" t="s">
         <v>324</v>
       </c>
@@ -9337,7 +9337,7 @@
         <v>0.5</v>
       </c>
       <c r="G163" s="12" t="s">
-        <v>54</v>
+        <v>76</v>
       </c>
       <c r="H163" s="11" t="s">
         <v>43</v>
@@ -9345,7 +9345,7 @@
       <c r="I163" s="11"/>
       <c r="J163" s="12"/>
     </row>
-    <row r="164" spans="1:10" ht="41.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="164" spans="1:10" ht="41.4" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A164" s="11" t="s">
         <v>325</v>
       </c>
@@ -9365,7 +9365,7 @@
         <v>1.5</v>
       </c>
       <c r="G164" s="12" t="s">
-        <v>54</v>
+        <v>76</v>
       </c>
       <c r="H164" s="11" t="s">
         <v>43</v>
@@ -9373,7 +9373,7 @@
       <c r="I164" s="11"/>
       <c r="J164" s="12"/>
     </row>
-    <row r="165" spans="1:10" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="165" spans="1:10" ht="27.6" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A165" s="11" t="s">
         <v>327</v>
       </c>
@@ -9401,7 +9401,7 @@
       <c r="I165" s="11"/>
       <c r="J165" s="12"/>
     </row>
-    <row r="166" spans="1:10" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="166" spans="1:10" ht="27.6" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A166" s="11" t="s">
         <v>328</v>
       </c>
@@ -9429,7 +9429,7 @@
       <c r="I166" s="11"/>
       <c r="J166" s="12"/>
     </row>
-    <row r="167" spans="1:10" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="167" spans="1:10" ht="27.6" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A167" s="11" t="s">
         <v>329</v>
       </c>
@@ -9457,7 +9457,7 @@
       <c r="I167" s="11"/>
       <c r="J167" s="12"/>
     </row>
-    <row r="168" spans="1:10" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="168" spans="1:10" ht="27.6" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A168" s="11" t="s">
         <v>330</v>
       </c>
@@ -9477,7 +9477,7 @@
         <v>0.5</v>
       </c>
       <c r="G168" s="12" t="s">
-        <v>54</v>
+        <v>76</v>
       </c>
       <c r="H168" s="11" t="s">
         <v>18</v>
@@ -9489,7 +9489,7 @@
         <v>334</v>
       </c>
     </row>
-    <row r="169" spans="1:10" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="169" spans="1:10" ht="27.6" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A169" s="11" t="s">
         <v>335</v>
       </c>
@@ -9509,7 +9509,7 @@
         <v>0.5</v>
       </c>
       <c r="G169" s="12" t="s">
-        <v>54</v>
+        <v>76</v>
       </c>
       <c r="H169" s="11" t="s">
         <v>18</v>
@@ -9521,7 +9521,7 @@
         <v>337</v>
       </c>
     </row>
-    <row r="170" spans="1:10" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="170" spans="1:10" ht="27.6" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A170" s="11" t="s">
         <v>338</v>
       </c>
@@ -9541,7 +9541,7 @@
         <v>0.5</v>
       </c>
       <c r="G170" s="12" t="s">
-        <v>54</v>
+        <v>76</v>
       </c>
       <c r="H170" s="11" t="s">
         <v>18</v>
@@ -9553,7 +9553,7 @@
         <v>340</v>
       </c>
     </row>
-    <row r="171" spans="1:10" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="171" spans="1:10" ht="27.6" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A171" s="11" t="s">
         <v>341</v>
       </c>
@@ -9573,7 +9573,7 @@
         <v>0.5</v>
       </c>
       <c r="G171" s="12" t="s">
-        <v>54</v>
+        <v>76</v>
       </c>
       <c r="H171" s="11" t="s">
         <v>18</v>
@@ -9585,7 +9585,7 @@
         <v>343</v>
       </c>
     </row>
-    <row r="172" spans="1:10" ht="41.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="172" spans="1:10" ht="41.4" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A172" s="11" t="s">
         <v>344</v>
       </c>
@@ -9605,7 +9605,7 @@
         <v>0.5</v>
       </c>
       <c r="G172" s="12" t="s">
-        <v>54</v>
+        <v>76</v>
       </c>
       <c r="H172" s="11" t="s">
         <v>18</v>
@@ -9617,7 +9617,7 @@
         <v>346</v>
       </c>
     </row>
-    <row r="173" spans="1:10" ht="55.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="173" spans="1:10" ht="55.2" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A173" s="11" t="s">
         <v>347</v>
       </c>
@@ -9637,7 +9637,7 @@
         <v>0.25</v>
       </c>
       <c r="G173" s="12" t="s">
-        <v>54</v>
+        <v>76</v>
       </c>
       <c r="H173" s="11" t="s">
         <v>18</v>
@@ -9649,7 +9649,7 @@
         <v>349</v>
       </c>
     </row>
-    <row r="174" spans="1:10" ht="41.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="174" spans="1:10" ht="41.4" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A174" s="11" t="s">
         <v>350</v>
       </c>
@@ -9669,7 +9669,7 @@
         <v>0.5</v>
       </c>
       <c r="G174" s="12" t="s">
-        <v>54</v>
+        <v>76</v>
       </c>
       <c r="H174" s="11" t="s">
         <v>18</v>
@@ -9681,7 +9681,7 @@
         <v>352</v>
       </c>
     </row>
-    <row r="175" spans="1:10" ht="41.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="175" spans="1:10" ht="41.4" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A175" s="11" t="s">
         <v>353</v>
       </c>
@@ -9701,7 +9701,7 @@
         <v>0.5</v>
       </c>
       <c r="G175" s="12" t="s">
-        <v>54</v>
+        <v>76</v>
       </c>
       <c r="H175" s="11" t="s">
         <v>18</v>
@@ -9713,7 +9713,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="176" spans="1:10" ht="41.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="176" spans="1:10" ht="41.4" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A176" s="11" t="s">
         <v>356</v>
       </c>
@@ -9733,7 +9733,7 @@
         <v>0.5</v>
       </c>
       <c r="G176" s="12" t="s">
-        <v>54</v>
+        <v>76</v>
       </c>
       <c r="H176" s="11" t="s">
         <v>18</v>
@@ -9745,7 +9745,7 @@
         <v>357</v>
       </c>
     </row>
-    <row r="177" spans="1:10" ht="41.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="177" spans="1:10" ht="41.4" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A177" s="11" t="s">
         <v>358</v>
       </c>
@@ -9765,7 +9765,7 @@
         <v>0.5</v>
       </c>
       <c r="G177" s="12" t="s">
-        <v>54</v>
+        <v>76</v>
       </c>
       <c r="H177" s="11" t="s">
         <v>18</v>
@@ -9777,7 +9777,7 @@
         <v>359</v>
       </c>
     </row>
-    <row r="178" spans="1:10" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="178" spans="1:10" ht="27.6" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A178" s="11" t="s">
         <v>360</v>
       </c>
@@ -9805,7 +9805,7 @@
       <c r="I178" s="11"/>
       <c r="J178" s="12"/>
     </row>
-    <row r="179" spans="1:10" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="179" spans="1:10" ht="27.6" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A179" s="11" t="s">
         <v>361</v>
       </c>
@@ -9833,7 +9833,7 @@
       <c r="I179" s="11"/>
       <c r="J179" s="12"/>
     </row>
-    <row r="180" spans="1:10" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="180" spans="1:10" ht="27.6" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A180" s="11" t="s">
         <v>362</v>
       </c>
@@ -9853,7 +9853,7 @@
         <v>0.75</v>
       </c>
       <c r="G180" s="12" t="s">
-        <v>54</v>
+        <v>76</v>
       </c>
       <c r="H180" s="11" t="s">
         <v>18</v>
@@ -9865,7 +9865,7 @@
         <v>366</v>
       </c>
     </row>
-    <row r="181" spans="1:10" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="181" spans="1:10" ht="27.6" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A181" s="11" t="s">
         <v>367</v>
       </c>
@@ -9885,7 +9885,7 @@
         <v>0.5</v>
       </c>
       <c r="G181" s="12" t="s">
-        <v>54</v>
+        <v>76</v>
       </c>
       <c r="H181" s="11" t="s">
         <v>18</v>
@@ -9897,7 +9897,7 @@
         <v>369</v>
       </c>
     </row>
-    <row r="182" spans="1:10" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="182" spans="1:10" ht="27.6" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A182" s="11" t="s">
         <v>370</v>
       </c>
@@ -9917,7 +9917,7 @@
         <v>0.5</v>
       </c>
       <c r="G182" s="12" t="s">
-        <v>54</v>
+        <v>76</v>
       </c>
       <c r="H182" s="11" t="s">
         <v>18</v>
@@ -9929,7 +9929,7 @@
         <v>372</v>
       </c>
     </row>
-    <row r="183" spans="1:10" ht="41.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="183" spans="1:10" ht="41.4" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A183" s="11" t="s">
         <v>373</v>
       </c>
@@ -9949,7 +9949,7 @@
         <v>0.5</v>
       </c>
       <c r="G183" s="12" t="s">
-        <v>54</v>
+        <v>76</v>
       </c>
       <c r="H183" s="11" t="s">
         <v>18</v>
@@ -9961,7 +9961,7 @@
         <v>375</v>
       </c>
     </row>
-    <row r="184" spans="1:10" ht="55.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="184" spans="1:10" ht="55.2" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A184" s="11" t="s">
         <v>376</v>
       </c>
@@ -9981,7 +9981,7 @@
         <v>0.5</v>
       </c>
       <c r="G184" s="12" t="s">
-        <v>54</v>
+        <v>76</v>
       </c>
       <c r="H184" s="11" t="s">
         <v>43</v>
@@ -9991,7 +9991,7 @@
         <v>378</v>
       </c>
     </row>
-    <row r="185" spans="1:10" ht="41.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="185" spans="1:10" ht="41.4" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A185" s="11" t="s">
         <v>379</v>
       </c>
@@ -10011,7 +10011,7 @@
         <v>0.75</v>
       </c>
       <c r="G185" s="12" t="s">
-        <v>54</v>
+        <v>76</v>
       </c>
       <c r="H185" s="11" t="s">
         <v>18</v>
@@ -10023,7 +10023,7 @@
         <v>381</v>
       </c>
     </row>
-    <row r="186" spans="1:10" ht="41.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="186" spans="1:10" ht="41.4" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A186" s="11" t="s">
         <v>382</v>
       </c>
@@ -10043,7 +10043,7 @@
         <v>0.75</v>
       </c>
       <c r="G186" s="12" t="s">
-        <v>54</v>
+        <v>76</v>
       </c>
       <c r="H186" s="11" t="s">
         <v>18</v>
@@ -10055,7 +10055,7 @@
         <v>384</v>
       </c>
     </row>
-    <row r="187" spans="1:10" ht="41.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="187" spans="1:10" ht="41.4" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A187" s="11" t="s">
         <v>385</v>
       </c>
@@ -10075,7 +10075,7 @@
         <v>0.5</v>
       </c>
       <c r="G187" s="12" t="s">
-        <v>54</v>
+        <v>76</v>
       </c>
       <c r="H187" s="11" t="s">
         <v>18</v>
@@ -10087,7 +10087,7 @@
         <v>386</v>
       </c>
     </row>
-    <row r="188" spans="1:10" ht="41.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="188" spans="1:10" ht="41.4" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A188" s="11" t="s">
         <v>387</v>
       </c>
@@ -10115,7 +10115,7 @@
       <c r="I188" s="11"/>
       <c r="J188" s="12"/>
     </row>
-    <row r="189" spans="1:10" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="189" spans="1:10" ht="27.6" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A189" s="11" t="s">
         <v>388</v>
       </c>
@@ -10163,7 +10163,7 @@
         <v>0.5</v>
       </c>
       <c r="G190" s="12" t="s">
-        <v>54</v>
+        <v>76</v>
       </c>
       <c r="H190" s="11" t="s">
         <v>43</v>
@@ -10247,7 +10247,7 @@
         <v>0.5</v>
       </c>
       <c r="G193" s="12" t="s">
-        <v>54</v>
+        <v>76</v>
       </c>
       <c r="H193" s="11" t="s">
         <v>43</v>
@@ -10331,7 +10331,7 @@
         <v>0.5</v>
       </c>
       <c r="G196" s="12" t="s">
-        <v>54</v>
+        <v>76</v>
       </c>
       <c r="H196" s="11" t="s">
         <v>43</v>
@@ -10387,7 +10387,7 @@
         <v>0.5</v>
       </c>
       <c r="G198" s="12" t="s">
-        <v>54</v>
+        <v>76</v>
       </c>
       <c r="H198" s="11" t="s">
         <v>43</v>
@@ -10415,7 +10415,7 @@
         <v>0.5</v>
       </c>
       <c r="G199" s="12" t="s">
-        <v>54</v>
+        <v>76</v>
       </c>
       <c r="H199" s="11" t="s">
         <v>43</v>
@@ -10423,7 +10423,7 @@
       <c r="I199" s="11"/>
       <c r="J199" s="12"/>
     </row>
-    <row r="200" spans="1:10" ht="41.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="200" spans="1:10" ht="41.4" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A200" s="11" t="s">
         <v>409</v>
       </c>
@@ -10451,7 +10451,7 @@
       <c r="I200" s="11"/>
       <c r="J200" s="12"/>
     </row>
-    <row r="201" spans="1:10" ht="41.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="201" spans="1:10" ht="41.4" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A201" s="11" t="s">
         <v>410</v>
       </c>
@@ -10479,7 +10479,7 @@
       <c r="I201" s="11"/>
       <c r="J201" s="12"/>
     </row>
-    <row r="202" spans="1:10" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="202" spans="1:10" ht="27.6" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A202" s="11" t="s">
         <v>411</v>
       </c>
@@ -10499,7 +10499,7 @@
         <v>0.5</v>
       </c>
       <c r="G202" s="12" t="s">
-        <v>54</v>
+        <v>76</v>
       </c>
       <c r="H202" s="11" t="s">
         <v>43</v>
@@ -10507,7 +10507,7 @@
       <c r="I202" s="11"/>
       <c r="J202" s="12"/>
     </row>
-    <row r="203" spans="1:10" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="203" spans="1:10" ht="27.6" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A203" s="11" t="s">
         <v>415</v>
       </c>
@@ -10535,7 +10535,7 @@
       <c r="I203" s="11"/>
       <c r="J203" s="12"/>
     </row>
-    <row r="204" spans="1:10" ht="41.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="204" spans="1:10" ht="41.4" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A204" s="11" t="s">
         <v>417</v>
       </c>
@@ -10563,7 +10563,7 @@
       <c r="I204" s="11"/>
       <c r="J204" s="12"/>
     </row>
-    <row r="205" spans="1:10" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="205" spans="1:10" ht="27.6" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A205" s="11" t="s">
         <v>419</v>
       </c>
@@ -10583,7 +10583,7 @@
         <v>0.5</v>
       </c>
       <c r="G205" s="12" t="s">
-        <v>54</v>
+        <v>76</v>
       </c>
       <c r="H205" s="11" t="s">
         <v>43</v>
@@ -10591,7 +10591,7 @@
       <c r="I205" s="11"/>
       <c r="J205" s="12"/>
     </row>
-    <row r="206" spans="1:10" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="206" spans="1:10" ht="27.6" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A206" s="11" t="s">
         <v>421</v>
       </c>
@@ -10619,7 +10619,7 @@
       <c r="I206" s="11"/>
       <c r="J206" s="12"/>
     </row>
-    <row r="207" spans="1:10" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="207" spans="1:10" ht="27.6" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A207" s="11" t="s">
         <v>423</v>
       </c>
@@ -10647,7 +10647,7 @@
       <c r="I207" s="11"/>
       <c r="J207" s="12"/>
     </row>
-    <row r="208" spans="1:10" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="208" spans="1:10" ht="27.6" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A208" s="11" t="s">
         <v>425</v>
       </c>
@@ -10675,7 +10675,7 @@
       <c r="I208" s="11"/>
       <c r="J208" s="12"/>
     </row>
-    <row r="209" spans="1:10" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="209" spans="1:10" ht="27.6" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A209" s="11" t="s">
         <v>427</v>
       </c>
@@ -10695,7 +10695,7 @@
         <v>0.5</v>
       </c>
       <c r="G209" s="12" t="s">
-        <v>54</v>
+        <v>76</v>
       </c>
       <c r="H209" s="11" t="s">
         <v>43</v>
@@ -10703,7 +10703,7 @@
       <c r="I209" s="11"/>
       <c r="J209" s="12"/>
     </row>
-    <row r="210" spans="1:10" ht="55.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="210" spans="1:10" ht="55.2" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A210" s="11" t="s">
         <v>429</v>
       </c>
@@ -10731,7 +10731,7 @@
       <c r="I210" s="11"/>
       <c r="J210" s="12"/>
     </row>
-    <row r="211" spans="1:10" ht="41.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="211" spans="1:10" ht="41.4" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A211" s="11" t="s">
         <v>430</v>
       </c>
@@ -10759,7 +10759,7 @@
       <c r="I211" s="11"/>
       <c r="J211" s="12"/>
     </row>
-    <row r="212" spans="1:10" ht="41.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="212" spans="1:10" ht="41.4" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A212" s="11" t="s">
         <v>431</v>
       </c>
@@ -10787,7 +10787,7 @@
       <c r="I212" s="11"/>
       <c r="J212" s="12"/>
     </row>
-    <row r="213" spans="1:10" ht="41.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="213" spans="1:10" ht="41.4" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A213" s="11" t="s">
         <v>432</v>
       </c>
@@ -10815,7 +10815,7 @@
       <c r="I213" s="11"/>
       <c r="J213" s="12"/>
     </row>
-    <row r="214" spans="1:10" ht="41.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="214" spans="1:10" ht="41.4" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A214" s="11" t="s">
         <v>433</v>
       </c>
@@ -10835,7 +10835,7 @@
         <v>0.5</v>
       </c>
       <c r="G214" s="12" t="s">
-        <v>54</v>
+        <v>76</v>
       </c>
       <c r="H214" s="11" t="s">
         <v>43</v>
@@ -10843,7 +10843,7 @@
       <c r="I214" s="11"/>
       <c r="J214" s="12"/>
     </row>
-    <row r="215" spans="1:10" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="215" spans="1:10" ht="27.6" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A215" s="11" t="s">
         <v>436</v>
       </c>
@@ -10871,7 +10871,7 @@
       <c r="I215" s="11"/>
       <c r="J215" s="12"/>
     </row>
-    <row r="216" spans="1:10" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="216" spans="1:10" ht="27.6" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A216" s="11" t="s">
         <v>438</v>
       </c>
@@ -10899,7 +10899,7 @@
       <c r="I216" s="11"/>
       <c r="J216" s="12"/>
     </row>
-    <row r="217" spans="1:10" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="217" spans="1:10" ht="27.6" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A217" s="11" t="s">
         <v>440</v>
       </c>
@@ -10919,7 +10919,7 @@
         <v>0.25</v>
       </c>
       <c r="G217" s="12" t="s">
-        <v>54</v>
+        <v>76</v>
       </c>
       <c r="H217" s="11" t="s">
         <v>43</v>
@@ -10927,7 +10927,7 @@
       <c r="I217" s="11"/>
       <c r="J217" s="12"/>
     </row>
-    <row r="218" spans="1:10" ht="41.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="218" spans="1:10" ht="41.4" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A218" s="11" t="s">
         <v>441</v>
       </c>
@@ -10947,7 +10947,7 @@
         <v>0.75</v>
       </c>
       <c r="G218" s="12" t="s">
-        <v>54</v>
+        <v>76</v>
       </c>
       <c r="H218" s="11" t="s">
         <v>43</v>
@@ -10955,7 +10955,7 @@
       <c r="I218" s="11"/>
       <c r="J218" s="12"/>
     </row>
-    <row r="219" spans="1:10" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="219" spans="1:10" ht="27.6" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A219" s="11" t="s">
         <v>443</v>
       </c>
@@ -10975,7 +10975,7 @@
         <v>0.25</v>
       </c>
       <c r="G219" s="12" t="s">
-        <v>54</v>
+        <v>76</v>
       </c>
       <c r="H219" s="11" t="s">
         <v>43</v>
@@ -10983,7 +10983,7 @@
       <c r="I219" s="11"/>
       <c r="J219" s="12"/>
     </row>
-    <row r="220" spans="1:10" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="220" spans="1:10" ht="27.6" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A220" s="11" t="s">
         <v>444</v>
       </c>
@@ -11011,7 +11011,7 @@
       <c r="I220" s="11"/>
       <c r="J220" s="12"/>
     </row>
-    <row r="221" spans="1:10" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="221" spans="1:10" ht="27.6" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A221" s="11" t="s">
         <v>445</v>
       </c>
@@ -11115,7 +11115,7 @@
         <v>0.25</v>
       </c>
       <c r="G224" s="12" t="s">
-        <v>54</v>
+        <v>76</v>
       </c>
       <c r="H224" s="11" t="s">
         <v>43</v>
@@ -11199,7 +11199,7 @@
         <v>0.25</v>
       </c>
       <c r="G227" s="12" t="s">
-        <v>54</v>
+        <v>76</v>
       </c>
       <c r="H227" s="11" t="s">
         <v>43</v>
@@ -11255,7 +11255,7 @@
         <v>0.25</v>
       </c>
       <c r="G229" s="12" t="s">
-        <v>54</v>
+        <v>76</v>
       </c>
       <c r="H229" s="11" t="s">
         <v>43</v>
@@ -11319,7 +11319,7 @@
       <c r="I231" s="11"/>
       <c r="J231" s="12"/>
     </row>
-    <row r="232" spans="1:10" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="232" spans="1:10" ht="27.6" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A232" s="11" t="s">
         <v>466</v>
       </c>
@@ -11347,7 +11347,7 @@
       <c r="I232" s="11"/>
       <c r="J232" s="12"/>
     </row>
-    <row r="233" spans="1:10" ht="41.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="233" spans="1:10" ht="41.4" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A233" s="11" t="s">
         <v>467</v>
       </c>
@@ -11375,7 +11375,7 @@
       <c r="I233" s="11"/>
       <c r="J233" s="12"/>
     </row>
-    <row r="234" spans="1:10" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="234" spans="1:10" ht="27.6" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A234" s="11" t="s">
         <v>468</v>
       </c>
@@ -11403,7 +11403,7 @@
       <c r="I234" s="11"/>
       <c r="J234" s="12"/>
     </row>
-    <row r="235" spans="1:10" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="235" spans="1:10" ht="27.6" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A235" s="11" t="s">
         <v>472</v>
       </c>
@@ -11431,7 +11431,7 @@
       <c r="I235" s="11"/>
       <c r="J235" s="12"/>
     </row>
-    <row r="236" spans="1:10" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="236" spans="1:10" ht="27.6" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A236" s="11" t="s">
         <v>474</v>
       </c>
@@ -11451,7 +11451,7 @@
         <v>0.5</v>
       </c>
       <c r="G236" s="12" t="s">
-        <v>54</v>
+        <v>76</v>
       </c>
       <c r="H236" s="11" t="s">
         <v>43</v>
@@ -11459,7 +11459,7 @@
       <c r="I236" s="11"/>
       <c r="J236" s="12"/>
     </row>
-    <row r="237" spans="1:10" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="237" spans="1:10" ht="27.6" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A237" s="11" t="s">
         <v>476</v>
       </c>
@@ -11487,7 +11487,7 @@
       <c r="I237" s="11"/>
       <c r="J237" s="12"/>
     </row>
-    <row r="238" spans="1:10" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="238" spans="1:10" ht="27.6" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A238" s="11" t="s">
         <v>478</v>
       </c>
@@ -11515,7 +11515,7 @@
       <c r="I238" s="11"/>
       <c r="J238" s="12"/>
     </row>
-    <row r="239" spans="1:10" ht="55.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="239" spans="1:10" ht="55.2" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A239" s="11" t="s">
         <v>480</v>
       </c>
@@ -11535,7 +11535,7 @@
         <v>0.25</v>
       </c>
       <c r="G239" s="12" t="s">
-        <v>54</v>
+        <v>76</v>
       </c>
       <c r="H239" s="11" t="s">
         <v>43</v>
@@ -11543,7 +11543,7 @@
       <c r="I239" s="11"/>
       <c r="J239" s="12"/>
     </row>
-    <row r="240" spans="1:10" ht="41.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="240" spans="1:10" ht="41.4" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A240" s="11" t="s">
         <v>482</v>
       </c>
@@ -11563,7 +11563,7 @@
         <v>0.5</v>
       </c>
       <c r="G240" s="12" t="s">
-        <v>54</v>
+        <v>76</v>
       </c>
       <c r="H240" s="11" t="s">
         <v>43</v>
@@ -11571,7 +11571,7 @@
       <c r="I240" s="11"/>
       <c r="J240" s="12"/>
     </row>
-    <row r="241" spans="1:10" ht="41.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="241" spans="1:10" ht="41.4" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A241" s="11" t="s">
         <v>484</v>
       </c>
@@ -11599,7 +11599,7 @@
       <c r="I241" s="11"/>
       <c r="J241" s="12"/>
     </row>
-    <row r="242" spans="1:10" ht="41.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="242" spans="1:10" ht="41.4" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A242" s="11" t="s">
         <v>486</v>
       </c>
@@ -11619,7 +11619,7 @@
         <v>0.5</v>
       </c>
       <c r="G242" s="12" t="s">
-        <v>54</v>
+        <v>76</v>
       </c>
       <c r="H242" s="11" t="s">
         <v>43</v>
@@ -11627,7 +11627,7 @@
       <c r="I242" s="11"/>
       <c r="J242" s="12"/>
     </row>
-    <row r="243" spans="1:10" ht="41.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="243" spans="1:10" ht="41.4" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A243" s="11" t="s">
         <v>487</v>
       </c>
@@ -11647,7 +11647,7 @@
         <v>0.5</v>
       </c>
       <c r="G243" s="12" t="s">
-        <v>54</v>
+        <v>76</v>
       </c>
       <c r="H243" s="11" t="s">
         <v>43</v>
@@ -11655,7 +11655,7 @@
       <c r="I243" s="11"/>
       <c r="J243" s="12"/>
     </row>
-    <row r="244" spans="1:10" ht="41.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="244" spans="1:10" ht="41.4" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A244" s="11" t="s">
         <v>488</v>
       </c>
@@ -11683,7 +11683,7 @@
       <c r="I244" s="11"/>
       <c r="J244" s="12"/>
     </row>
-    <row r="245" spans="1:10" ht="41.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="245" spans="1:10" ht="41.4" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A245" s="11" t="s">
         <v>489</v>
       </c>
@@ -11787,7 +11787,7 @@
         <v>0.5</v>
       </c>
       <c r="G248" s="12" t="s">
-        <v>54</v>
+        <v>76</v>
       </c>
       <c r="H248" s="11" t="s">
         <v>43</v>
@@ -11871,7 +11871,7 @@
         <v>0.25</v>
       </c>
       <c r="G251" s="12" t="s">
-        <v>54</v>
+        <v>76</v>
       </c>
       <c r="H251" s="11" t="s">
         <v>43</v>
@@ -11927,7 +11927,7 @@
         <v>0.5</v>
       </c>
       <c r="G253" s="12" t="s">
-        <v>54</v>
+        <v>76</v>
       </c>
       <c r="H253" s="11" t="s">
         <v>43</v>
@@ -11991,7 +11991,7 @@
       <c r="I255" s="11"/>
       <c r="J255" s="12"/>
     </row>
-    <row r="256" spans="1:10" ht="41.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="256" spans="1:10" ht="41.4" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A256" s="11" t="s">
         <v>510</v>
       </c>
@@ -12019,7 +12019,7 @@
       <c r="I256" s="11"/>
       <c r="J256" s="12"/>
     </row>
-    <row r="257" spans="1:10" ht="41.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="257" spans="1:10" ht="41.4" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A257" s="11" t="s">
         <v>511</v>
       </c>
@@ -12104,7 +12104,33 @@
     <row r="314" ht="41.4" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="315" ht="41.4" customHeight="1" x14ac:dyDescent="0.3"/>
   </sheetData>
-  <autoFilter ref="A5:J141" xr:uid="{00000000-0009-0000-0000-000002000000}"/>
+  <autoFilter ref="A5:J257" xr:uid="{00000000-0009-0000-0000-000002000000}">
+    <filterColumn colId="2">
+      <filters>
+        <filter val="Administrar modelos de activo"/>
+        <filter val="Administrar tipos de activo"/>
+        <filter val="Cambiar el estado de un activo indicando el motivo"/>
+        <filter val="Configurar el medidor de un activo"/>
+        <filter val="Consultar la ficha y el historial de un activo"/>
+        <filter val="Definir los atributos técnicos de un tipo de activo"/>
+        <filter val="Registrar los componentes de un activo"/>
+        <filter val="Registrar un activo"/>
+      </filters>
+    </filterColumn>
+    <filterColumn colId="4">
+      <filters>
+        <filter val="API"/>
+        <filter val="Base de datos"/>
+        <filter val="Seguridad"/>
+        <filter val="Web"/>
+      </filters>
+    </filterColumn>
+    <filterColumn colId="7">
+      <filters>
+        <filter val="Por hacer"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <mergeCells count="2">
     <mergeCell ref="A1:J1"/>
     <mergeCell ref="A2:J2"/>
@@ -12340,10 +12366,10 @@
     </row>
     <row r="13" spans="1:6" ht="39" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="13" t="s">
+        <v>73</v>
+      </c>
+      <c r="B13" s="14" t="s">
         <v>74</v>
-      </c>
-      <c r="B13" s="14" t="s">
-        <v>75</v>
       </c>
       <c r="C13" s="13">
         <v>1</v>
@@ -12360,10 +12386,10 @@
     </row>
     <row r="14" spans="1:6" ht="39" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="11" t="s">
+        <v>73</v>
+      </c>
+      <c r="B14" s="12" t="s">
         <v>74</v>
-      </c>
-      <c r="B14" s="12" t="s">
-        <v>75</v>
       </c>
       <c r="C14" s="11">
         <v>2</v>
@@ -12380,10 +12406,10 @@
     </row>
     <row r="15" spans="1:6" ht="39" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="13" t="s">
+        <v>73</v>
+      </c>
+      <c r="B15" s="14" t="s">
         <v>74</v>
-      </c>
-      <c r="B15" s="14" t="s">
-        <v>75</v>
       </c>
       <c r="C15" s="13">
         <v>3</v>

--- a/Fase 2/Sprint Backlogs/SIGMA_Sprint_Backlog_S2.xlsx
+++ b/Fase 2/Sprint Backlogs/SIGMA_Sprint_Backlog_S2.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Capstone\Fase 2\Sprint Backlogs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B0BFA16B-7389-42CC-8487-355E941CF3B0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5D82FA00-82BF-44CD-BD23-98FE975E5623}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="15504" yWindow="3432" windowWidth="7536" windowHeight="9072" tabRatio="500" firstSheet="2" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12720" tabRatio="500" firstSheet="2" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sprint" sheetId="1" r:id="rId1"/>
@@ -1264,6 +1264,9 @@
     <t>T-2235</t>
   </si>
   <si>
+    <t>En curso</t>
+  </si>
+  <si>
     <t>T-2236</t>
   </si>
   <si>
@@ -1754,9 +1757,6 @@
   </si>
   <si>
     <t>HU-033, HU-032</t>
-  </si>
-  <si>
-    <t>En curso</t>
   </si>
   <si>
     <t>registrar el horómetro o contador de un equipo</t>
@@ -3169,27 +3169,27 @@
   <sheetData>
     <row r="6" spans="2:8" ht="22.05" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B6" s="1" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
     </row>
     <row r="7" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B7" s="2" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
     </row>
     <row r="8" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B8" s="3" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
     </row>
     <row r="10" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B10" s="4" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
     </row>
     <row r="11" spans="2:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B11" s="23" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="C11" s="24"/>
       <c r="D11" s="24"/>
@@ -3218,15 +3218,15 @@
     </row>
     <row r="15" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B15" s="4" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
     </row>
     <row r="16" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B16" s="5" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="C16" s="21" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="D16" s="19"/>
       <c r="E16" s="19"/>
@@ -3236,10 +3236,10 @@
     </row>
     <row r="17" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B17" s="5" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="C17" s="21" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="D17" s="19"/>
       <c r="E17" s="19"/>
@@ -3249,10 +3249,10 @@
     </row>
     <row r="18" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B18" s="5" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="C18" s="21" t="s">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="D18" s="19"/>
       <c r="E18" s="19"/>
@@ -3262,10 +3262,10 @@
     </row>
     <row r="19" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B19" s="5" t="s">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="C19" s="21" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="D19" s="19"/>
       <c r="E19" s="19"/>
@@ -3275,7 +3275,7 @@
     </row>
     <row r="20" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B20" s="5" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="C20" s="21" t="s">
         <v>42</v>
@@ -3288,7 +3288,7 @@
     </row>
     <row r="21" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B21" s="5" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="C21" s="21" t="s">
         <v>17</v>
@@ -3301,7 +3301,7 @@
     </row>
     <row r="22" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B22" s="5" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="C22" s="21" t="s">
         <v>76</v>
@@ -3314,10 +3314,10 @@
     </row>
     <row r="23" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B23" s="5" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="C23" s="21" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="D23" s="19"/>
       <c r="E23" s="19"/>
@@ -3327,12 +3327,12 @@
     </row>
     <row r="25" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B25" s="4" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
     </row>
     <row r="26" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B26" s="5" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="C26" s="6">
         <v>3</v>
@@ -3340,7 +3340,7 @@
     </row>
     <row r="27" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B27" s="5" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="C27" s="6">
         <v>40</v>
@@ -3348,7 +3348,7 @@
     </row>
     <row r="28" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B28" s="5" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="C28" s="6">
         <v>2</v>
@@ -3356,7 +3356,7 @@
     </row>
     <row r="29" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B29" s="5" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="C29" s="7">
         <f>$C$26*$C$27*$C$28</f>
@@ -3365,7 +3365,7 @@
     </row>
     <row r="30" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B30" s="5" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="C30" s="7">
         <f>COUNTA(Historias!$A$6:$A$27)</f>
@@ -3374,7 +3374,7 @@
     </row>
     <row r="31" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B31" s="5" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="C31" s="7">
         <f>SUM(Historias!$H$6:$H$27)</f>
@@ -3383,7 +3383,7 @@
     </row>
     <row r="32" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B32" s="5" t="s">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="C32" s="8">
         <f>SUM(Tareas!$F$6:$F$257)</f>
@@ -3392,7 +3392,7 @@
     </row>
     <row r="33" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B33" s="5" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="C33" s="9">
         <f>IFERROR($C$32/$C$29,0)</f>
@@ -3401,7 +3401,7 @@
     </row>
     <row r="34" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B34" s="5" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="C34" s="8">
         <f>$C$29-$C$32</f>
@@ -3410,29 +3410,29 @@
     </row>
     <row r="36" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B36" s="4" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
     </row>
     <row r="37" spans="2:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B37" s="10" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="C37" s="10" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="D37" s="10" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="E37" s="10" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
     </row>
     <row r="38" spans="2:8" ht="23.85" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B38" s="11" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="C38" s="12" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="D38" s="11">
         <f>COUNTIF(Historias!$B$6:$B$27,$B38)</f>
@@ -3445,10 +3445,10 @@
     </row>
     <row r="39" spans="2:8" ht="23.85" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B39" s="13" t="s">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="C39" s="14" t="s">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="D39" s="13">
         <f>COUNTIF(Historias!$B$6:$B$27,$B39)</f>
@@ -3461,10 +3461,10 @@
     </row>
     <row r="40" spans="2:8" ht="23.85" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B40" s="11" t="s">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="C40" s="12" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="D40" s="11">
         <f>COUNTIF(Historias!$B$6:$B$27,$B40)</f>
@@ -3477,10 +3477,10 @@
     </row>
     <row r="41" spans="2:8" ht="23.85" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B41" s="13" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="C41" s="14" t="s">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="D41" s="13">
         <f>COUNTIF(Historias!$B$6:$B$27,$B41)</f>
@@ -3493,7 +3493,7 @@
     </row>
     <row r="43" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B43" s="22" t="s">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="C43" s="19"/>
       <c r="D43" s="19"/>
@@ -3514,10 +3514,10 @@
   </sheetData>
   <mergeCells count="10">
     <mergeCell ref="B11:H13"/>
+    <mergeCell ref="C20:H20"/>
+    <mergeCell ref="C19:H19"/>
+    <mergeCell ref="C16:H16"/>
     <mergeCell ref="C21:H21"/>
-    <mergeCell ref="C20:H20"/>
-    <mergeCell ref="C16:H16"/>
-    <mergeCell ref="C19:H19"/>
     <mergeCell ref="C22:H22"/>
     <mergeCell ref="B43:H44"/>
     <mergeCell ref="C23:H23"/>
@@ -3563,7 +3563,7 @@
   <sheetData>
     <row r="1" spans="1:16" ht="24" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A1" s="18" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="B1" s="19"/>
       <c r="C1" s="19"/>
@@ -3583,7 +3583,7 @@
     </row>
     <row r="2" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="20" t="s">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="B2" s="19"/>
       <c r="C2" s="19"/>
@@ -3603,43 +3603,43 @@
     </row>
     <row r="5" spans="1:16" ht="27.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="10" t="s">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="B5" s="10" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="C5" s="10" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="D5" s="10" t="s">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="E5" s="10" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="F5" s="10" t="s">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="G5" s="10" t="s">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="H5" s="10" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="I5" s="10" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="J5" s="10" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="K5" s="10" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="L5" s="10" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="M5" s="10" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="N5" s="10" t="s">
         <v>9</v>
@@ -3656,19 +3656,19 @@
         <v>13</v>
       </c>
       <c r="B6" s="11" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="C6" s="12" t="s">
         <v>14</v>
       </c>
       <c r="D6" s="12" t="s">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="E6" s="12" t="s">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="F6" s="12" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="G6" s="11" t="s">
         <v>31</v>
@@ -3680,10 +3680,10 @@
         <v>100</v>
       </c>
       <c r="J6" s="11" t="s">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="K6" s="12" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="L6" s="11">
         <v>4</v>
@@ -3693,7 +3693,7 @@
         <v>9.25</v>
       </c>
       <c r="N6" s="11" t="s">
-        <v>574</v>
+        <v>410</v>
       </c>
       <c r="O6" s="12"/>
       <c r="P6" s="12"/>
@@ -3703,13 +3703,13 @@
         <v>51</v>
       </c>
       <c r="B7" s="13" t="s">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="C7" s="14" t="s">
         <v>52</v>
       </c>
       <c r="D7" s="14" t="s">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="E7" s="14" t="s">
         <v>575</v>
@@ -3727,7 +3727,7 @@
         <v>95</v>
       </c>
       <c r="J7" s="13" t="s">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="K7" s="14" t="s">
         <v>13</v>
@@ -3750,7 +3750,7 @@
         <v>73</v>
       </c>
       <c r="B8" s="11" t="s">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="C8" s="12" t="s">
         <v>74</v>
@@ -3774,7 +3774,7 @@
         <v>95</v>
       </c>
       <c r="J8" s="11" t="s">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="K8" s="12" t="s">
         <v>13</v>
@@ -3797,7 +3797,7 @@
         <v>102</v>
       </c>
       <c r="B9" s="13" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="C9" s="14" t="s">
         <v>103</v>
@@ -3821,7 +3821,7 @@
         <v>90</v>
       </c>
       <c r="J9" s="13" t="s">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="K9" s="14" t="s">
         <v>13</v>
@@ -3844,7 +3844,7 @@
         <v>121</v>
       </c>
       <c r="B10" s="11" t="s">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="C10" s="12" t="s">
         <v>122</v>
@@ -3868,7 +3868,7 @@
         <v>90</v>
       </c>
       <c r="J10" s="11" t="s">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="K10" s="12" t="s">
         <v>51</v>
@@ -3893,7 +3893,7 @@
         <v>143</v>
       </c>
       <c r="B11" s="13" t="s">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="C11" s="14" t="s">
         <v>144</v>
@@ -3917,7 +3917,7 @@
         <v>90</v>
       </c>
       <c r="J11" s="13" t="s">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="K11" s="14" t="s">
         <v>590</v>
@@ -3940,13 +3940,13 @@
         <v>165</v>
       </c>
       <c r="B12" s="11" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="C12" s="12" t="s">
         <v>166</v>
       </c>
       <c r="D12" s="12" t="s">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="E12" s="12" t="s">
         <v>591</v>
@@ -3964,7 +3964,7 @@
         <v>85</v>
       </c>
       <c r="J12" s="11" t="s">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="K12" s="12" t="s">
         <v>593</v>
@@ -3987,13 +3987,13 @@
         <v>185</v>
       </c>
       <c r="B13" s="13" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="C13" s="14" t="s">
         <v>186</v>
       </c>
       <c r="D13" s="14" t="s">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="E13" s="14" t="s">
         <v>594</v>
@@ -4034,7 +4034,7 @@
         <v>207</v>
       </c>
       <c r="B14" s="11" t="s">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="C14" s="12" t="s">
         <v>208</v>
@@ -4061,7 +4061,7 @@
         <v>596</v>
       </c>
       <c r="K14" s="12" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="L14" s="11">
         <v>2</v>
@@ -4083,7 +4083,7 @@
         <v>228</v>
       </c>
       <c r="B15" s="13" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="C15" s="14" t="s">
         <v>229</v>
@@ -4134,7 +4134,7 @@
         <v>259</v>
       </c>
       <c r="B16" s="11" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="C16" s="12" t="s">
         <v>260</v>
@@ -4181,7 +4181,7 @@
         <v>279</v>
       </c>
       <c r="B17" s="13" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="C17" s="14" t="s">
         <v>280</v>
@@ -4232,13 +4232,13 @@
         <v>304</v>
       </c>
       <c r="B18" s="11" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="C18" s="12" t="s">
         <v>305</v>
       </c>
       <c r="D18" s="12" t="s">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="E18" s="12" t="s">
         <v>610</v>
@@ -4279,7 +4279,7 @@
         <v>318</v>
       </c>
       <c r="B19" s="13" t="s">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="C19" s="14" t="s">
         <v>319</v>
@@ -4326,7 +4326,7 @@
         <v>331</v>
       </c>
       <c r="B20" s="11" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="C20" s="12" t="s">
         <v>332</v>
@@ -4377,7 +4377,7 @@
         <v>363</v>
       </c>
       <c r="B21" s="13" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="C21" s="14" t="s">
         <v>364</v>
@@ -4414,7 +4414,7 @@
         <v>5.75</v>
       </c>
       <c r="N21" s="13" t="s">
-        <v>574</v>
+        <v>410</v>
       </c>
       <c r="O21" s="14" t="s">
         <v>76</v>
@@ -4428,13 +4428,13 @@
         <v>390</v>
       </c>
       <c r="B22" s="11" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="C22" s="12" t="s">
         <v>391</v>
       </c>
       <c r="D22" s="12" t="s">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="E22" s="12" t="s">
         <v>623</v>
@@ -4472,16 +4472,16 @@
     </row>
     <row r="23" spans="1:16" ht="96.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="13" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="B23" s="13" t="s">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="C23" s="14" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="D23" s="14" t="s">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="E23" s="14" t="s">
         <v>625</v>
@@ -4502,7 +4502,7 @@
         <v>596</v>
       </c>
       <c r="K23" s="14" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="L23" s="13">
         <v>2</v>
@@ -4519,13 +4519,13 @@
     </row>
     <row r="24" spans="1:16" ht="69" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="11" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="B24" s="11" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="C24" s="12" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="D24" s="12" t="s">
         <v>619</v>
@@ -4566,16 +4566,16 @@
     </row>
     <row r="25" spans="1:16" ht="55.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="13" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="B25" s="13" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="C25" s="14" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="D25" s="14" t="s">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="E25" s="14" t="s">
         <v>629</v>
@@ -4613,13 +4613,13 @@
     </row>
     <row r="26" spans="1:16" ht="82.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="11" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="B26" s="11" t="s">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="C26" s="12" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="D26" s="12" t="s">
         <v>619</v>
@@ -4660,16 +4660,16 @@
     </row>
     <row r="27" spans="1:16" ht="82.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="13" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="B27" s="13" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="C27" s="14" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="D27" s="14" t="s">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="E27" s="14" t="s">
         <v>634</v>
@@ -10163,10 +10163,10 @@
         <v>0.5</v>
       </c>
       <c r="G190" s="12" t="s">
-        <v>76</v>
+        <v>17</v>
       </c>
       <c r="H190" s="11" t="s">
-        <v>43</v>
+        <v>18</v>
       </c>
       <c r="I190" s="11"/>
       <c r="J190" s="12"/>
@@ -10194,7 +10194,7 @@
         <v>17</v>
       </c>
       <c r="H191" s="11" t="s">
-        <v>43</v>
+        <v>18</v>
       </c>
       <c r="I191" s="11"/>
       <c r="J191" s="12"/>
@@ -10219,10 +10219,10 @@
         <v>0.5</v>
       </c>
       <c r="G192" s="12" t="s">
-        <v>42</v>
+        <v>17</v>
       </c>
       <c r="H192" s="11" t="s">
-        <v>43</v>
+        <v>18</v>
       </c>
       <c r="I192" s="11"/>
       <c r="J192" s="12"/>
@@ -10247,10 +10247,10 @@
         <v>0.5</v>
       </c>
       <c r="G193" s="12" t="s">
-        <v>76</v>
+        <v>17</v>
       </c>
       <c r="H193" s="11" t="s">
-        <v>43</v>
+        <v>18</v>
       </c>
       <c r="I193" s="11"/>
       <c r="J193" s="12"/>
@@ -10278,7 +10278,7 @@
         <v>17</v>
       </c>
       <c r="H194" s="11" t="s">
-        <v>43</v>
+        <v>18</v>
       </c>
       <c r="I194" s="11"/>
       <c r="J194" s="12"/>
@@ -10303,10 +10303,10 @@
         <v>0.25</v>
       </c>
       <c r="G195" s="12" t="s">
-        <v>42</v>
+        <v>17</v>
       </c>
       <c r="H195" s="11" t="s">
-        <v>43</v>
+        <v>18</v>
       </c>
       <c r="I195" s="11"/>
       <c r="J195" s="12"/>
@@ -10331,10 +10331,10 @@
         <v>0.5</v>
       </c>
       <c r="G196" s="12" t="s">
-        <v>76</v>
+        <v>17</v>
       </c>
       <c r="H196" s="11" t="s">
-        <v>43</v>
+        <v>18</v>
       </c>
       <c r="I196" s="11"/>
       <c r="J196" s="12"/>
@@ -10362,7 +10362,7 @@
         <v>17</v>
       </c>
       <c r="H197" s="11" t="s">
-        <v>43</v>
+        <v>18</v>
       </c>
       <c r="I197" s="11"/>
       <c r="J197" s="12"/>
@@ -10387,10 +10387,10 @@
         <v>0.5</v>
       </c>
       <c r="G198" s="12" t="s">
-        <v>76</v>
+        <v>17</v>
       </c>
       <c r="H198" s="11" t="s">
-        <v>43</v>
+        <v>18</v>
       </c>
       <c r="I198" s="11"/>
       <c r="J198" s="12"/>
@@ -10415,10 +10415,10 @@
         <v>0.5</v>
       </c>
       <c r="G199" s="12" t="s">
-        <v>76</v>
+        <v>17</v>
       </c>
       <c r="H199" s="11" t="s">
-        <v>43</v>
+        <v>18</v>
       </c>
       <c r="I199" s="11"/>
       <c r="J199" s="12"/>
@@ -10443,17 +10443,17 @@
         <v>0.5</v>
       </c>
       <c r="G200" s="12" t="s">
-        <v>42</v>
+        <v>17</v>
       </c>
       <c r="H200" s="11" t="s">
-        <v>43</v>
+        <v>410</v>
       </c>
       <c r="I200" s="11"/>
       <c r="J200" s="12"/>
     </row>
     <row r="201" spans="1:10" ht="41.4" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A201" s="11" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="B201" s="11" t="s">
         <v>390</v>
@@ -10471,26 +10471,26 @@
         <v>0.25</v>
       </c>
       <c r="G201" s="12" t="s">
-        <v>42</v>
+        <v>17</v>
       </c>
       <c r="H201" s="11" t="s">
-        <v>43</v>
+        <v>18</v>
       </c>
       <c r="I201" s="11"/>
       <c r="J201" s="12"/>
     </row>
     <row r="202" spans="1:10" ht="27.6" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A202" s="11" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="B202" s="11" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="C202" s="12" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="D202" s="17" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="E202" s="11" t="s">
         <v>16</v>
@@ -10509,16 +10509,16 @@
     </row>
     <row r="203" spans="1:10" ht="27.6" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A203" s="11" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="B203" s="11" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="C203" s="12" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="D203" s="17" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="E203" s="11" t="s">
         <v>16</v>
@@ -10537,16 +10537,16 @@
     </row>
     <row r="204" spans="1:10" ht="41.4" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A204" s="11" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="B204" s="11" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="C204" s="12" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="D204" s="17" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="E204" s="11" t="s">
         <v>16</v>
@@ -10565,16 +10565,16 @@
     </row>
     <row r="205" spans="1:10" ht="27.6" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A205" s="11" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="B205" s="11" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="C205" s="12" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="D205" s="17" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="E205" s="11" t="s">
         <v>16</v>
@@ -10593,16 +10593,16 @@
     </row>
     <row r="206" spans="1:10" ht="27.6" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A206" s="11" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="B206" s="11" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="C206" s="12" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="D206" s="17" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="E206" s="11" t="s">
         <v>16</v>
@@ -10621,16 +10621,16 @@
     </row>
     <row r="207" spans="1:10" ht="27.6" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A207" s="11" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="B207" s="11" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="C207" s="12" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="D207" s="17" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="E207" s="11" t="s">
         <v>16</v>
@@ -10649,16 +10649,16 @@
     </row>
     <row r="208" spans="1:10" ht="27.6" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A208" s="11" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="B208" s="11" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="C208" s="12" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="D208" s="17" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="E208" s="11" t="s">
         <v>31</v>
@@ -10677,16 +10677,16 @@
     </row>
     <row r="209" spans="1:10" ht="27.6" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A209" s="11" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="B209" s="11" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="C209" s="12" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="D209" s="17" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="E209" s="11" t="s">
         <v>31</v>
@@ -10705,13 +10705,13 @@
     </row>
     <row r="210" spans="1:10" ht="55.2" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A210" s="11" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="B210" s="11" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="C210" s="12" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="D210" s="17" t="s">
         <v>35</v>
@@ -10733,13 +10733,13 @@
     </row>
     <row r="211" spans="1:10" ht="41.4" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A211" s="11" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="B211" s="11" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="C211" s="12" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="D211" s="17" t="s">
         <v>37</v>
@@ -10761,13 +10761,13 @@
     </row>
     <row r="212" spans="1:10" ht="41.4" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A212" s="11" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="B212" s="11" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="C212" s="12" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="D212" s="17" t="s">
         <v>40</v>
@@ -10789,13 +10789,13 @@
     </row>
     <row r="213" spans="1:10" ht="41.4" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A213" s="11" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="B213" s="11" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="C213" s="12" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="D213" s="17" t="s">
         <v>45</v>
@@ -10817,13 +10817,13 @@
     </row>
     <row r="214" spans="1:10" ht="41.4" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A214" s="11" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="B214" s="11" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="C214" s="12" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="D214" s="17" t="s">
         <v>230</v>
@@ -10845,16 +10845,16 @@
     </row>
     <row r="215" spans="1:10" ht="27.6" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A215" s="11" t="s">
+        <v>437</v>
+      </c>
+      <c r="B215" s="11" t="s">
+        <v>435</v>
+      </c>
+      <c r="C215" s="12" t="s">
         <v>436</v>
       </c>
-      <c r="B215" s="11" t="s">
-        <v>434</v>
-      </c>
-      <c r="C215" s="12" t="s">
-        <v>435</v>
-      </c>
       <c r="D215" s="17" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="E215" s="11" t="s">
         <v>16</v>
@@ -10873,16 +10873,16 @@
     </row>
     <row r="216" spans="1:10" ht="27.6" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A216" s="11" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="B216" s="11" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="C216" s="12" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="D216" s="17" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="E216" s="11" t="s">
         <v>16</v>
@@ -10901,13 +10901,13 @@
     </row>
     <row r="217" spans="1:10" ht="27.6" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A217" s="11" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="B217" s="11" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="C217" s="12" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="D217" s="17" t="s">
         <v>242</v>
@@ -10929,16 +10929,16 @@
     </row>
     <row r="218" spans="1:10" ht="41.4" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A218" s="11" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="B218" s="11" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="C218" s="12" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="D218" s="17" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="E218" s="11" t="s">
         <v>31</v>
@@ -10957,13 +10957,13 @@
     </row>
     <row r="219" spans="1:10" ht="27.6" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A219" s="11" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="B219" s="11" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="C219" s="12" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="D219" s="17" t="s">
         <v>37</v>
@@ -10985,13 +10985,13 @@
     </row>
     <row r="220" spans="1:10" ht="27.6" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A220" s="11" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="B220" s="11" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="C220" s="12" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="D220" s="17" t="s">
         <v>40</v>
@@ -11013,13 +11013,13 @@
     </row>
     <row r="221" spans="1:10" ht="27.6" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A221" s="11" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="B221" s="11" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="C221" s="12" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="D221" s="17" t="s">
         <v>45</v>
@@ -11041,16 +11041,16 @@
     </row>
     <row r="222" spans="1:10" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A222" s="11" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="B222" s="11" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="C222" s="12" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="D222" s="17" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="E222" s="11" t="s">
         <v>16</v>
@@ -11069,16 +11069,16 @@
     </row>
     <row r="223" spans="1:10" ht="55.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A223" s="11" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="B223" s="11" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="C223" s="12" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="D223" s="17" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="E223" s="11" t="s">
         <v>16</v>
@@ -11097,16 +11097,16 @@
     </row>
     <row r="224" spans="1:10" ht="41.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A224" s="11" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="B224" s="11" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="C224" s="12" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="D224" s="17" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="E224" s="11" t="s">
         <v>16</v>
@@ -11125,16 +11125,16 @@
     </row>
     <row r="225" spans="1:10" ht="41.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A225" s="11" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="B225" s="11" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="C225" s="12" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="D225" s="17" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="E225" s="11" t="s">
         <v>16</v>
@@ -11153,16 +11153,16 @@
     </row>
     <row r="226" spans="1:10" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A226" s="11" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="B226" s="11" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="C226" s="12" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="D226" s="17" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="E226" s="11" t="s">
         <v>16</v>
@@ -11181,16 +11181,16 @@
     </row>
     <row r="227" spans="1:10" ht="41.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A227" s="11" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="B227" s="11" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="C227" s="12" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="D227" s="17" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="E227" s="11" t="s">
         <v>16</v>
@@ -11209,16 +11209,16 @@
     </row>
     <row r="228" spans="1:10" ht="41.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A228" s="11" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="B228" s="11" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="C228" s="12" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="D228" s="17" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="E228" s="11" t="s">
         <v>31</v>
@@ -11237,16 +11237,16 @@
     </row>
     <row r="229" spans="1:10" ht="41.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A229" s="11" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="B229" s="11" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="C229" s="12" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="D229" s="17" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="E229" s="11" t="s">
         <v>31</v>
@@ -11265,13 +11265,13 @@
     </row>
     <row r="230" spans="1:10" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A230" s="11" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="B230" s="11" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="C230" s="12" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="D230" s="17" t="s">
         <v>35</v>
@@ -11293,13 +11293,13 @@
     </row>
     <row r="231" spans="1:10" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A231" s="11" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="B231" s="11" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="C231" s="12" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="D231" s="17" t="s">
         <v>37</v>
@@ -11321,13 +11321,13 @@
     </row>
     <row r="232" spans="1:10" ht="27.6" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A232" s="11" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="B232" s="11" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="C232" s="12" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="D232" s="17" t="s">
         <v>40</v>
@@ -11349,13 +11349,13 @@
     </row>
     <row r="233" spans="1:10" ht="41.4" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A233" s="11" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="B233" s="11" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="C233" s="12" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="D233" s="17" t="s">
         <v>45</v>
@@ -11377,16 +11377,16 @@
     </row>
     <row r="234" spans="1:10" ht="27.6" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A234" s="11" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="B234" s="11" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="C234" s="12" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="D234" s="17" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="E234" s="11" t="s">
         <v>16</v>
@@ -11405,16 +11405,16 @@
     </row>
     <row r="235" spans="1:10" ht="27.6" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A235" s="11" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="B235" s="11" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="C235" s="12" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="D235" s="17" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="E235" s="11" t="s">
         <v>16</v>
@@ -11433,16 +11433,16 @@
     </row>
     <row r="236" spans="1:10" ht="27.6" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A236" s="11" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="B236" s="11" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="C236" s="12" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="D236" s="17" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="E236" s="11" t="s">
         <v>16</v>
@@ -11461,16 +11461,16 @@
     </row>
     <row r="237" spans="1:10" ht="27.6" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A237" s="11" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="B237" s="11" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="C237" s="12" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="D237" s="17" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="E237" s="11" t="s">
         <v>16</v>
@@ -11489,16 +11489,16 @@
     </row>
     <row r="238" spans="1:10" ht="27.6" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A238" s="11" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="B238" s="11" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="C238" s="12" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="D238" s="17" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="E238" s="11" t="s">
         <v>16</v>
@@ -11517,16 +11517,16 @@
     </row>
     <row r="239" spans="1:10" ht="55.2" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A239" s="11" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="B239" s="11" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="C239" s="12" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="D239" s="17" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="E239" s="11" t="s">
         <v>16</v>
@@ -11545,16 +11545,16 @@
     </row>
     <row r="240" spans="1:10" ht="41.4" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A240" s="11" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="B240" s="11" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="C240" s="12" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="D240" s="17" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="E240" s="11" t="s">
         <v>31</v>
@@ -11573,16 +11573,16 @@
     </row>
     <row r="241" spans="1:10" ht="41.4" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A241" s="11" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="B241" s="11" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="C241" s="12" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="D241" s="17" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="E241" s="11" t="s">
         <v>31</v>
@@ -11601,13 +11601,13 @@
     </row>
     <row r="242" spans="1:10" ht="41.4" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A242" s="11" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="B242" s="11" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="C242" s="12" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="D242" s="17" t="s">
         <v>35</v>
@@ -11629,13 +11629,13 @@
     </row>
     <row r="243" spans="1:10" ht="41.4" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A243" s="11" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="B243" s="11" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="C243" s="12" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="D243" s="17" t="s">
         <v>37</v>
@@ -11657,13 +11657,13 @@
     </row>
     <row r="244" spans="1:10" ht="41.4" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A244" s="11" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="B244" s="11" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="C244" s="12" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="D244" s="17" t="s">
         <v>40</v>
@@ -11685,13 +11685,13 @@
     </row>
     <row r="245" spans="1:10" ht="41.4" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A245" s="11" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="B245" s="11" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="C245" s="12" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="D245" s="17" t="s">
         <v>45</v>
@@ -11713,16 +11713,16 @@
     </row>
     <row r="246" spans="1:10" ht="41.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A246" s="11" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="B246" s="11" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="C246" s="12" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="D246" s="17" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="E246" s="11" t="s">
         <v>16</v>
@@ -11741,16 +11741,16 @@
     </row>
     <row r="247" spans="1:10" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A247" s="11" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="B247" s="11" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="C247" s="12" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="D247" s="17" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="E247" s="11" t="s">
         <v>16</v>
@@ -11769,16 +11769,16 @@
     </row>
     <row r="248" spans="1:10" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A248" s="11" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="B248" s="11" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="C248" s="12" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="D248" s="17" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="E248" s="11" t="s">
         <v>16</v>
@@ -11797,16 +11797,16 @@
     </row>
     <row r="249" spans="1:10" ht="41.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A249" s="11" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="B249" s="11" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="C249" s="12" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="D249" s="17" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="E249" s="11" t="s">
         <v>16</v>
@@ -11825,16 +11825,16 @@
     </row>
     <row r="250" spans="1:10" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A250" s="11" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="B250" s="11" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="C250" s="12" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="D250" s="17" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="E250" s="11" t="s">
         <v>16</v>
@@ -11853,16 +11853,16 @@
     </row>
     <row r="251" spans="1:10" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A251" s="11" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="B251" s="11" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="C251" s="12" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="D251" s="17" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="E251" s="11" t="s">
         <v>16</v>
@@ -11881,16 +11881,16 @@
     </row>
     <row r="252" spans="1:10" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A252" s="11" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="B252" s="11" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="C252" s="12" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="D252" s="17" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="E252" s="11" t="s">
         <v>31</v>
@@ -11909,16 +11909,16 @@
     </row>
     <row r="253" spans="1:10" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A253" s="11" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="B253" s="11" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="C253" s="12" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="D253" s="17" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="E253" s="11" t="s">
         <v>31</v>
@@ -11937,13 +11937,13 @@
     </row>
     <row r="254" spans="1:10" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A254" s="11" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="B254" s="11" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="C254" s="12" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="D254" s="17" t="s">
         <v>35</v>
@@ -11965,13 +11965,13 @@
     </row>
     <row r="255" spans="1:10" ht="55.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A255" s="11" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="B255" s="11" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="C255" s="12" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="D255" s="17" t="s">
         <v>37</v>
@@ -11993,13 +11993,13 @@
     </row>
     <row r="256" spans="1:10" ht="41.4" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A256" s="11" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="B256" s="11" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="C256" s="12" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="D256" s="17" t="s">
         <v>40</v>
@@ -12021,13 +12021,13 @@
     </row>
     <row r="257" spans="1:10" ht="41.4" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A257" s="11" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="B257" s="11" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="C257" s="12" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="D257" s="17" t="s">
         <v>45</v>
@@ -13166,10 +13166,10 @@
     </row>
     <row r="53" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A53" s="13" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="B53" s="14" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="C53" s="13">
         <v>1</v>
@@ -13186,10 +13186,10 @@
     </row>
     <row r="54" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A54" s="11" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="B54" s="12" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="C54" s="11">
         <v>2</v>
@@ -13206,10 +13206,10 @@
     </row>
     <row r="55" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A55" s="13" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="B55" s="14" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="C55" s="13">
         <v>1</v>
@@ -13226,10 +13226,10 @@
     </row>
     <row r="56" spans="1:6" ht="39" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A56" s="11" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="B56" s="12" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="C56" s="11">
         <v>2</v>
@@ -13246,10 +13246,10 @@
     </row>
     <row r="57" spans="1:6" ht="39" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A57" s="13" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="B57" s="14" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="C57" s="13">
         <v>1</v>
@@ -13266,10 +13266,10 @@
     </row>
     <row r="58" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A58" s="11" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="B58" s="12" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="C58" s="11">
         <v>1</v>
@@ -13286,10 +13286,10 @@
     </row>
     <row r="59" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A59" s="13" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="B59" s="14" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="C59" s="13">
         <v>2</v>
@@ -13306,10 +13306,10 @@
     </row>
     <row r="60" spans="1:6" ht="39" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A60" s="11" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="B60" s="12" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="C60" s="11">
         <v>1</v>
@@ -13326,10 +13326,10 @@
     </row>
     <row r="61" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A61" s="13" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="B61" s="14" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="C61" s="13">
         <v>2</v>

--- a/Fase 2/Sprint Backlogs/SIGMA_Sprint_Backlog_S2.xlsx
+++ b/Fase 2/Sprint Backlogs/SIGMA_Sprint_Backlog_S2.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Capstone\Fase 2\Sprint Backlogs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5D82FA00-82BF-44CD-BD23-98FE975E5623}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9B6CB4F6-39C1-456C-95C2-BD4E2A47C274}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12720" tabRatio="500" firstSheet="2" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="15504" yWindow="3432" windowWidth="7536" windowHeight="9072" tabRatio="500" firstSheet="2" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sprint" sheetId="1" r:id="rId1"/>
@@ -3514,10 +3514,10 @@
   </sheetData>
   <mergeCells count="10">
     <mergeCell ref="B11:H13"/>
+    <mergeCell ref="C21:H21"/>
     <mergeCell ref="C20:H20"/>
+    <mergeCell ref="C16:H16"/>
     <mergeCell ref="C19:H19"/>
-    <mergeCell ref="C16:H16"/>
-    <mergeCell ref="C21:H21"/>
     <mergeCell ref="C22:H22"/>
     <mergeCell ref="B43:H44"/>
     <mergeCell ref="C23:H23"/>
@@ -5217,7 +5217,7 @@
       <c r="I18" s="11"/>
       <c r="J18" s="12"/>
     </row>
-    <row r="19" spans="1:10" ht="55.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:10" ht="55.2" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="11" t="s">
         <v>50</v>
       </c>
@@ -5245,7 +5245,7 @@
       <c r="I19" s="11"/>
       <c r="J19" s="12"/>
     </row>
-    <row r="20" spans="1:10" ht="41.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:10" ht="41.4" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="11" t="s">
         <v>54</v>
       </c>
@@ -5273,7 +5273,7 @@
       <c r="I20" s="11"/>
       <c r="J20" s="12"/>
     </row>
-    <row r="21" spans="1:10" ht="41.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:10" ht="41.4" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="11" t="s">
         <v>56</v>
       </c>
@@ -5301,7 +5301,7 @@
       <c r="I21" s="11"/>
       <c r="J21" s="12"/>
     </row>
-    <row r="22" spans="1:10" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:10" ht="27.6" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="11" t="s">
         <v>58</v>
       </c>
@@ -5329,7 +5329,7 @@
       <c r="I22" s="11"/>
       <c r="J22" s="12"/>
     </row>
-    <row r="23" spans="1:10" ht="41.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:10" ht="41.4" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="11" t="s">
         <v>60</v>
       </c>
@@ -5357,7 +5357,7 @@
       <c r="I23" s="11"/>
       <c r="J23" s="12"/>
     </row>
-    <row r="24" spans="1:10" ht="41.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:10" ht="41.4" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="11" t="s">
         <v>62</v>
       </c>
@@ -5385,7 +5385,7 @@
       <c r="I24" s="11"/>
       <c r="J24" s="12"/>
     </row>
-    <row r="25" spans="1:10" ht="41.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:10" ht="41.4" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="11" t="s">
         <v>64</v>
       </c>
@@ -5413,7 +5413,7 @@
       <c r="I25" s="11"/>
       <c r="J25" s="12"/>
     </row>
-    <row r="26" spans="1:10" ht="41.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:10" ht="41.4" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="11" t="s">
         <v>66</v>
       </c>
@@ -5441,7 +5441,7 @@
       <c r="I26" s="11"/>
       <c r="J26" s="12"/>
     </row>
-    <row r="27" spans="1:10" ht="41.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:10" ht="41.4" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="11" t="s">
         <v>68</v>
       </c>
@@ -5469,7 +5469,7 @@
       <c r="I27" s="11"/>
       <c r="J27" s="12"/>
     </row>
-    <row r="28" spans="1:10" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:10" ht="27.6" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="11" t="s">
         <v>69</v>
       </c>
@@ -5968,7 +5968,7 @@
         <v>17</v>
       </c>
       <c r="H45" s="11" t="s">
-        <v>43</v>
+        <v>18</v>
       </c>
       <c r="I45" s="11"/>
       <c r="J45" s="12"/>
@@ -5993,10 +5993,10 @@
         <v>0.75</v>
       </c>
       <c r="G46" s="12" t="s">
-        <v>42</v>
+        <v>17</v>
       </c>
       <c r="H46" s="11" t="s">
-        <v>43</v>
+        <v>18</v>
       </c>
       <c r="I46" s="11"/>
       <c r="J46" s="12"/>
@@ -6021,10 +6021,10 @@
         <v>0.5</v>
       </c>
       <c r="G47" s="12" t="s">
-        <v>76</v>
+        <v>17</v>
       </c>
       <c r="H47" s="11" t="s">
-        <v>43</v>
+        <v>18</v>
       </c>
       <c r="I47" s="11"/>
       <c r="J47" s="12"/>
@@ -6052,7 +6052,7 @@
         <v>17</v>
       </c>
       <c r="H48" s="11" t="s">
-        <v>43</v>
+        <v>18</v>
       </c>
       <c r="I48" s="11"/>
       <c r="J48" s="12"/>
@@ -6080,7 +6080,7 @@
         <v>17</v>
       </c>
       <c r="H49" s="11" t="s">
-        <v>43</v>
+        <v>18</v>
       </c>
       <c r="I49" s="11"/>
       <c r="J49" s="12"/>
@@ -6105,10 +6105,10 @@
         <v>0.75</v>
       </c>
       <c r="G50" s="12" t="s">
-        <v>76</v>
+        <v>17</v>
       </c>
       <c r="H50" s="11" t="s">
-        <v>43</v>
+        <v>18</v>
       </c>
       <c r="I50" s="11"/>
       <c r="J50" s="12"/>
@@ -6136,7 +6136,7 @@
         <v>17</v>
       </c>
       <c r="H51" s="11" t="s">
-        <v>43</v>
+        <v>18</v>
       </c>
       <c r="I51" s="11"/>
       <c r="J51" s="12"/>
@@ -6192,7 +6192,7 @@
         <v>17</v>
       </c>
       <c r="H53" s="11" t="s">
-        <v>43</v>
+        <v>18</v>
       </c>
       <c r="I53" s="11"/>
       <c r="J53" s="12"/>
@@ -10143,7 +10143,7 @@
       <c r="I189" s="11"/>
       <c r="J189" s="12"/>
     </row>
-    <row r="190" spans="1:10" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="190" spans="1:10" ht="27.6" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A190" s="11" t="s">
         <v>389</v>
       </c>
@@ -10171,7 +10171,7 @@
       <c r="I190" s="11"/>
       <c r="J190" s="12"/>
     </row>
-    <row r="191" spans="1:10" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="191" spans="1:10" ht="27.6" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A191" s="11" t="s">
         <v>393</v>
       </c>
@@ -10199,7 +10199,7 @@
       <c r="I191" s="11"/>
       <c r="J191" s="12"/>
     </row>
-    <row r="192" spans="1:10" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="192" spans="1:10" ht="27.6" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A192" s="11" t="s">
         <v>395</v>
       </c>
@@ -10227,7 +10227,7 @@
       <c r="I192" s="11"/>
       <c r="J192" s="12"/>
     </row>
-    <row r="193" spans="1:10" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="193" spans="1:10" ht="27.6" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A193" s="11" t="s">
         <v>397</v>
       </c>
@@ -10255,7 +10255,7 @@
       <c r="I193" s="11"/>
       <c r="J193" s="12"/>
     </row>
-    <row r="194" spans="1:10" ht="55.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="194" spans="1:10" ht="55.2" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A194" s="11" t="s">
         <v>399</v>
       </c>
@@ -10283,7 +10283,7 @@
       <c r="I194" s="11"/>
       <c r="J194" s="12"/>
     </row>
-    <row r="195" spans="1:10" ht="41.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="195" spans="1:10" ht="41.4" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A195" s="11" t="s">
         <v>401</v>
       </c>
@@ -10311,7 +10311,7 @@
       <c r="I195" s="11"/>
       <c r="J195" s="12"/>
     </row>
-    <row r="196" spans="1:10" ht="41.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="196" spans="1:10" ht="41.4" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A196" s="11" t="s">
         <v>403</v>
       </c>
@@ -10339,7 +10339,7 @@
       <c r="I196" s="11"/>
       <c r="J196" s="12"/>
     </row>
-    <row r="197" spans="1:10" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="197" spans="1:10" ht="27.6" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A197" s="11" t="s">
         <v>405</v>
       </c>
@@ -10367,7 +10367,7 @@
       <c r="I197" s="11"/>
       <c r="J197" s="12"/>
     </row>
-    <row r="198" spans="1:10" ht="41.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="198" spans="1:10" ht="41.4" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A198" s="11" t="s">
         <v>407</v>
       </c>
@@ -10395,7 +10395,7 @@
       <c r="I198" s="11"/>
       <c r="J198" s="12"/>
     </row>
-    <row r="199" spans="1:10" ht="41.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="199" spans="1:10" ht="41.4" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A199" s="11" t="s">
         <v>408</v>
       </c>

--- a/Fase 2/Sprint Backlogs/SIGMA_Sprint_Backlog_S2.xlsx
+++ b/Fase 2/Sprint Backlogs/SIGMA_Sprint_Backlog_S2.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Capstone\Fase 2\Sprint Backlogs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9B6CB4F6-39C1-456C-95C2-BD4E2A47C274}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5CDDDEA6-7DD0-422B-A384-C0508F704AC0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="15504" yWindow="3432" windowWidth="7536" windowHeight="9072" tabRatio="500" firstSheet="2" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3514,10 +3514,10 @@
   </sheetData>
   <mergeCells count="10">
     <mergeCell ref="B11:H13"/>
+    <mergeCell ref="C20:H20"/>
+    <mergeCell ref="C19:H19"/>
+    <mergeCell ref="C16:H16"/>
     <mergeCell ref="C21:H21"/>
-    <mergeCell ref="C20:H20"/>
-    <mergeCell ref="C16:H16"/>
-    <mergeCell ref="C19:H19"/>
     <mergeCell ref="C22:H22"/>
     <mergeCell ref="B43:H44"/>
     <mergeCell ref="C23:H23"/>
@@ -11398,7 +11398,7 @@
         <v>17</v>
       </c>
       <c r="H234" s="11" t="s">
-        <v>43</v>
+        <v>18</v>
       </c>
       <c r="I234" s="11"/>
       <c r="J234" s="12"/>
@@ -11423,10 +11423,10 @@
         <v>0.5</v>
       </c>
       <c r="G235" s="12" t="s">
-        <v>42</v>
+        <v>17</v>
       </c>
       <c r="H235" s="11" t="s">
-        <v>43</v>
+        <v>18</v>
       </c>
       <c r="I235" s="11"/>
       <c r="J235" s="12"/>
@@ -11451,10 +11451,10 @@
         <v>0.5</v>
       </c>
       <c r="G236" s="12" t="s">
-        <v>76</v>
+        <v>17</v>
       </c>
       <c r="H236" s="11" t="s">
-        <v>43</v>
+        <v>18</v>
       </c>
       <c r="I236" s="11"/>
       <c r="J236" s="12"/>
@@ -11482,7 +11482,7 @@
         <v>17</v>
       </c>
       <c r="H237" s="11" t="s">
-        <v>43</v>
+        <v>18</v>
       </c>
       <c r="I237" s="11"/>
       <c r="J237" s="12"/>
@@ -11507,10 +11507,10 @@
         <v>0.5</v>
       </c>
       <c r="G238" s="12" t="s">
-        <v>42</v>
+        <v>17</v>
       </c>
       <c r="H238" s="11" t="s">
-        <v>43</v>
+        <v>18</v>
       </c>
       <c r="I238" s="11"/>
       <c r="J238" s="12"/>
@@ -11535,10 +11535,10 @@
         <v>0.25</v>
       </c>
       <c r="G239" s="12" t="s">
-        <v>76</v>
+        <v>17</v>
       </c>
       <c r="H239" s="11" t="s">
-        <v>43</v>
+        <v>18</v>
       </c>
       <c r="I239" s="11"/>
       <c r="J239" s="12"/>
@@ -11563,10 +11563,10 @@
         <v>0.5</v>
       </c>
       <c r="G240" s="12" t="s">
-        <v>76</v>
+        <v>17</v>
       </c>
       <c r="H240" s="11" t="s">
-        <v>43</v>
+        <v>18</v>
       </c>
       <c r="I240" s="11"/>
       <c r="J240" s="12"/>
@@ -11594,7 +11594,7 @@
         <v>17</v>
       </c>
       <c r="H241" s="11" t="s">
-        <v>43</v>
+        <v>18</v>
       </c>
       <c r="I241" s="11"/>
       <c r="J241" s="12"/>
@@ -11619,10 +11619,10 @@
         <v>0.5</v>
       </c>
       <c r="G242" s="12" t="s">
-        <v>76</v>
+        <v>17</v>
       </c>
       <c r="H242" s="11" t="s">
-        <v>43</v>
+        <v>18</v>
       </c>
       <c r="I242" s="11"/>
       <c r="J242" s="12"/>
@@ -11647,10 +11647,10 @@
         <v>0.5</v>
       </c>
       <c r="G243" s="12" t="s">
-        <v>76</v>
+        <v>17</v>
       </c>
       <c r="H243" s="11" t="s">
-        <v>43</v>
+        <v>18</v>
       </c>
       <c r="I243" s="11"/>
       <c r="J243" s="12"/>

--- a/Fase 2/Sprint Backlogs/SIGMA_Sprint_Backlog_S2.xlsx
+++ b/Fase 2/Sprint Backlogs/SIGMA_Sprint_Backlog_S2.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Capstone\Fase 2\Sprint Backlogs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5CDDDEA6-7DD0-422B-A384-C0508F704AC0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1600E5EF-322B-489C-AD90-FB3AED775A70}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="15504" yWindow="3432" windowWidth="7536" windowHeight="9072" tabRatio="500" firstSheet="2" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12720" tabRatio="500" firstSheet="2" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sprint" sheetId="1" r:id="rId1"/>
@@ -7309,10 +7309,10 @@
         <v>0.5</v>
       </c>
       <c r="G93" s="12" t="s">
-        <v>42</v>
+        <v>17</v>
       </c>
       <c r="H93" s="11" t="s">
-        <v>43</v>
+        <v>18</v>
       </c>
       <c r="I93" s="11"/>
       <c r="J93" s="12"/>
@@ -7337,10 +7337,10 @@
         <v>0.5</v>
       </c>
       <c r="G94" s="12" t="s">
-        <v>76</v>
+        <v>17</v>
       </c>
       <c r="H94" s="11" t="s">
-        <v>43</v>
+        <v>18</v>
       </c>
       <c r="I94" s="11"/>
       <c r="J94" s="12"/>
@@ -7368,7 +7368,7 @@
         <v>17</v>
       </c>
       <c r="H95" s="11" t="s">
-        <v>43</v>
+        <v>18</v>
       </c>
       <c r="I95" s="11"/>
       <c r="J95" s="12"/>
@@ -7393,10 +7393,10 @@
         <v>0.5</v>
       </c>
       <c r="G96" s="12" t="s">
-        <v>42</v>
+        <v>17</v>
       </c>
       <c r="H96" s="11" t="s">
-        <v>43</v>
+        <v>18</v>
       </c>
       <c r="I96" s="11"/>
       <c r="J96" s="12"/>
@@ -7421,10 +7421,10 @@
         <v>0.5</v>
       </c>
       <c r="G97" s="12" t="s">
-        <v>76</v>
+        <v>17</v>
       </c>
       <c r="H97" s="11" t="s">
-        <v>43</v>
+        <v>18</v>
       </c>
       <c r="I97" s="11"/>
       <c r="J97" s="12"/>
@@ -7452,7 +7452,7 @@
         <v>17</v>
       </c>
       <c r="H98" s="11" t="s">
-        <v>43</v>
+        <v>18</v>
       </c>
       <c r="I98" s="11"/>
       <c r="J98" s="12"/>
@@ -7477,10 +7477,10 @@
         <v>0.5</v>
       </c>
       <c r="G99" s="12" t="s">
-        <v>76</v>
+        <v>17</v>
       </c>
       <c r="H99" s="11" t="s">
-        <v>43</v>
+        <v>18</v>
       </c>
       <c r="I99" s="11"/>
       <c r="J99" s="12"/>
@@ -7508,7 +7508,7 @@
         <v>17</v>
       </c>
       <c r="H100" s="11" t="s">
-        <v>43</v>
+        <v>18</v>
       </c>
       <c r="I100" s="11"/>
       <c r="J100" s="12"/>
@@ -7533,10 +7533,10 @@
         <v>0.5</v>
       </c>
       <c r="G101" s="12" t="s">
-        <v>76</v>
+        <v>17</v>
       </c>
       <c r="H101" s="11" t="s">
-        <v>43</v>
+        <v>18</v>
       </c>
       <c r="I101" s="11"/>
       <c r="J101" s="12"/>
@@ -7564,7 +7564,7 @@
         <v>17</v>
       </c>
       <c r="H102" s="11" t="s">
-        <v>43</v>
+        <v>18</v>
       </c>
       <c r="I102" s="11"/>
       <c r="J102" s="12"/>

--- a/Fase 2/Sprint Backlogs/SIGMA_Sprint_Backlog_S2.xlsx
+++ b/Fase 2/Sprint Backlogs/SIGMA_Sprint_Backlog_S2.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Capstone\Fase 2\Sprint Backlogs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1600E5EF-322B-489C-AD90-FB3AED775A70}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CD2546D2-DE23-4961-B0CB-33DCF64FC3C3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12720" tabRatio="500" firstSheet="2" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -8353,10 +8353,10 @@
         <v>0.5</v>
       </c>
       <c r="G129" s="12" t="s">
-        <v>76</v>
+        <v>17</v>
       </c>
       <c r="H129" s="11" t="s">
-        <v>43</v>
+        <v>18</v>
       </c>
       <c r="I129" s="11"/>
       <c r="J129" s="12"/>
@@ -8384,7 +8384,7 @@
         <v>17</v>
       </c>
       <c r="H130" s="11" t="s">
-        <v>43</v>
+        <v>18</v>
       </c>
       <c r="I130" s="11"/>
       <c r="J130" s="12"/>
@@ -8409,10 +8409,10 @@
         <v>0.25</v>
       </c>
       <c r="G131" s="12" t="s">
-        <v>42</v>
+        <v>17</v>
       </c>
       <c r="H131" s="11" t="s">
-        <v>43</v>
+        <v>18</v>
       </c>
       <c r="I131" s="11"/>
       <c r="J131" s="12"/>
@@ -8437,10 +8437,10 @@
         <v>0.25</v>
       </c>
       <c r="G132" s="12" t="s">
-        <v>76</v>
+        <v>17</v>
       </c>
       <c r="H132" s="11" t="s">
-        <v>43</v>
+        <v>18</v>
       </c>
       <c r="I132" s="11"/>
       <c r="J132" s="12"/>
@@ -8468,7 +8468,7 @@
         <v>17</v>
       </c>
       <c r="H133" s="11" t="s">
-        <v>43</v>
+        <v>18</v>
       </c>
       <c r="I133" s="11"/>
       <c r="J133" s="12"/>
@@ -8493,10 +8493,10 @@
         <v>0.5</v>
       </c>
       <c r="G134" s="12" t="s">
-        <v>76</v>
+        <v>17</v>
       </c>
       <c r="H134" s="11" t="s">
-        <v>43</v>
+        <v>18</v>
       </c>
       <c r="I134" s="11"/>
       <c r="J134" s="12"/>
@@ -8524,7 +8524,7 @@
         <v>17</v>
       </c>
       <c r="H135" s="11" t="s">
-        <v>43</v>
+        <v>18</v>
       </c>
       <c r="I135" s="11"/>
       <c r="J135" s="12"/>
@@ -8549,10 +8549,10 @@
         <v>0.75</v>
       </c>
       <c r="G136" s="12" t="s">
-        <v>76</v>
+        <v>17</v>
       </c>
       <c r="H136" s="11" t="s">
-        <v>43</v>
+        <v>18</v>
       </c>
       <c r="I136" s="11"/>
       <c r="J136" s="12"/>
@@ -8605,10 +8605,10 @@
         <v>0.25</v>
       </c>
       <c r="G138" s="12" t="s">
-        <v>76</v>
+        <v>17</v>
       </c>
       <c r="H138" s="11" t="s">
-        <v>43</v>
+        <v>18</v>
       </c>
       <c r="I138" s="11"/>
       <c r="J138" s="12"/>

--- a/Fase 2/Sprint Backlogs/SIGMA_Sprint_Backlog_S2.xlsx
+++ b/Fase 2/Sprint Backlogs/SIGMA_Sprint_Backlog_S2.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Capstone\Fase 2\Sprint Backlogs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CD2546D2-DE23-4961-B0CB-33DCF64FC3C3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{732B707F-13BC-492E-AA4B-211E22E77C76}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12720" tabRatio="500" firstSheet="2" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12720" tabRatio="500" firstSheet="1" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sprint" sheetId="1" r:id="rId1"/>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2431" uniqueCount="779">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2432" uniqueCount="779">
   <si>
     <t>Sprint 2 · Tareas del Sprint</t>
   </si>
@@ -3514,10 +3514,10 @@
   </sheetData>
   <mergeCells count="10">
     <mergeCell ref="B11:H13"/>
+    <mergeCell ref="C21:H21"/>
     <mergeCell ref="C20:H20"/>
+    <mergeCell ref="C16:H16"/>
     <mergeCell ref="C19:H19"/>
-    <mergeCell ref="C16:H16"/>
-    <mergeCell ref="C21:H21"/>
     <mergeCell ref="C22:H22"/>
     <mergeCell ref="B43:H44"/>
     <mergeCell ref="C23:H23"/>
@@ -4653,9 +4653,11 @@
         <v>5.5</v>
       </c>
       <c r="N26" s="11" t="s">
-        <v>43</v>
-      </c>
-      <c r="O26" s="12"/>
+        <v>18</v>
+      </c>
+      <c r="O26" s="12" t="s">
+        <v>17</v>
+      </c>
       <c r="P26" s="12"/>
     </row>
     <row r="27" spans="1:16" ht="82.8" customHeight="1" x14ac:dyDescent="0.3">
@@ -11062,7 +11064,7 @@
         <v>17</v>
       </c>
       <c r="H222" s="11" t="s">
-        <v>43</v>
+        <v>18</v>
       </c>
       <c r="I222" s="11"/>
       <c r="J222" s="12"/>
@@ -11087,10 +11089,10 @@
         <v>0.25</v>
       </c>
       <c r="G223" s="12" t="s">
-        <v>42</v>
+        <v>17</v>
       </c>
       <c r="H223" s="11" t="s">
-        <v>43</v>
+        <v>18</v>
       </c>
       <c r="I223" s="11"/>
       <c r="J223" s="12"/>
@@ -11115,10 +11117,10 @@
         <v>0.25</v>
       </c>
       <c r="G224" s="12" t="s">
-        <v>76</v>
+        <v>17</v>
       </c>
       <c r="H224" s="11" t="s">
-        <v>43</v>
+        <v>18</v>
       </c>
       <c r="I224" s="11"/>
       <c r="J224" s="12"/>
@@ -11146,7 +11148,7 @@
         <v>17</v>
       </c>
       <c r="H225" s="11" t="s">
-        <v>43</v>
+        <v>18</v>
       </c>
       <c r="I225" s="11"/>
       <c r="J225" s="12"/>
@@ -11171,10 +11173,10 @@
         <v>0.25</v>
       </c>
       <c r="G226" s="12" t="s">
-        <v>42</v>
+        <v>17</v>
       </c>
       <c r="H226" s="11" t="s">
-        <v>43</v>
+        <v>18</v>
       </c>
       <c r="I226" s="11"/>
       <c r="J226" s="12"/>
@@ -11199,10 +11201,10 @@
         <v>0.25</v>
       </c>
       <c r="G227" s="12" t="s">
-        <v>76</v>
+        <v>17</v>
       </c>
       <c r="H227" s="11" t="s">
-        <v>43</v>
+        <v>18</v>
       </c>
       <c r="I227" s="11"/>
       <c r="J227" s="12"/>
@@ -11230,7 +11232,7 @@
         <v>17</v>
       </c>
       <c r="H228" s="11" t="s">
-        <v>43</v>
+        <v>18</v>
       </c>
       <c r="I228" s="11"/>
       <c r="J228" s="12"/>
@@ -11255,10 +11257,10 @@
         <v>0.25</v>
       </c>
       <c r="G229" s="12" t="s">
-        <v>76</v>
+        <v>17</v>
       </c>
       <c r="H229" s="11" t="s">
-        <v>43</v>
+        <v>18</v>
       </c>
       <c r="I229" s="11"/>
       <c r="J229" s="12"/>
@@ -11286,7 +11288,7 @@
         <v>17</v>
       </c>
       <c r="H230" s="11" t="s">
-        <v>43</v>
+        <v>18</v>
       </c>
       <c r="I230" s="11"/>
       <c r="J230" s="12"/>
@@ -11314,7 +11316,7 @@
         <v>17</v>
       </c>
       <c r="H231" s="11" t="s">
-        <v>43</v>
+        <v>18</v>
       </c>
       <c r="I231" s="11"/>
       <c r="J231" s="12"/>

--- a/Fase 2/Sprint Backlogs/SIGMA_Sprint_Backlog_S2.xlsx
+++ b/Fase 2/Sprint Backlogs/SIGMA_Sprint_Backlog_S2.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Capstone\Fase 2\Sprint Backlogs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{732B707F-13BC-492E-AA4B-211E22E77C76}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4C93C91B-537B-4296-92D3-F7CCAC41890C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12720" tabRatio="500" firstSheet="1" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3514,10 +3514,10 @@
   </sheetData>
   <mergeCells count="10">
     <mergeCell ref="B11:H13"/>
+    <mergeCell ref="C20:H20"/>
+    <mergeCell ref="C19:H19"/>
+    <mergeCell ref="C16:H16"/>
     <mergeCell ref="C21:H21"/>
-    <mergeCell ref="C20:H20"/>
-    <mergeCell ref="C16:H16"/>
-    <mergeCell ref="C19:H19"/>
     <mergeCell ref="C22:H22"/>
     <mergeCell ref="B43:H44"/>
     <mergeCell ref="C23:H23"/>
@@ -11736,7 +11736,7 @@
         <v>17</v>
       </c>
       <c r="H246" s="11" t="s">
-        <v>43</v>
+        <v>18</v>
       </c>
       <c r="I246" s="11"/>
       <c r="J246" s="12"/>
@@ -11761,10 +11761,10 @@
         <v>0.5</v>
       </c>
       <c r="G247" s="12" t="s">
-        <v>42</v>
+        <v>17</v>
       </c>
       <c r="H247" s="11" t="s">
-        <v>43</v>
+        <v>18</v>
       </c>
       <c r="I247" s="11"/>
       <c r="J247" s="12"/>
@@ -11789,10 +11789,10 @@
         <v>0.5</v>
       </c>
       <c r="G248" s="12" t="s">
-        <v>76</v>
+        <v>17</v>
       </c>
       <c r="H248" s="11" t="s">
-        <v>43</v>
+        <v>18</v>
       </c>
       <c r="I248" s="11"/>
       <c r="J248" s="12"/>
@@ -11820,7 +11820,7 @@
         <v>17</v>
       </c>
       <c r="H249" s="11" t="s">
-        <v>43</v>
+        <v>18</v>
       </c>
       <c r="I249" s="11"/>
       <c r="J249" s="12"/>
@@ -11845,10 +11845,10 @@
         <v>0.5</v>
       </c>
       <c r="G250" s="12" t="s">
-        <v>42</v>
+        <v>17</v>
       </c>
       <c r="H250" s="11" t="s">
-        <v>43</v>
+        <v>18</v>
       </c>
       <c r="I250" s="11"/>
       <c r="J250" s="12"/>
@@ -11873,10 +11873,10 @@
         <v>0.25</v>
       </c>
       <c r="G251" s="12" t="s">
-        <v>76</v>
+        <v>17</v>
       </c>
       <c r="H251" s="11" t="s">
-        <v>43</v>
+        <v>18</v>
       </c>
       <c r="I251" s="11"/>
       <c r="J251" s="12"/>
@@ -11904,7 +11904,7 @@
         <v>17</v>
       </c>
       <c r="H252" s="11" t="s">
-        <v>43</v>
+        <v>18</v>
       </c>
       <c r="I252" s="11"/>
       <c r="J252" s="12"/>
@@ -11929,10 +11929,10 @@
         <v>0.5</v>
       </c>
       <c r="G253" s="12" t="s">
-        <v>76</v>
+        <v>17</v>
       </c>
       <c r="H253" s="11" t="s">
-        <v>43</v>
+        <v>18</v>
       </c>
       <c r="I253" s="11"/>
       <c r="J253" s="12"/>
@@ -11960,7 +11960,7 @@
         <v>17</v>
       </c>
       <c r="H254" s="11" t="s">
-        <v>43</v>
+        <v>18</v>
       </c>
       <c r="I254" s="11"/>
       <c r="J254" s="12"/>
@@ -11988,7 +11988,7 @@
         <v>17</v>
       </c>
       <c r="H255" s="11" t="s">
-        <v>43</v>
+        <v>18</v>
       </c>
       <c r="I255" s="11"/>
       <c r="J255" s="12"/>
